--- a/betterwaste-kw-audit/Better_Waste_Keyword_Plan.xlsx
+++ b/betterwaste-kw-audit/Better_Waste_Keyword_Plan.xlsx
@@ -578,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -832,13 +832,25 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
+    <row r="27" ht="42" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>Formulas</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>The Keywords, Total SV and Already Ranking columns on Page Summary are live COUNTIF/SUMIF formulas. They show no value until Excel opens and recalculates the file — that is expected. Best Position is a static snapshot of current Semrush rankings, not a formula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>Not verified</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>The Manchester / London / Birmingham city URLs return 301 while the "-old" equivalents return 200. Confirm where those redirects point before acting — see the Fix List.</t>
         </is>
@@ -11902,7 +11914,7 @@
       </c>
       <c r="H1" s="5" t="inlineStr">
         <is>
-          <t>Best Position</t>
+          <t>Best Position (snapshot)</t>
         </is>
       </c>
     </row>
@@ -11939,9 +11951,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A2,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H2" s="14">
-        <f>IF(G2=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A2,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -11977,9 +11990,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A3,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H3" s="14">
-        <f>IF(G3=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A3,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -12015,9 +12029,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A4,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H4" s="14">
-        <f>IF(G4=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A4,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -12053,9 +12068,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A5,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H5" s="14">
-        <f>IF(G5=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A5,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -12091,9 +12107,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A6,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H6" s="14">
-        <f>IF(G6=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A6,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -12129,9 +12146,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A7,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H7" s="14">
-        <f>IF(G7=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A7,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -12167,9 +12185,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A8,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H8" s="14">
-        <f>IF(G8=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A8,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H8" s="14" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -12205,9 +12222,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A9,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H9" s="14">
-        <f>IF(G9=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A9,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -12243,9 +12261,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A10,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H10" s="14">
-        <f>IF(G10=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A10,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H10" s="14" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -12281,9 +12298,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A11,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H11" s="14">
-        <f>IF(G11=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A11,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -12319,9 +12337,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A12,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H12" s="14">
-        <f>IF(G12=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A12,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -12357,9 +12376,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A13,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H13" s="14">
-        <f>IF(G13=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A13,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H13" s="14" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="14">
@@ -12395,9 +12413,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A14,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H14" s="14">
-        <f>IF(G14=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A14,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H14" s="14" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -12433,9 +12450,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A15,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H15" s="14">
-        <f>IF(G15=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A15,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -12471,9 +12489,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A16,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H16" s="14">
-        <f>IF(G16=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A16,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H16" s="14" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -12509,9 +12526,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A17,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H17" s="14">
-        <f>IF(G17=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A17,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H17" s="14" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -12547,9 +12563,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A18,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H18" s="14">
-        <f>IF(G18=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A18,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H18" s="14" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -12585,9 +12600,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A19,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H19" s="14">
-        <f>IF(G19=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A19,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H19" s="14" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="20">
@@ -12623,9 +12637,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A20,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H20" s="14">
-        <f>IF(G20=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A20,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H20" s="14" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="21">
@@ -12661,9 +12674,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A21,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H21" s="14">
-        <f>IF(G21=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A21,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -12699,9 +12713,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A22,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H22" s="14">
-        <f>IF(G22=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A22,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H22" s="14" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -12737,9 +12750,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A23,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H23" s="14">
-        <f>IF(G23=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A23,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -12775,9 +12789,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A24,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H24" s="14">
-        <f>IF(G24=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A24,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -12813,9 +12828,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A25,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H25" s="14">
-        <f>IF(G25=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A25,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -12851,9 +12867,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A26,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H26" s="14">
-        <f>IF(G26=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A26,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H26" s="14" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="27">
@@ -12889,9 +12904,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A27,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H27" s="14">
-        <f>IF(G27=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A27,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H27" s="14" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="28">
@@ -12927,9 +12941,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A28,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H28" s="14">
-        <f>IF(G28=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A28,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H28" s="14" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="29">
@@ -12965,9 +12978,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A29,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H29" s="14">
-        <f>IF(G29=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A29,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -13003,9 +13017,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A30,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H30" s="14">
-        <f>IF(G30=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A30,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H30" s="14" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="31">
@@ -13041,9 +13054,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A31,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H31" s="14">
-        <f>IF(G31=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A31,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -13079,9 +13093,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A32,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H32" s="14">
-        <f>IF(G32=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A32,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -13117,9 +13132,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A33,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H33" s="14">
-        <f>IF(G33=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A33,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H33" s="14" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="34">
@@ -13155,9 +13169,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A34,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H34" s="14">
-        <f>IF(G34=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A34,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H34" s="14" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="35">
@@ -13193,9 +13206,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A35,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H35" s="14">
-        <f>IF(G35=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A35,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -13231,9 +13245,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A36,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H36" s="14">
-        <f>IF(G36=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A36,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -13269,9 +13284,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A37,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H37" s="14">
-        <f>IF(G37=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A37,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H37" s="14" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="38">
@@ -13307,9 +13321,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A38,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H38" s="14">
-        <f>IF(G38=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A38,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H38" s="14" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="39">
@@ -13345,9 +13358,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A39,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H39" s="14">
-        <f>IF(G39=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A39,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -13383,9 +13397,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A40,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H40" s="14">
-        <f>IF(G40=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A40,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -13421,9 +13436,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A41,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H41" s="14">
-        <f>IF(G41=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A41,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -13459,9 +13475,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A42,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H42" s="14">
-        <f>IF(G42=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A42,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -13497,9 +13514,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A43,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H43" s="14">
-        <f>IF(G43=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A43,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -13535,9 +13553,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A44,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H44" s="14">
-        <f>IF(G44=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A44,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H44" s="14" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="45">
@@ -13573,9 +13590,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A45,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H45" s="14">
-        <f>IF(G45=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A45,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -13611,9 +13629,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A46,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H46" s="14">
-        <f>IF(G46=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A46,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -13649,9 +13668,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A47,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H47" s="14">
-        <f>IF(G47=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A47,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -13687,9 +13707,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A48,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H48" s="14">
-        <f>IF(G48=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A48,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -13725,9 +13746,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A49,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H49" s="14">
-        <f>IF(G49=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A49,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -13763,9 +13785,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A50,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H50" s="14">
-        <f>IF(G50=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A50,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -13801,9 +13824,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A51,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H51" s="14">
-        <f>IF(G51=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A51,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -13839,9 +13863,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A52,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H52" s="14">
-        <f>IF(G52=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A52,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H52" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -13877,9 +13902,10 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A53,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H53" s="14">
-        <f>IF(G53=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A53,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -13911,9 +13937,8 @@
         <f>COUNTIFS('Master Plan'!$D$2:$D$170,$A54,'Master Plan'!$K$2:$K$170,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H54" s="14">
-        <f>IF(G54=0,"-",_xlfn.MINIFS('Master Plan'!$K$2:$K$170,'Master Plan'!$D$2:$D$170,$A54,'Master Plan'!$K$2:$K$170,"&gt;0"))</f>
-        <v/>
+      <c r="H54" s="14" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="56">

--- a/betterwaste-kw-audit/Better_Waste_Keyword_Plan.xlsx
+++ b/betterwaste-kw-audit/Better_Waste_Keyword_Plan.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Opportunities'!$A$1:$O$143</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Summary'!$A$1:$H$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Summary'!$A$1:$H$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fix List'!$A$1:$F$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/weee-recycling/</t>
+          <t>https://betterwaste.co.uk/it-equipment-disposal/</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>Page already exists; businesswaste ranks p9</t>
+          <t>Page already exists; businesswaste ranks p9 | This is the form to target on this page (distinct SERP from the spelled-out variant).</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>Page already exists; businesswaste ranks p5</t>
+          <t>Page already exists; businesswaste ranks p5 | This is the form to target on this page (distinct SERP from the spelled-out variant).</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
-          <t>businesswaste ranks p8</t>
+          <t>businesswaste ranks p8 | This is the form to target on this page (distinct SERP from the spelled-out variant).</t>
         </is>
       </c>
     </row>
@@ -1888,12 +1888,12 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/confidential-waste/</t>
+          <t>https://betterwaste.co.uk/paper-and-cardboard-waste/</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>OPTIMISE</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>Page already exists; businesswaste ranks p4</t>
+          <t>Page already exists; businesswaste ranks p4 | This is the form to target on this page (distinct SERP from the spelled-out variant).</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>Page already exists; businesswaste ranks p6</t>
+          <t>Page already exists; businesswaste ranks p6 | This is the form to target on this page (distinct SERP from the spelled-out variant).</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>Page already exists; businesswaste ranks p4</t>
+          <t>Page already exists; businesswaste ranks p4 | This is the form to target on this page (distinct SERP from the spelled-out variant).</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>Page already exists; businesswaste ranks p4</t>
+          <t>Page already exists; businesswaste ranks p4 | This is the form to target on this page (distinct SERP from the spelled-out variant).</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/weee-recycling/</t>
+          <t>https://betterwaste.co.uk/it-equipment-disposal/</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>inherited from "commercial waste collection manchester": BORDERLINE: no site at AS&lt;=25, but lowest is AS 27 (kennywastemanagement) vs Better Waste AS 20; only 2 council/gov slots</t>
+          <t>BORDERLINE: no site at AS&lt;=25 on the shared Manchester commercial-waste SERP, but lowest is AS 27 (kennywastemanagement) vs Better Waste AS 20; only 2 council/gov slots</t>
         </is>
       </c>
       <c r="N66" s="6" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>inherited from "commercial waste collection manchester": BORDERLINE: no site at AS&lt;=25, but lowest is AS 27 (kennywastemanagement) vs Better Waste AS 20; only 2 council/gov slots</t>
+          <t>BORDERLINE: no site at AS&lt;=25 on the shared Manchester commercial-waste SERP, but lowest is AS 27 (kennywastemanagement) vs Better Waste AS 20; only 2 council/gov slots</t>
         </is>
       </c>
       <c r="N70" s="6" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>inherited from "commercial waste collection manchester": BORDERLINE: no site at AS&lt;=25, but lowest is AS 27 (kennywastemanagement) vs Better Waste AS 20; only 2 council/gov slots</t>
+          <t>BORDERLINE: no site at AS&lt;=25 on the shared Manchester commercial-waste SERP, but lowest is AS 27 (kennywastemanagement) vs Better Waste AS 20; only 2 council/gov slots</t>
         </is>
       </c>
       <c r="N71" s="6" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>inherited from "commercial waste collection manchester": BORDERLINE: no site at AS&lt;=25, but lowest is AS 27 (kennywastemanagement) vs Better Waste AS 20; only 2 council/gov slots</t>
+          <t>BORDERLINE: no site at AS&lt;=25 on the shared Manchester commercial-waste SERP, but lowest is AS 27 (kennywastemanagement) vs Better Waste AS 20; only 2 council/gov slots</t>
         </is>
       </c>
       <c r="N74" s="6" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>inherited from "commercial waste collection london": AS 18, 25 at or below Better Waste (AS 20); 3 council/gov slots</t>
+          <t>AS 18 (greenlineenvironmental) and 25 (envirowastemanagement) at or below Better Waste (AS 20) on the shared London commercial-waste SERP; 3 council/gov slots</t>
         </is>
       </c>
       <c r="N75" s="6" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="M78" s="7" t="inlineStr">
         <is>
-          <t>inherited from "commercial waste collection london": AS 18, 25 at or below Better Waste (AS 20); 3 council/gov slots</t>
+          <t>AS 18 (greenlineenvironmental) and 25 (envirowastemanagement) at or below Better Waste (AS 20) on the shared London commercial-waste SERP; 3 council/gov slots</t>
         </is>
       </c>
       <c r="N78" s="6" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
-          <t>inherited from "commercial waste collection manchester": BORDERLINE: no site at AS&lt;=25, but lowest is AS 27 (kennywastemanagement) vs Better Waste AS 20; only 2 council/gov slots</t>
+          <t>BORDERLINE: no site at AS&lt;=25 on the shared Manchester commercial-waste SERP, but lowest is AS 27 (kennywastemanagement) vs Better Waste AS 20; only 2 council/gov slots</t>
         </is>
       </c>
       <c r="N79" s="6" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="M80" s="7" t="inlineStr">
         <is>
-          <t>inherited from "commercial waste collection manchester": BORDERLINE: no site at AS&lt;=25, but lowest is AS 27 (kennywastemanagement) vs Better Waste AS 20; only 2 council/gov slots</t>
+          <t>BORDERLINE: no site at AS&lt;=25 on the shared Manchester commercial-waste SERP, but lowest is AS 27 (kennywastemanagement) vs Better Waste AS 20; only 2 council/gov slots</t>
         </is>
       </c>
       <c r="N80" s="6" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>inherited from "commercial waste collection manchester": BORDERLINE: no site at AS&lt;=25, but lowest is AS 27 (kennywastemanagement) vs Better Waste AS 20; only 2 council/gov slots</t>
+          <t>BORDERLINE: no site at AS&lt;=25 on the shared Manchester commercial-waste SERP, but lowest is AS 27 (kennywastemanagement) vs Better Waste AS 20; only 2 council/gov slots</t>
         </is>
       </c>
       <c r="N85" s="6" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>inherited from "commercial waste collection manchester": BORDERLINE: no site at AS&lt;=25, but lowest is AS 27 (kennywastemanagement) vs Better Waste AS 20; only 2 council/gov slots</t>
+          <t>BORDERLINE: no site at AS&lt;=25 on the shared Manchester commercial-waste SERP, but lowest is AS 27 (kennywastemanagement) vs Better Waste AS 20; only 2 council/gov slots</t>
         </is>
       </c>
       <c r="N89" s="6" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="O130" s="7" t="inlineStr">
         <is>
-          <t>Currently p39 - already ranking</t>
+          <t>Currently p39 - already ranking | Do NOT target on this page - retail SERP. The abbreviated form on the same page is the winnable one.</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="O135" s="7" t="inlineStr">
         <is>
-          <t>/binpedia/ already p39 for waste container</t>
+          <t>/binpedia/ already p39 for waste container | Do NOT target on this page - retail SERP. The abbreviated form on the same page is the winnable one.</t>
         </is>
       </c>
     </row>
@@ -9837,7 +9837,11 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="O136" s="7" t="inlineStr"/>
+      <c r="O136" s="7" t="inlineStr">
+        <is>
+          <t>Do NOT target on this page - retail SERP. The abbreviated form on the same page is the winnable one.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
@@ -9959,7 +9963,11 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="O138" s="7" t="inlineStr"/>
+      <c r="O138" s="7" t="inlineStr">
+        <is>
+          <t>Do NOT target on this page - retail SERP. The abbreviated form on the same page is the winnable one.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
@@ -10085,7 +10093,11 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="O140" s="7" t="inlineStr"/>
+      <c r="O140" s="7" t="inlineStr">
+        <is>
+          <t>Do NOT target on this page - retail SERP. The abbreviated form on the same page is the winnable one.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
@@ -10146,7 +10158,11 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="O141" s="7" t="inlineStr"/>
+      <c r="O141" s="7" t="inlineStr">
+        <is>
+          <t>Do NOT target on this page - retail SERP. The abbreviated form on the same page is the winnable one.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
@@ -10268,7 +10284,11 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="O143" s="7" t="inlineStr"/>
+      <c r="O143" s="7" t="inlineStr">
+        <is>
+          <t>Do NOT target on this page - retail SERP. The abbreviated form on the same page is the winnable one.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O143"/>
@@ -10282,7 +10302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -11071,12 +11091,12 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/metal-waste/</t>
+          <t>https://betterwaste.co.uk/it-equipment-disposal/</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Waste Type</t>
+          <t>Gap vs competitors</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -11110,17 +11130,17 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/office-waste-management/</t>
+          <t>https://betterwaste.co.uk/metal-waste/</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Gap vs competitors</t>
+          <t>Waste Type</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>OPTIMISE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
@@ -11140,14 +11160,16 @@
         <f>COUNTIFS('Opportunities'!$D$2:$D$143,$A22,'Opportunities'!$J$2:$J$143,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H22" s="12" t="n">
-        <v>65</v>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/paper-and-cardboard-waste/</t>
+          <t>https://betterwaste.co.uk/office-waste-management/</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
@@ -11178,18 +11200,18 @@
         <v/>
       </c>
       <c r="H23" s="12" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/pub-waste-management/</t>
+          <t>https://betterwaste.co.uk/paper-and-cardboard-waste/</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Gap vs competitors</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
@@ -11215,13 +11237,13 @@
         <v/>
       </c>
       <c r="H24" s="12" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/restaurant-waste-management/</t>
+          <t>https://betterwaste.co.uk/pub-waste-management/</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
@@ -11252,13 +11274,13 @@
         <v/>
       </c>
       <c r="H25" s="12" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/retail-waste-management/</t>
+          <t>https://betterwaste.co.uk/restaurant-waste-management/</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
@@ -11289,23 +11311,23 @@
         <v/>
       </c>
       <c r="H26" s="12" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/sanitary-waste/</t>
+          <t>https://betterwaste.co.uk/retail-waste-management/</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Waste Type</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>OPTIMISE</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
@@ -11325,26 +11347,24 @@
         <f>COUNTIFS('Opportunities'!$D$2:$D$143,$A27,'Opportunities'!$J$2:$J$143,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H27" s="12" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/takeaway-waste-management/</t>
+          <t>https://betterwaste.co.uk/sanitary-waste/</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Waste Type</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>OPTIMISE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
@@ -11364,24 +11384,26 @@
         <f>COUNTIFS('Opportunities'!$D$2:$D$143,$A28,'Opportunities'!$J$2:$J$143,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H28" s="12" t="n">
-        <v>15</v>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/weee-recycling/</t>
+          <t>https://betterwaste.co.uk/takeaway-waste-management/</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Gap vs competitors</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>OPTIMISE</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
@@ -11401,10 +11423,8 @@
         <f>COUNTIFS('Opportunities'!$D$2:$D$143,$A29,'Opportunities'!$J$2:$J$143,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H29" s="12" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -12369,22 +12389,22 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/bins/fel-container/</t>
+          <t>https://betterwaste.co.uk/weee-recycling/</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Gap vs competitors</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>OPTIMISE</t>
-        </is>
-      </c>
-      <c r="D55" s="16" t="inlineStr">
-        <is>
-          <t>AVOID</t>
+          <t>CREATE</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>HARD</t>
         </is>
       </c>
       <c r="E55" s="12">
@@ -12408,17 +12428,17 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/hazardous-waste/</t>
+          <t>https://betterwaste.co.uk/bins/fel-container/</t>
         </is>
       </c>
       <c r="B56" s="12" t="inlineStr">
         <is>
-          <t>Waste Type</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>OPTIMISE</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
@@ -12447,7 +12467,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>https://betterwaste.co.uk/hazardous-waste/</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
@@ -12457,7 +12477,7 @@
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>EXCLUDE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
@@ -12483,27 +12503,66 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>Waste Type</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="E58" s="12">
+        <f>COUNTIF('Opportunities'!$D$2:$D$143,$A58)</f>
+        <v/>
+      </c>
+      <c r="F58" s="12">
+        <f>SUMIF('Opportunities'!$D$2:$D$143,$A58,'Opportunities'!$H$2:$H$143)</f>
+        <v/>
+      </c>
+      <c r="G58" s="12">
+        <f>COUNTIFS('Opportunities'!$D$2:$D$143,$A58,'Opportunities'!$J$2:$J$143,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="H58" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E59" s="2">
-        <f>SUM(E2:E57)</f>
-        <v/>
-      </c>
-      <c r="F59" s="2">
-        <f>SUM(F2:F57)</f>
-        <v/>
-      </c>
-      <c r="G59" s="2">
-        <f>SUM(G2:G57)</f>
+      <c r="E60" s="2">
+        <f>SUM(E2:E58)</f>
+        <v/>
+      </c>
+      <c r="F60" s="2">
+        <f>SUM(F2:F58)</f>
+        <v/>
+      </c>
+      <c r="G60" s="2">
+        <f>SUM(G2:G58)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H57"/>
+  <autoFilter ref="A1:H58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13049,7 +13108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
@@ -13589,7 +13648,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>/wood-waste/</t>
+          <t>/it-equipment-disposal/</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -13604,14 +13663,14 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>EASY · 390 SV</t>
+          <t>EASY · 2,490 SV — split out of the WEEE page, which is mostly AVOID/HARD</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>/cooking-oil-collection/</t>
+          <t>/commercial-skip-hire/</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -13626,14 +13685,14 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>EASY · 320 SV</t>
+          <t>EASY · 8,120 SV — check service fit first</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>/butchers-waste-collection/</t>
+          <t>/wood-waste/</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -13648,14 +13707,14 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>EASY · 260 SV</t>
+          <t>EASY · 390 SV</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>/metal-waste/</t>
+          <t>/cooking-oil-collection/</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -13670,14 +13729,14 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>EASY · 260 SV — check service model first</t>
+          <t>EASY · 320 SV</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>/areas-we-cover/liverpool/</t>
+          <t>/butchers-waste-collection/</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -13699,89 +13758,89 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
+          <t>/metal-waste/</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>EASY · 260 SV — check service model first</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>/areas-we-cover/liverpool/</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>Missing</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>EASY · 260 SV</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
           <t>/areas-we-cover/glasgow/</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C36" s="22" t="inlineStr">
         <is>
           <t>Missing</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>EASY · 70 SV</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr"/>
-      <c r="B35" s="7" t="inlineStr"/>
-      <c r="C35" s="7" t="inlineStr"/>
-      <c r="D35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr"/>
+      <c r="B37" s="7" t="inlineStr"/>
+      <c r="C37" s="7" t="inlineStr"/>
+      <c r="D37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>INDEX BLOAT — live 200s that should not be indexable</t>
         </is>
       </c>
-      <c r="B36" s="20" t="n"/>
-      <c r="C36" s="20" t="n"/>
-      <c r="D36" s="20" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>/222-2/ · /test-2/ · /home/ · /thank-you/ · /thank-you-2/ · /trial-form/ · /demos/</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Remove or noindex</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>/quote2-old/ · /quote-commercial-waste-old/ · /quote-waste-services-old/</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Superseded quote forms</t>
-        </is>
-      </c>
+      <c r="B38" s="20" t="n"/>
+      <c r="C38" s="20" t="n"/>
+      <c r="D38" s="20" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>/quote2/?slink= (six parameter variants)</t>
+          <t>/222-2/ · /test-2/ · /home/ · /thank-you/ · /thank-you-2/ · /trial-form/ · /demos/</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -13796,87 +13855,131 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Add parameter handling</t>
+          <t>Remove or noindex</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
+          <t>/quote2-old/ · /quote-commercial-waste-old/ · /quote-waste-services-old/</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Superseded quote forms</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>/quote2/?slink= (six parameter variants)</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>Add parameter handling</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
           <t>/about · /binpedia · /contact-us · /blog · /faqs · /how-to-be-green</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>Also resolve with a trailing slash — pick one convention</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr"/>
-      <c r="B41" s="7" t="inlineStr"/>
-      <c r="C41" s="7" t="inlineStr"/>
-      <c r="D41" s="7" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="19" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr"/>
+      <c r="B43" s="7" t="inlineStr"/>
+      <c r="C43" s="7" t="inlineStr"/>
+      <c r="D43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>404 — former pages that may hold links</t>
         </is>
       </c>
-      <c r="B42" s="20" t="n"/>
-      <c r="C42" s="20" t="n"/>
-      <c r="D42" s="20" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="B44" s="20" t="n"/>
+      <c r="C44" s="20" t="n"/>
+      <c r="D44" s="20" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>/better-waste-solutions-birmingham/ · -london/ · -manchester/</t>
         </is>
       </c>
-      <c r="B43" s="17" t="inlineStr">
+      <c r="B45" s="17" t="inlineStr">
         <is>
           <t>404</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>Gone</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>Check referring domains, then 301 to the city pages</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>/business-waste-management-yorkshire/</t>
         </is>
       </c>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B46" s="17" t="inlineStr">
         <is>
           <t>404</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>Gone</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>Check referring domains</t>
         </is>

--- a/betterwaste-kw-audit/Better_Waste_Keyword_Plan.xlsx
+++ b/betterwaste-kw-audit/Better_Waste_Keyword_Plan.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Page Inventory" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Opportunities'!$A$1:$O$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Opportunities'!$A$1:$P$143</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Summary'!$A$1:$H$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Fix List'!$A$1:$F$16</definedName>
   </definedNames>
@@ -566,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -835,22 +835,34 @@
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>Data Confidence</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Every volume was re-pulled from Semrush and diffed against the sheet; 20 values were corrected. Seven long-tail keywords return no Semrush keyword-overview data at all - their volume comes from the organic rankings report only and they are flagged LOW in the Data Confidence column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>Formulas</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>The Keywords, Total SV and Already Ranking columns on Page Summary are live COUNTIF/SUMIF formulas. They show no value until Excel opens and recalculates the file — that is expected. Best Position is a static snapshot of current Semrush rankings, not a formula.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Not verified</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>The Manchester / London / Birmingham city URLs return 301 while the "-old" equivalents return 200. Confirm where those redirects point before acting — see the Fix List.</t>
         </is>
@@ -867,7 +879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O143"/>
+  <dimension ref="A1:P143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -883,8 +895,9 @@
     <col width="46" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="70" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="44" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="44" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -955,10 +968,15 @@
       </c>
       <c r="N1" s="5" t="inlineStr">
         <is>
+          <t>Data Confidence</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1020,10 +1038,15 @@
       </c>
       <c r="N2" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O2" s="7" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>CHECK SERVICE FIT before building</t>
         </is>
@@ -1085,10 +1108,15 @@
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O3" s="7" t="inlineStr">
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>thefirstmile.co.uk ranks p3</t>
         </is>
@@ -1150,10 +1178,15 @@
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O4" s="7" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>CHECK SERVICE FIT</t>
         </is>
@@ -1215,10 +1248,15 @@
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>thefirstmile.co.uk ranks p3</t>
         </is>
@@ -1280,10 +1318,15 @@
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>Page already exists; businesswaste ranks p9 | This is the form to target on this page (distinct SERP from the spelled-out variant).</t>
         </is>
@@ -1345,10 +1388,15 @@
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O7" s="7" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>BEST ROI - lowest KD highest value. businesswaste p3</t>
         </is>
@@ -1410,10 +1458,15 @@
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O8" s="7" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>businesswaste.co.uk p4</t>
         </is>
@@ -1475,10 +1528,15 @@
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O9" s="7" t="inlineStr">
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>CHECK SERVICE FIT</t>
         </is>
@@ -1540,10 +1598,15 @@
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O10" s="7" t="inlineStr">
+      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>CHECK SERVICE FIT</t>
         </is>
@@ -1605,10 +1668,15 @@
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O11" s="7" t="inlineStr">
+      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>Small shredders dominate; Restore AS 37 is the only large player</t>
         </is>
@@ -1670,10 +1738,15 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>Very low KD</t>
         </is>
@@ -1735,10 +1808,15 @@
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr"/>
+      <c r="P13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1796,10 +1874,15 @@
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>Page already exists; businesswaste ranks p5 | This is the form to target on this page (distinct SERP from the spelled-out variant).</t>
         </is>
@@ -1861,10 +1944,15 @@
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
+      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>businesswaste ranks p8 | This is the form to target on this page (distinct SERP from the spelled-out variant).</t>
         </is>
@@ -1926,10 +2014,15 @@
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>Map to paper/cardboard page; thefirstmile ranks p2</t>
         </is>
@@ -1991,10 +2084,15 @@
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
+      <c r="P17" s="7" t="inlineStr">
         <is>
           <t>thefirstmile.co.uk ranks p5</t>
         </is>
@@ -2056,10 +2154,15 @@
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O18" s="7" t="inlineStr">
+      <c r="P18" s="7" t="inlineStr">
         <is>
           <t>thefirstmile.co.uk ranks p3</t>
         </is>
@@ -2121,10 +2224,15 @@
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O19" s="7" t="inlineStr">
+      <c r="P19" s="7" t="inlineStr">
         <is>
           <t>Page already exists; businesswaste ranks p4 | This is the form to target on this page (distinct SERP from the spelled-out variant).</t>
         </is>
@@ -2186,10 +2294,15 @@
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O20" s="7" t="inlineStr">
+      <c r="P20" s="7" t="inlineStr">
         <is>
           <t>Page already exists; businesswaste ranks p6 | This is the form to target on this page (distinct SERP from the spelled-out variant).</t>
         </is>
@@ -2251,10 +2364,15 @@
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O21" s="7" t="inlineStr">
+      <c r="P21" s="7" t="inlineStr">
         <is>
           <t>Page already exists; businesswaste ranks p4 | This is the form to target on this page (distinct SERP from the spelled-out variant).</t>
         </is>
@@ -2316,10 +2434,15 @@
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O22" s="7" t="inlineStr">
+      <c r="P22" s="7" t="inlineStr">
         <is>
           <t>recorra ranks p6. KD 9</t>
         </is>
@@ -2381,10 +2504,15 @@
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O23" s="7" t="inlineStr">
+      <c r="P23" s="7" t="inlineStr">
         <is>
           <t>recorra.co.uk ranks p8</t>
         </is>
@@ -2446,10 +2574,15 @@
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O24" s="7" t="inlineStr">
+      <c r="P24" s="7" t="inlineStr">
         <is>
           <t>Page already exists; businesswaste ranks p4 | This is the form to target on this page (distinct SERP from the spelled-out variant).</t>
         </is>
@@ -2511,10 +2644,15 @@
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O25" s="7" t="inlineStr">
+      <c r="P25" s="7" t="inlineStr">
         <is>
           <t>CHECK SERVICE FIT</t>
         </is>
@@ -2576,10 +2714,15 @@
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O26" s="7" t="inlineStr">
+      <c r="P26" s="7" t="inlineStr">
         <is>
           <t>Transactional intent, KD 9</t>
         </is>
@@ -2641,10 +2784,15 @@
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O27" s="7" t="inlineStr"/>
+      <c r="P27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -2702,10 +2850,15 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O28" s="7" t="inlineStr"/>
+      <c r="P28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -2769,10 +2922,15 @@
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O29" s="7" t="inlineStr"/>
+      <c r="P29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -2830,10 +2988,15 @@
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O30" s="7" t="inlineStr">
+      <c r="P30" s="7" t="inlineStr">
         <is>
           <t>Very low KD</t>
         </is>
@@ -2895,10 +3058,15 @@
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O31" s="7" t="inlineStr"/>
+      <c r="P31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -2940,7 +3108,7 @@
         <v>390</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>63</v>
@@ -2962,10 +3130,15 @@
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O32" s="7" t="inlineStr">
+      <c r="P32" s="7" t="inlineStr">
         <is>
           <t>Not in sheet. Currently p63</t>
         </is>
@@ -3027,10 +3200,15 @@
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O33" s="7" t="inlineStr">
+      <c r="P33" s="7" t="inlineStr">
         <is>
           <t>Pairs with existing food waste pages</t>
         </is>
@@ -3092,10 +3270,15 @@
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O34" s="7" t="inlineStr"/>
+      <c r="P34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -3153,10 +3336,15 @@
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O35" s="7" t="inlineStr"/>
+      <c r="P35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -3220,10 +3408,15 @@
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O36" s="7" t="inlineStr"/>
+      <c r="P36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -3281,10 +3474,15 @@
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O37" s="7" t="inlineStr">
+      <c r="P37" s="7" t="inlineStr">
         <is>
           <t>wastemanaged.co.uk p4. Lowest KD in cluster</t>
         </is>
@@ -3298,17 +3496,17 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>E - Existing push</t>
+          <t>F - Locations</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/hair-salon-waste-management/</t>
+          <t>https://betterwaste.co.uk/areas-we-cover/leeds/</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -3318,28 +3516,22 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>salon waste management</t>
+          <t>commercial waste collection leeds</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H38" s="6" t="n">
         <v>260</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J38" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="K38" s="7" t="inlineStr">
-        <is>
-          <t>https://betterwaste.co.uk/hair-salon-waste-management/</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="J38" s="6" t="inlineStr"/>
+      <c r="K38" s="7" t="inlineStr"/>
       <c r="L38" s="8" t="inlineStr">
         <is>
           <t>EASY</t>
@@ -3347,19 +3539,20 @@
       </c>
       <c r="M38" s="7" t="inlineStr">
         <is>
-          <t>inherited from "butchers waste collection": AS 10, 10, 24 at or below Better Waste (AS 20); 1 council/gov slots</t>
+          <t>AS 13, 21, 21, 24, 25 at or below Better Waste (AS 20); 2 council/gov slots</t>
         </is>
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O38" s="7" t="inlineStr">
-        <is>
-          <t>Currently p21</t>
-        </is>
-      </c>
+      <c r="P38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -3379,17 +3572,17 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/areas-we-cover/leeds/</t>
+          <t>https://betterwaste.co.uk/areas-we-cover/liverpool/</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>OPTIMISE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>commercial waste collection leeds</t>
+          <t>commercial waste collection liverpool</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
@@ -3401,7 +3594,7 @@
         <v>260</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J39" s="6" t="inlineStr"/>
       <c r="K39" s="7" t="inlineStr"/>
@@ -3412,15 +3605,24 @@
       </c>
       <c r="M39" s="7" t="inlineStr">
         <is>
-          <t>AS 13, 21, 21, 24, 25 at or below Better Waste (AS 20); 2 council/gov slots</t>
+          <t>inherited from "commercial waste collection leeds": AS 13, 21, 21, 24, 25 at or below Better Waste (AS 20); 2 council/gov slots</t>
         </is>
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O39" s="7" t="inlineStr"/>
+      <c r="P39" s="7" t="inlineStr">
+        <is>
+          <t>No page exists</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -3430,32 +3632,32 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Waste Type</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>F - Locations</t>
+          <t>Sheet gap</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/areas-we-cover/liverpool/</t>
+          <t>https://betterwaste.co.uk/paper-and-cardboard-waste/</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>OPTIMISE</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>commercial waste collection liverpool</t>
+          <t>commercial paper recycling</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H40" s="6" t="n">
@@ -3464,8 +3666,14 @@
       <c r="I40" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="J40" s="6" t="inlineStr"/>
-      <c r="K40" s="7" t="inlineStr"/>
+      <c r="J40" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>https://betterwaste.co.uk/paper-and-cardboard-waste/</t>
+        </is>
+      </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
           <t>EASY</t>
@@ -3473,17 +3681,22 @@
       </c>
       <c r="M40" s="7" t="inlineStr">
         <is>
-          <t>inherited from "commercial waste collection leeds": AS 13, 21, 21, 24, 25 at or below Better Waste (AS 20); 2 council/gov slots</t>
+          <t>inherited from "business cardboard recycling": AS 16, 18, 20 at or below Better Waste (AS 20)</t>
         </is>
       </c>
       <c r="N40" s="6" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="O40" s="7" t="inlineStr">
-        <is>
-          <t>No page exists</t>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>Not in sheet. Currently p73</t>
         </is>
       </c>
     </row>
@@ -3495,17 +3708,17 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Waste Type</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Sheet gap</t>
+          <t>E - Existing push</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/paper-and-cardboard-waste/</t>
+          <t>https://betterwaste.co.uk/hair-salon-waste-management/</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -3515,7 +3728,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>commercial paper recycling</t>
+          <t>salon waste management</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -3524,17 +3737,17 @@
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/paper-and-cardboard-waste/</t>
+          <t>https://betterwaste.co.uk/hair-salon-waste-management/</t>
         </is>
       </c>
       <c r="L41" s="8" t="inlineStr">
@@ -3544,17 +3757,22 @@
       </c>
       <c r="M41" s="7" t="inlineStr">
         <is>
-          <t>inherited from "business cardboard recycling": AS 16, 18, 20 at or below Better Waste (AS 20)</t>
+          <t>inherited from "butchers waste collection": AS 10, 10, 24 at or below Better Waste (AS 20); 1 council/gov slots</t>
         </is>
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="O41" s="7" t="inlineStr">
-        <is>
-          <t>Not in sheet. Currently p73</t>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O41" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="P41" s="7" t="inlineStr">
+        <is>
+          <t>Currently p21</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3804,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>cafe waste collection</t>
+          <t>cafe waste management</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -3598,10 +3816,10 @@
         <v>210</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
@@ -3620,12 +3838,17 @@
       </c>
       <c r="N42" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O42" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O42" s="7" t="inlineStr">
-        <is>
-          <t>Currently p19</t>
+      <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>Currently p22</t>
         </is>
       </c>
     </row>
@@ -3637,17 +3860,17 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Waste Type</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>E - Existing push</t>
+          <t>Sheet gap</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/cafe-waste-management/</t>
+          <t>https://betterwaste.co.uk/paper-and-cardboard-waste/</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -3657,26 +3880,26 @@
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>cafe waste management</t>
+          <t>commercial cardboard collection</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
         <v>210</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/cafe-waste-management/</t>
+          <t>https://betterwaste.co.uk/paper-and-cardboard-waste/</t>
         </is>
       </c>
       <c r="L43" s="8" t="inlineStr">
@@ -3686,17 +3909,22 @@
       </c>
       <c r="M43" s="7" t="inlineStr">
         <is>
-          <t>inherited from "butchers waste collection": AS 10, 10, 24 at or below Better Waste (AS 20); 1 council/gov slots</t>
+          <t>inherited from "business cardboard recycling": AS 16, 18, 20 at or below Better Waste (AS 20)</t>
         </is>
       </c>
       <c r="N43" s="6" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="O43" s="7" t="inlineStr">
-        <is>
-          <t>Currently p22</t>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O43" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="P43" s="7" t="inlineStr">
+        <is>
+          <t>Not in sheet. Currently p36</t>
         </is>
       </c>
     </row>
@@ -3737,10 +3965,10 @@
         </is>
       </c>
       <c r="H44" s="6" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J44" s="6" t="n">
         <v>25</v>
@@ -3762,10 +3990,15 @@
       </c>
       <c r="N44" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O44" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O44" s="7" t="inlineStr">
+      <c r="P44" s="7" t="inlineStr">
         <is>
           <t>Currently p25</t>
         </is>
@@ -3779,17 +4012,17 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Waste Type</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Sheet gap</t>
+          <t>E - Existing push</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/paper-and-cardboard-waste/</t>
+          <t>https://betterwaste.co.uk/restaurant-waste-management/</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -3799,26 +4032,26 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>commercial cardboard collection</t>
+          <t>restaurant waste disposal</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/paper-and-cardboard-waste/</t>
+          <t>https://betterwaste.co.uk/restaurant-waste-management/</t>
         </is>
       </c>
       <c r="L45" s="8" t="inlineStr">
@@ -3828,17 +4061,22 @@
       </c>
       <c r="M45" s="7" t="inlineStr">
         <is>
-          <t>inherited from "business cardboard recycling": AS 16, 18, 20 at or below Better Waste (AS 20)</t>
+          <t>inherited from "butchers waste collection": AS 10, 10, 24 at or below Better Waste (AS 20); 1 council/gov slots</t>
         </is>
       </c>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="O45" s="7" t="inlineStr">
-        <is>
-          <t>Not in sheet. Currently p36</t>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O45" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>Currently p27</t>
         </is>
       </c>
     </row>
@@ -3860,7 +4098,7 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/restaurant-waste-management/</t>
+          <t>https://betterwaste.co.uk/takeaway-waste-management/</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -3870,7 +4108,7 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>restaurant waste disposal</t>
+          <t>takeaway waste collection</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -3879,17 +4117,17 @@
         </is>
       </c>
       <c r="H46" s="6" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/restaurant-waste-management/</t>
+          <t>https://betterwaste.co.uk/takeaway-waste-management/</t>
         </is>
       </c>
       <c r="L46" s="8" t="inlineStr">
@@ -3904,12 +4142,17 @@
       </c>
       <c r="N46" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O46" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O46" s="7" t="inlineStr">
-        <is>
-          <t>Currently p27</t>
+      <c r="P46" s="7" t="inlineStr">
+        <is>
+          <t>Currently p15</t>
         </is>
       </c>
     </row>
@@ -3931,7 +4174,7 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/takeaway-waste-management/</t>
+          <t>https://betterwaste.co.uk/pub-waste-management/</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -3941,7 +4184,7 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>takeaway waste collection</t>
+          <t>pub waste management</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -3950,17 +4193,17 @@
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>8</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/takeaway-waste-management/</t>
+          <t>https://betterwaste.co.uk/pub-waste-management/</t>
         </is>
       </c>
       <c r="L47" s="8" t="inlineStr">
@@ -3975,12 +4218,17 @@
       </c>
       <c r="N47" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O47" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O47" s="7" t="inlineStr">
-        <is>
-          <t>Currently p15</t>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>Currently p13</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4250,7 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/pub-waste-management/</t>
+          <t>https://betterwaste.co.uk/restaurant-waste-management/</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -4012,7 +4260,7 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>pub waste management</t>
+          <t>restaurant waste collection</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -4024,14 +4272,14 @@
         <v>140</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/pub-waste-management/</t>
+          <t>https://betterwaste.co.uk/restaurant-waste-management/</t>
         </is>
       </c>
       <c r="L48" s="8" t="inlineStr">
@@ -4046,12 +4294,17 @@
       </c>
       <c r="N48" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O48" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O48" s="7" t="inlineStr">
-        <is>
-          <t>Currently p13</t>
+      <c r="P48" s="7" t="inlineStr">
+        <is>
+          <t>Currently p26</t>
         </is>
       </c>
     </row>
@@ -4063,17 +4316,17 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Waste Type</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>E - Existing push</t>
+          <t>Sheet gap</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/restaurant-waste-management/</t>
+          <t>https://betterwaste.co.uk/paper-and-cardboard-waste/</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -4083,7 +4336,7 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>restaurant waste collection</t>
+          <t>cardboard recycling for businesses</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -4095,14 +4348,14 @@
         <v>140</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/restaurant-waste-management/</t>
+          <t>https://betterwaste.co.uk/paper-and-cardboard-waste/</t>
         </is>
       </c>
       <c r="L49" s="8" t="inlineStr">
@@ -4112,17 +4365,22 @@
       </c>
       <c r="M49" s="7" t="inlineStr">
         <is>
-          <t>inherited from "butchers waste collection": AS 10, 10, 24 at or below Better Waste (AS 20); 1 council/gov slots</t>
+          <t>inherited from "business cardboard recycling": AS 16, 18, 20 at or below Better Waste (AS 20)</t>
         </is>
       </c>
       <c r="N49" s="6" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="O49" s="7" t="inlineStr">
-        <is>
-          <t>Currently p26</t>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O49" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>Not in sheet. Currently p63</t>
         </is>
       </c>
     </row>
@@ -4134,17 +4392,17 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Waste Type</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Sheet gap</t>
+          <t>E - Existing push</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/paper-and-cardboard-waste/</t>
+          <t>https://betterwaste.co.uk/restaurant-waste-management/</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -4154,26 +4412,26 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>cardboard recycling for businesses</t>
+          <t>restaurant waste removal</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H50" s="6" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/paper-and-cardboard-waste/</t>
+          <t>https://betterwaste.co.uk/restaurant-waste-management/</t>
         </is>
       </c>
       <c r="L50" s="8" t="inlineStr">
@@ -4183,17 +4441,22 @@
       </c>
       <c r="M50" s="7" t="inlineStr">
         <is>
-          <t>inherited from "business cardboard recycling": AS 16, 18, 20 at or below Better Waste (AS 20)</t>
+          <t>inherited from "butchers waste collection": AS 10, 10, 24 at or below Better Waste (AS 20); 1 council/gov slots</t>
         </is>
       </c>
       <c r="N50" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="O50" s="7" t="inlineStr">
-        <is>
-          <t>Not in sheet. Currently p63</t>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O50" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="P50" s="7" t="inlineStr">
+        <is>
+          <t>Currently p25</t>
         </is>
       </c>
     </row>
@@ -4205,17 +4468,17 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>E - Existing push</t>
+          <t>F - Locations</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/restaurant-waste-management/</t>
+          <t>https://betterwaste.co.uk/areas-we-cover/bristol/</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -4225,7 +4488,7 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>restaurant waste removal</t>
+          <t>commercial waste collection bristol</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -4234,19 +4497,13 @@
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="J51" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>https://betterwaste.co.uk/restaurant-waste-management/</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="J51" s="6" t="inlineStr"/>
+      <c r="K51" s="7" t="inlineStr"/>
       <c r="L51" s="8" t="inlineStr">
         <is>
           <t>EASY</t>
@@ -4254,17 +4511,22 @@
       </c>
       <c r="M51" s="7" t="inlineStr">
         <is>
-          <t>inherited from "butchers waste collection": AS 10, 10, 24 at or below Better Waste (AS 20); 1 council/gov slots</t>
+          <t>inherited from "commercial waste collection leeds": AS 13, 21, 21, 24, 25 at or below Better Waste (AS 20); 2 council/gov slots</t>
         </is>
       </c>
       <c r="N51" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O51" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O51" s="7" t="inlineStr">
-        <is>
-          <t>Currently p25</t>
+      <c r="P51" s="7" t="inlineStr">
+        <is>
+          <t>No page exists</t>
         </is>
       </c>
     </row>
@@ -4276,17 +4538,17 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Waste Type</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Sheet gap</t>
+          <t>F - Locations</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/dry-mixed-recycling-waste/</t>
+          <t>https://betterwaste.co.uk/areas-we-cover/nottingham/</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -4296,28 +4558,22 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>mixed recycling collection</t>
+          <t>commercial waste collection nottingham</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H52" s="6" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="J52" s="6" t="n">
-        <v>57</v>
-      </c>
-      <c r="K52" s="7" t="inlineStr">
-        <is>
-          <t>https://betterwaste.co.uk/dry-mixed-recycling-waste/</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J52" s="6" t="inlineStr"/>
+      <c r="K52" s="7" t="inlineStr"/>
       <c r="L52" s="8" t="inlineStr">
         <is>
           <t>EASY</t>
@@ -4325,17 +4581,22 @@
       </c>
       <c r="M52" s="7" t="inlineStr">
         <is>
-          <t>inherited from "business cardboard recycling": AS 16, 18, 20 at or below Better Waste (AS 20)</t>
+          <t>inherited from "commercial waste collection leeds": AS 13, 21, 21, 24, 25 at or below Better Waste (AS 20); 2 council/gov slots</t>
         </is>
       </c>
       <c r="N52" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="O52" s="7" t="inlineStr">
-        <is>
-          <t>Not in sheet. Currently p57</t>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O52" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>No page exists</t>
         </is>
       </c>
     </row>
@@ -4347,17 +4608,17 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Waste Type</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>F - Locations</t>
+          <t>Sheet gap</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/areas-we-cover/bristol/</t>
+          <t>https://betterwaste.co.uk/dry-mixed-recycling-waste/</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -4367,22 +4628,28 @@
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>commercial waste collection bristol</t>
+          <t>mixed recycling collection</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
         <v>90</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="J53" s="6" t="inlineStr"/>
-      <c r="K53" s="7" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>https://betterwaste.co.uk/dry-mixed-recycling-waste/</t>
+        </is>
+      </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
           <t>EASY</t>
@@ -4390,17 +4657,22 @@
       </c>
       <c r="M53" s="7" t="inlineStr">
         <is>
-          <t>inherited from "commercial waste collection leeds": AS 13, 21, 21, 24, 25 at or below Better Waste (AS 20); 2 council/gov slots</t>
+          <t>inherited from "business cardboard recycling": AS 16, 18, 20 at or below Better Waste (AS 20)</t>
         </is>
       </c>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="O53" s="7" t="inlineStr">
-        <is>
-          <t>No page exists</t>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O53" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>Not in sheet. Currently p57</t>
         </is>
       </c>
     </row>
@@ -4422,29 +4694,29 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/areas-we-cover/nottingham/</t>
+          <t>https://betterwaste.co.uk/areas-we-cover/glasgow/</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>OPTIMISE</t>
+          <t>CREATE</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>commercial waste collection nottingham</t>
+          <t>commercial waste collection glasgow</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="H54" s="6" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J54" s="6" t="inlineStr"/>
       <c r="K54" s="7" t="inlineStr"/>
@@ -4460,12 +4732,17 @@
       </c>
       <c r="N54" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O54" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O54" s="7" t="inlineStr">
-        <is>
-          <t>No page exists</t>
+      <c r="P54" s="7" t="inlineStr">
+        <is>
+          <t>No page exists. High commercial value</t>
         </is>
       </c>
     </row>
@@ -4487,17 +4764,17 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/areas-we-cover/glasgow/</t>
+          <t>https://betterwaste.co.uk/areas-we-cover/leicester/</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>CREATE</t>
+          <t>OPTIMISE</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>commercial waste collection glasgow</t>
+          <t>commercial waste collection leicester</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
@@ -4506,7 +4783,7 @@
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="I55" s="6" t="n">
         <v>0</v>
@@ -4525,14 +4802,15 @@
       </c>
       <c r="N55" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O55" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O55" s="7" t="inlineStr">
-        <is>
-          <t>No page exists. High commercial value</t>
-        </is>
-      </c>
+      <c r="P55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -4542,17 +4820,17 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>F - Locations</t>
+          <t>E - Existing push</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/areas-we-cover/leicester/</t>
+          <t>https://betterwaste.co.uk/cafe-waste-management/</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -4562,22 +4840,28 @@
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>commercial waste collection leicester</t>
+          <t>cafe waste collection</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H56" s="6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I56" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="6" t="inlineStr"/>
-      <c r="K56" s="7" t="inlineStr"/>
+      <c r="J56" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K56" s="7" t="inlineStr">
+        <is>
+          <t>https://betterwaste.co.uk/cafe-waste-management/</t>
+        </is>
+      </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
           <t>EASY</t>
@@ -4585,15 +4869,24 @@
       </c>
       <c r="M56" s="7" t="inlineStr">
         <is>
-          <t>inherited from "commercial waste collection leeds": AS 13, 21, 21, 24, 25 at or below Better Waste (AS 20); 2 council/gov slots</t>
+          <t>inherited from "butchers waste collection": AS 10, 10, 24 at or below Better Waste (AS 20); 1 council/gov slots</t>
         </is>
       </c>
       <c r="N56" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="O56" s="7" t="inlineStr"/>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O56" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="P56" s="7" t="inlineStr">
+        <is>
+          <t>Currently p19</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -4651,10 +4944,15 @@
       </c>
       <c r="N57" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O57" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O57" s="7" t="inlineStr">
+      <c r="P57" s="7" t="inlineStr">
         <is>
           <t>Page already exists. businesswaste.co.uk ranks p5</t>
         </is>
@@ -4716,10 +5014,15 @@
       </c>
       <c r="N58" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O58" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O58" s="7" t="inlineStr">
+      <c r="P58" s="7" t="inlineStr">
         <is>
           <t>No page exists</t>
         </is>
@@ -4781,10 +5084,15 @@
       </c>
       <c r="N59" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O59" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O59" s="7" t="inlineStr">
+      <c r="P59" s="7" t="inlineStr">
         <is>
           <t>Page already exists</t>
         </is>
@@ -4846,10 +5154,15 @@
       </c>
       <c r="N60" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O60" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O60" s="7" t="inlineStr">
+      <c r="P60" s="7" t="inlineStr">
         <is>
           <t>Page already exists</t>
         </is>
@@ -4911,10 +5224,15 @@
       </c>
       <c r="N61" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O61" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O61" s="7" t="inlineStr">
+      <c r="P61" s="7" t="inlineStr">
         <is>
           <t>Page already exists</t>
         </is>
@@ -4976,10 +5294,15 @@
       </c>
       <c r="N62" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O62" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O62" s="7" t="inlineStr">
+      <c r="P62" s="7" t="inlineStr">
         <is>
           <t>Page already exists</t>
         </is>
@@ -5041,10 +5364,15 @@
       </c>
       <c r="N63" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O63" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O63" s="7" t="inlineStr">
+      <c r="P63" s="7" t="inlineStr">
         <is>
           <t>Commercial entry point to the clinical cluster; page exists</t>
         </is>
@@ -5106,10 +5434,15 @@
       </c>
       <c r="N64" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O64" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O64" s="7" t="inlineStr">
+      <c r="P64" s="7" t="inlineStr">
         <is>
           <t>businesswaste p8, thefirstmile p5</t>
         </is>
@@ -5171,10 +5504,15 @@
       </c>
       <c r="N65" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O65" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O65" s="7" t="inlineStr">
+      <c r="P65" s="7" t="inlineStr">
         <is>
           <t>businesswaste p2 / wastemanaged p9</t>
         </is>
@@ -5242,12 +5580,17 @@
       </c>
       <c r="N66" s="6" t="inlineStr">
         <is>
+          <t>LOW - no Semrush keyword-overview data; volume is from the organic rankings report only</t>
+        </is>
+      </c>
+      <c r="O66" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O66" s="7" t="inlineStr">
-        <is>
-          <t>Currently p16 on the -old URL</t>
+      <c r="P66" s="7" t="inlineStr">
+        <is>
+          <t>Currently p16 on the -old URL | LOW CONFIDENCE volume - treat as indicative</t>
         </is>
       </c>
     </row>
@@ -5307,10 +5650,15 @@
       </c>
       <c r="N67" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O67" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O67" s="7" t="inlineStr"/>
+      <c r="P67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -5368,10 +5716,15 @@
       </c>
       <c r="N68" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O68" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O68" s="7" t="inlineStr"/>
+      <c r="P68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -5413,7 +5766,7 @@
         <v>590</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J69" s="6" t="n">
         <v>49</v>
@@ -5435,10 +5788,15 @@
       </c>
       <c r="N69" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O69" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O69" s="7" t="inlineStr">
+      <c r="P69" s="7" t="inlineStr">
         <is>
           <t>Currently p49 - already ranking</t>
         </is>
@@ -5506,12 +5864,17 @@
       </c>
       <c r="N70" s="6" t="inlineStr">
         <is>
+          <t>LOW - no Semrush keyword-overview data; volume is from the organic rankings report only</t>
+        </is>
+      </c>
+      <c r="O70" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O70" s="7" t="inlineStr">
-        <is>
-          <t>Currently p21</t>
+      <c r="P70" s="7" t="inlineStr">
+        <is>
+          <t>Currently p21 | LOW CONFIDENCE volume - treat as indicative</t>
         </is>
       </c>
     </row>
@@ -5577,12 +5940,17 @@
       </c>
       <c r="N71" s="6" t="inlineStr">
         <is>
+          <t>LOW - no Semrush keyword-overview data; volume is from the organic rankings report only</t>
+        </is>
+      </c>
+      <c r="O71" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O71" s="7" t="inlineStr">
-        <is>
-          <t>Currently p11 on the -old URL</t>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>Currently p11 on the -old URL | LOW CONFIDENCE volume - treat as indicative</t>
         </is>
       </c>
     </row>
@@ -5642,10 +6010,15 @@
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O72" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O72" s="7" t="inlineStr">
+      <c r="P72" s="7" t="inlineStr">
         <is>
           <t>wastemanaged.co.uk p10. Very low KD</t>
         </is>
@@ -5707,10 +6080,15 @@
       </c>
       <c r="N73" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O73" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O73" s="7" t="inlineStr">
+      <c r="P73" s="7" t="inlineStr">
         <is>
           <t>wastemanaged.co.uk p9</t>
         </is>
@@ -5778,12 +6156,17 @@
       </c>
       <c r="N74" s="6" t="inlineStr">
         <is>
+          <t>LOW - no Semrush keyword-overview data; volume is from the organic rankings report only</t>
+        </is>
+      </c>
+      <c r="O74" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O74" s="7" t="inlineStr">
-        <is>
-          <t>Currently p18 on the -old URL</t>
+      <c r="P74" s="7" t="inlineStr">
+        <is>
+          <t>Currently p18 on the -old URL | LOW CONFIDENCE volume - treat as indicative</t>
         </is>
       </c>
     </row>
@@ -5849,12 +6232,17 @@
       </c>
       <c r="N75" s="6" t="inlineStr">
         <is>
+          <t>LOW - no Semrush keyword-overview data; volume is from the organic rankings report only</t>
+        </is>
+      </c>
+      <c r="O75" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O75" s="7" t="inlineStr">
-        <is>
-          <t>Currently p28</t>
+      <c r="P75" s="7" t="inlineStr">
+        <is>
+          <t>Currently p28 | LOW CONFIDENCE volume - treat as indicative</t>
         </is>
       </c>
     </row>
@@ -5898,7 +6286,7 @@
         <v>480</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J76" s="6" t="n">
         <v>30</v>
@@ -5920,10 +6308,15 @@
       </c>
       <c r="N76" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O76" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O76" s="7" t="inlineStr">
+      <c r="P76" s="7" t="inlineStr">
         <is>
           <t>Not in sheet. Currently p30 - closest to top 10 of all waste-type terms</t>
         </is>
@@ -5985,10 +6378,15 @@
       </c>
       <c r="N77" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O77" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O77" s="7" t="inlineStr"/>
+      <c r="P77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -6008,36 +6406,36 @@
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/areas-we-cover/london/</t>
+          <t>https://betterwaste.co.uk/areas-we-cover/manchester/</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>OPTIMISE</t>
+          <t>FIX</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>commercial recycling london</t>
+          <t>commercial rubbish collection near fallowfield manchester</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H78" s="6" t="n">
         <v>390</v>
       </c>
       <c r="I78" s="6" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/areas-we-cover/london/</t>
+          <t>https://betterwaste.co.uk/areas-we-cover-old/manchester/</t>
         </is>
       </c>
       <c r="L78" s="9" t="inlineStr">
@@ -6047,17 +6445,22 @@
       </c>
       <c r="M78" s="7" t="inlineStr">
         <is>
-          <t>AS 18 (greenlineenvironmental) and 25 (envirowastemanagement) at or below Better Waste (AS 20) on the shared London commercial-waste SERP; 3 council/gov slots</t>
+          <t>BORDERLINE: no site at AS&lt;=25 on the shared Manchester commercial-waste SERP, but lowest is AS 27 (kennywastemanagement) vs Better Waste AS 20; only 2 council/gov slots</t>
         </is>
       </c>
       <c r="N78" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="O78" s="7" t="inlineStr">
-        <is>
-          <t>Currently p28</t>
+          <t>LOW - no Semrush keyword-overview data; volume is from the organic rankings report only</t>
+        </is>
+      </c>
+      <c r="O78" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="P78" s="7" t="inlineStr">
+        <is>
+          <t>Currently p13 on the -old URL | LOW CONFIDENCE volume - treat as indicative</t>
         </is>
       </c>
     </row>
@@ -6079,36 +6482,36 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/areas-we-cover/manchester/</t>
+          <t>https://betterwaste.co.uk/areas-we-cover/birmingham/</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>OPTIMISE</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>commercial rubbish collection near fallowfield manchester</t>
+          <t>commercial dump collection service birmingham</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
         <v>390</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/areas-we-cover-old/manchester/</t>
+          <t>https://betterwaste.co.uk/areas-we-cover/birmingham/</t>
         </is>
       </c>
       <c r="L79" s="9" t="inlineStr">
@@ -6123,12 +6526,17 @@
       </c>
       <c r="N79" s="6" t="inlineStr">
         <is>
+          <t>LOW - no Semrush keyword-overview data; volume is from the organic rankings report only</t>
+        </is>
+      </c>
+      <c r="O79" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O79" s="7" t="inlineStr">
-        <is>
-          <t>Currently p13 on the -old URL</t>
+      <c r="P79" s="7" t="inlineStr">
+        <is>
+          <t>Currently p27 | LOW CONFIDENCE volume - treat as indicative</t>
         </is>
       </c>
     </row>
@@ -6140,17 +6548,17 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>F - Long tail</t>
+          <t>A - Core commercial</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/areas-we-cover/birmingham/</t>
+          <t>https://betterwaste.co.uk/commercial-waste-collection/</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -6160,7 +6568,7 @@
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>commercial dump collection service birmingham</t>
+          <t>commercial rubbish removal</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
@@ -6169,17 +6577,17 @@
         </is>
       </c>
       <c r="H80" s="6" t="n">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="I80" s="6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="K80" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/areas-we-cover/birmingham/</t>
+          <t>https://betterwaste.co.uk/areas-we-cover/</t>
         </is>
       </c>
       <c r="L80" s="9" t="inlineStr">
@@ -6189,17 +6597,22 @@
       </c>
       <c r="M80" s="7" t="inlineStr">
         <is>
-          <t>BORDERLINE: no site at AS&lt;=25 on the shared Manchester commercial-waste SERP, but lowest is AS 27 (kennywastemanagement) vs Better Waste AS 20; only 2 council/gov slots</t>
+          <t>AS 10 at or below Better Waste (AS 20)</t>
         </is>
       </c>
       <c r="N80" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="O80" s="7" t="inlineStr">
-        <is>
-          <t>Currently p27</t>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O80" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="P80" s="7" t="inlineStr">
+        <is>
+          <t>Low KD, high commercial value</t>
         </is>
       </c>
     </row>
@@ -6211,17 +6624,17 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>A - Core commercial</t>
+          <t>E - New sectors</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/commercial-waste-collection/</t>
+          <t>https://betterwaste.co.uk/hotel-waste-disposal/</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -6231,28 +6644,22 @@
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>commercial rubbish removal</t>
+          <t>hotel waste management</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
         <v>320</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="J81" s="6" t="n">
-        <v>69</v>
-      </c>
-      <c r="K81" s="7" t="inlineStr">
-        <is>
-          <t>https://betterwaste.co.uk/areas-we-cover/</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J81" s="6" t="inlineStr"/>
+      <c r="K81" s="7" t="inlineStr"/>
       <c r="L81" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -6260,19 +6667,20 @@
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
-          <t>AS 10 at or below Better Waste (AS 20)</t>
+          <t>inherited from "care home waste management": AS 10, 22 at or below Better Waste (AS 20)</t>
         </is>
       </c>
       <c r="N81" s="6" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="O81" s="7" t="inlineStr">
-        <is>
-          <t>Low KD, high commercial value</t>
-        </is>
-      </c>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O81" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="P81" s="7" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -6282,17 +6690,17 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>E - New sectors</t>
+          <t>F - Long tail</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/hotel-waste-disposal/</t>
+          <t>https://betterwaste.co.uk/areas-we-cover/london/</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -6302,22 +6710,28 @@
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>hotel waste management</t>
+          <t>commercial recycling london</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H82" s="6" t="n">
         <v>320</v>
       </c>
       <c r="I82" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="J82" s="6" t="inlineStr"/>
-      <c r="K82" s="7" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="J82" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="K82" s="7" t="inlineStr">
+        <is>
+          <t>https://betterwaste.co.uk/areas-we-cover/london/</t>
+        </is>
+      </c>
       <c r="L82" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -6325,15 +6739,24 @@
       </c>
       <c r="M82" s="7" t="inlineStr">
         <is>
-          <t>inherited from "care home waste management": AS 10, 22 at or below Better Waste (AS 20)</t>
+          <t>AS 18 (greenlineenvironmental) and 25 (envirowastemanagement) at or below Better Waste (AS 20) on the shared London commercial-waste SERP; 3 council/gov slots</t>
         </is>
       </c>
       <c r="N82" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O82" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O82" s="7" t="inlineStr"/>
+      <c r="P82" s="7" t="inlineStr">
+        <is>
+          <t>Currently p28</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -6391,10 +6814,15 @@
       </c>
       <c r="N83" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O83" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O83" s="7" t="inlineStr"/>
+      <c r="P83" s="7" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -6452,10 +6880,15 @@
       </c>
       <c r="N84" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O84" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O84" s="7" t="inlineStr"/>
+      <c r="P84" s="7" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -6513,10 +6946,15 @@
       </c>
       <c r="N85" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O85" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O85" s="7" t="inlineStr">
+      <c r="P85" s="7" t="inlineStr">
         <is>
           <t>Local intent</t>
         </is>
@@ -6562,7 +7000,7 @@
         <v>260</v>
       </c>
       <c r="I86" s="6" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="J86" s="6" t="n">
         <v>55</v>
@@ -6584,10 +7022,15 @@
       </c>
       <c r="N86" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O86" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O86" s="7" t="inlineStr">
+      <c r="P86" s="7" t="inlineStr">
         <is>
           <t>Not in sheet. Currently p55</t>
         </is>
@@ -6649,10 +7092,15 @@
       </c>
       <c r="N87" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O87" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O87" s="7" t="inlineStr">
+      <c r="P87" s="7" t="inlineStr">
         <is>
           <t>Lowest KD on the site</t>
         </is>
@@ -6714,10 +7162,15 @@
       </c>
       <c r="N88" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O88" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O88" s="7" t="inlineStr"/>
+      <c r="P88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
@@ -6775,10 +7228,15 @@
       </c>
       <c r="N89" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O89" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O89" s="7" t="inlineStr">
+      <c r="P89" s="7" t="inlineStr">
         <is>
           <t>Local intent</t>
         </is>
@@ -6824,7 +7282,7 @@
         <v>140</v>
       </c>
       <c r="I90" s="6" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J90" s="6" t="n">
         <v>37</v>
@@ -6846,10 +7304,15 @@
       </c>
       <c r="N90" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O90" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O90" s="7" t="inlineStr">
+      <c r="P90" s="7" t="inlineStr">
         <is>
           <t>Not in sheet. Currently p37</t>
         </is>
@@ -6911,10 +7374,15 @@
       </c>
       <c r="N91" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O91" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O91" s="7" t="inlineStr">
+      <c r="P91" s="7" t="inlineStr">
         <is>
           <t>Highest commercial value of the city terms</t>
         </is>
@@ -6982,10 +7450,15 @@
       </c>
       <c r="N92" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O92" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O92" s="7" t="inlineStr">
+      <c r="P92" s="7" t="inlineStr">
         <is>
           <t>Currently p52</t>
         </is>
@@ -7047,10 +7520,15 @@
       </c>
       <c r="N93" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O93" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O93" s="7" t="inlineStr">
+      <c r="P93" s="7" t="inlineStr">
         <is>
           <t>thefirstmile.co.uk ranks p3</t>
         </is>
@@ -7112,10 +7590,15 @@
       </c>
       <c r="N94" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O94" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O94" s="7" t="inlineStr">
+      <c r="P94" s="7" t="inlineStr">
         <is>
           <t>thefirstmile.co.uk ranks p3</t>
         </is>
@@ -7177,10 +7660,15 @@
       </c>
       <c r="N95" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O95" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O95" s="7" t="inlineStr">
+      <c r="P95" s="7" t="inlineStr">
         <is>
           <t>Link-bait. businesswaste.co.uk p7</t>
         </is>
@@ -7242,10 +7730,15 @@
       </c>
       <c r="N96" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O96" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O96" s="7" t="inlineStr">
+      <c r="P96" s="7" t="inlineStr">
         <is>
           <t>Primary target. businesswaste.co.uk ranks p5</t>
         </is>
@@ -7307,10 +7800,15 @@
       </c>
       <c r="N97" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O97" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O97" s="7" t="inlineStr">
+      <c r="P97" s="7" t="inlineStr">
         <is>
           <t>businesswaste.co.uk ranks p5</t>
         </is>
@@ -7372,10 +7870,15 @@
       </c>
       <c r="N98" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O98" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O98" s="7" t="inlineStr">
+      <c r="P98" s="7" t="inlineStr">
         <is>
           <t>Highest KD in cluster</t>
         </is>
@@ -7437,10 +7940,15 @@
       </c>
       <c r="N99" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O99" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O99" s="7" t="inlineStr">
+      <c r="P99" s="7" t="inlineStr">
         <is>
           <t>businesswaste.co.uk ranks p2</t>
         </is>
@@ -7502,10 +8010,15 @@
       </c>
       <c r="N100" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O100" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O100" s="7" t="inlineStr">
+      <c r="P100" s="7" t="inlineStr">
         <is>
           <t>Consolidate existing /commercial-waste-management/ here</t>
         </is>
@@ -7567,10 +8080,15 @@
       </c>
       <c r="N101" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O101" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O101" s="7" t="inlineStr">
+      <c r="P101" s="7" t="inlineStr">
         <is>
           <t>thefirstmile.co.uk ranks p9</t>
         </is>
@@ -7632,10 +8150,15 @@
       </c>
       <c r="N102" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O102" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O102" s="7" t="inlineStr">
+      <c r="P102" s="7" t="inlineStr">
         <is>
           <t>Checked and rejected as a primary target - see Evidence</t>
         </is>
@@ -7697,10 +8220,15 @@
       </c>
       <c r="N103" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O103" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O103" s="7" t="inlineStr">
+      <c r="P103" s="7" t="inlineStr">
         <is>
           <t>businesswaste.co.uk ranks p5</t>
         </is>
@@ -7762,10 +8290,15 @@
       </c>
       <c r="N104" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O104" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O104" s="7" t="inlineStr">
+      <c r="P104" s="7" t="inlineStr">
         <is>
           <t>Low KD high relevance link target</t>
         </is>
@@ -7833,10 +8366,15 @@
       </c>
       <c r="N105" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O105" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O105" s="7" t="inlineStr">
+      <c r="P105" s="7" t="inlineStr">
         <is>
           <t>businesswaste.co.uk ranks p6</t>
         </is>
@@ -7898,10 +8436,15 @@
       </c>
       <c r="N106" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O106" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O106" s="7" t="inlineStr">
+      <c r="P106" s="7" t="inlineStr">
         <is>
           <t>thefirstmile.co.uk ranks p8</t>
         </is>
@@ -7963,10 +8506,15 @@
       </c>
       <c r="N107" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O107" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O107" s="7" t="inlineStr">
+      <c r="P107" s="7" t="inlineStr">
         <is>
           <t>businesswaste.co.uk ranks p3</t>
         </is>
@@ -8034,10 +8582,15 @@
       </c>
       <c r="N108" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O108" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O108" s="7" t="inlineStr">
+      <c r="P108" s="7" t="inlineStr">
         <is>
           <t>businesswaste.co.uk ranks p2</t>
         </is>
@@ -8099,10 +8652,15 @@
       </c>
       <c r="N109" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O109" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O109" s="7" t="inlineStr"/>
+      <c r="P109" s="7" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
@@ -8166,10 +8724,15 @@
       </c>
       <c r="N110" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O110" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O110" s="7" t="inlineStr">
+      <c r="P110" s="7" t="inlineStr">
         <is>
           <t>CURRENTLY P14 - cheapest win on the site</t>
         </is>
@@ -8231,10 +8794,15 @@
       </c>
       <c r="N111" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O111" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O111" s="7" t="inlineStr">
+      <c r="P111" s="7" t="inlineStr">
         <is>
           <t>thefirstmile.co.uk ranks p3</t>
         </is>
@@ -8296,10 +8864,15 @@
       </c>
       <c r="N112" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O112" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O112" s="7" t="inlineStr">
+      <c r="P112" s="7" t="inlineStr">
         <is>
           <t>Same SERP family as weee waste</t>
         </is>
@@ -8361,10 +8934,15 @@
       </c>
       <c r="N113" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O113" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O113" s="7" t="inlineStr">
+      <c r="P113" s="7" t="inlineStr">
         <is>
           <t>Highest KD in cluster</t>
         </is>
@@ -8426,10 +9004,15 @@
       </c>
       <c r="N114" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O114" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O114" s="7" t="inlineStr"/>
+      <c r="P114" s="7" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
@@ -8487,10 +9070,15 @@
       </c>
       <c r="N115" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O115" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O115" s="7" t="inlineStr">
+      <c r="P115" s="7" t="inlineStr">
         <is>
           <t>businesswaste.co.uk ranks p4</t>
         </is>
@@ -8552,10 +9140,15 @@
       </c>
       <c r="N116" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O116" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O116" s="7" t="inlineStr">
+      <c r="P116" s="7" t="inlineStr">
         <is>
           <t>Highest commercial value in cluster</t>
         </is>
@@ -8617,10 +9210,15 @@
       </c>
       <c r="N117" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O117" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O117" s="7" t="inlineStr">
+      <c r="P117" s="7" t="inlineStr">
         <is>
           <t>Lowest KD in cluster</t>
         </is>
@@ -8682,10 +9280,15 @@
       </c>
       <c r="N118" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O118" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O118" s="7" t="inlineStr"/>
+      <c r="P118" s="7" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
@@ -8743,10 +9346,15 @@
       </c>
       <c r="N119" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O119" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O119" s="7" t="inlineStr"/>
+      <c r="P119" s="7" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
@@ -8810,10 +9418,15 @@
       </c>
       <c r="N120" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O120" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O120" s="7" t="inlineStr"/>
+      <c r="P120" s="7" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
@@ -8877,10 +9490,15 @@
       </c>
       <c r="N121" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O121" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O121" s="7" t="inlineStr">
+      <c r="P121" s="7" t="inlineStr">
         <is>
           <t>Currently /areas-we-cover/ p54 - wrong page</t>
         </is>
@@ -8942,10 +9560,15 @@
       </c>
       <c r="N122" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O122" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O122" s="7" t="inlineStr">
+      <c r="P122" s="7" t="inlineStr">
         <is>
           <t>Pairs with existing cafe page</t>
         </is>
@@ -9007,10 +9630,15 @@
       </c>
       <c r="N123" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O123" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O123" s="7" t="inlineStr"/>
+      <c r="P123" s="7" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
@@ -9068,10 +9696,15 @@
       </c>
       <c r="N124" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O124" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O124" s="7" t="inlineStr"/>
+      <c r="P124" s="7" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
@@ -9129,10 +9762,15 @@
       </c>
       <c r="N125" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O125" s="6" t="inlineStr">
+        <is>
           <t>EXCLUDE</t>
         </is>
       </c>
-      <c r="O125" s="7" t="inlineStr">
+      <c r="P125" s="7" t="inlineStr">
         <is>
           <t>SERP is council pages / residential intent - do not target</t>
         </is>
@@ -9194,10 +9832,15 @@
       </c>
       <c r="N126" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O126" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O126" s="7" t="inlineStr">
+      <c r="P126" s="7" t="inlineStr">
         <is>
           <t>businesswaste.co.uk ranks p6</t>
         </is>
@@ -9259,10 +9902,15 @@
       </c>
       <c r="N127" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O127" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O127" s="7" t="inlineStr"/>
+      <c r="P127" s="7" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
@@ -9320,10 +9968,15 @@
       </c>
       <c r="N128" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O128" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O128" s="7" t="inlineStr">
+      <c r="P128" s="7" t="inlineStr">
         <is>
           <t>No page exists. Pairs with clinical waste disposal</t>
         </is>
@@ -9385,10 +10038,15 @@
       </c>
       <c r="N129" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O129" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O129" s="7" t="inlineStr"/>
+      <c r="P129" s="7" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
@@ -9398,48 +10056,42 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
+          <t>Waste Type</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>B - Missing streams</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>https://betterwaste.co.uk/clinical-waste-disposal-clinical-waste-collection-companies/</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>OPTIMISE</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>clinical waste</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
           <t>Informational</t>
         </is>
       </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>C - Bin specs</t>
-        </is>
-      </c>
-      <c r="D130" s="7" t="inlineStr">
-        <is>
-          <t>https://betterwaste.co.uk/binpedia/</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>OPTIMISE</t>
-        </is>
-      </c>
-      <c r="F130" s="6" t="inlineStr">
-        <is>
-          <t>waste container</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="inlineStr">
-        <is>
-          <t>Informational</t>
-        </is>
-      </c>
       <c r="H130" s="6" t="n">
-        <v>1900</v>
+        <v>1600</v>
       </c>
       <c r="I130" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="J130" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="K130" s="7" t="inlineStr">
-        <is>
-          <t>https://betterwaste.co.uk/binpedia/</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="J130" s="6" t="inlineStr"/>
+      <c r="K130" s="7" t="inlineStr"/>
       <c r="L130" s="11" t="inlineStr">
         <is>
           <t>AVOID</t>
@@ -9447,19 +10099,20 @@
       </c>
       <c r="M130" s="7" t="inlineStr">
         <is>
-          <t>inherited from "1100 litre bin": 0 council/gov slots; intent is household not commercial</t>
+          <t>inherited from "clinical waste collection": 6 council/gov slots; intent is household not commercial</t>
         </is>
       </c>
       <c r="N130" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O130" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O130" s="7" t="inlineStr">
-        <is>
-          <t>Currently p39 - already ranking | Do NOT target on this page - retail SERP. The abbreviated form on the same page is the winnable one.</t>
-        </is>
-      </c>
+      <c r="P130" s="7" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
@@ -9469,17 +10122,17 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>Waste Type</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>B - Missing streams</t>
+          <t>C - Bin specs</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>https://betterwaste.co.uk/clinical-waste-disposal-clinical-waste-collection-companies/</t>
+          <t>https://betterwaste.co.uk/binpedia/</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -9489,7 +10142,7 @@
       </c>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>clinical waste</t>
+          <t>waste container</t>
         </is>
       </c>
       <c r="G131" s="6" t="inlineStr">
@@ -9501,10 +10154,16 @@
         <v>1600</v>
       </c>
       <c r="I131" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J131" s="6" t="inlineStr"/>
-      <c r="K131" s="7" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="J131" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="K131" s="7" t="inlineStr">
+        <is>
+          <t>https://betterwaste.co.uk/binpedia/</t>
+        </is>
+      </c>
       <c r="L131" s="11" t="inlineStr">
         <is>
           <t>AVOID</t>
@@ -9512,15 +10171,24 @@
       </c>
       <c r="M131" s="7" t="inlineStr">
         <is>
-          <t>inherited from "clinical waste collection": 6 council/gov slots; intent is household not commercial</t>
+          <t>inherited from "1100 litre bin": 0 council/gov slots; intent is household not commercial</t>
         </is>
       </c>
       <c r="N131" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O131" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O131" s="7" t="inlineStr"/>
+      <c r="P131" s="7" t="inlineStr">
+        <is>
+          <t>Currently p39 - already ranking | Do NOT target on this page - retail SERP. The abbreviated form on the same page is the winnable one.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
@@ -9578,10 +10246,15 @@
       </c>
       <c r="N132" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O132" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O132" s="7" t="inlineStr"/>
+      <c r="P132" s="7" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
@@ -9639,10 +10312,15 @@
       </c>
       <c r="N133" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O133" s="6" t="inlineStr">
+        <is>
           <t>EXCLUDE</t>
         </is>
       </c>
-      <c r="O133" s="7" t="inlineStr">
+      <c r="P133" s="7" t="inlineStr">
         <is>
           <t>Residential/council intent. Use commercial garden waste instead</t>
         </is>
@@ -9704,10 +10382,15 @@
       </c>
       <c r="N134" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O134" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O134" s="7" t="inlineStr">
+      <c r="P134" s="7" t="inlineStr">
         <is>
           <t>Checked - council-dominated, household intent</t>
         </is>
@@ -9769,10 +10452,15 @@
       </c>
       <c r="N135" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O135" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O135" s="7" t="inlineStr">
+      <c r="P135" s="7" t="inlineStr">
         <is>
           <t>/binpedia/ already p39 for waste container | Do NOT target on this page - retail SERP. The abbreviated form on the same page is the winnable one.</t>
         </is>
@@ -9834,10 +10522,15 @@
       </c>
       <c r="N136" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O136" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O136" s="7" t="inlineStr">
+      <c r="P136" s="7" t="inlineStr">
         <is>
           <t>Do NOT target on this page - retail SERP. The abbreviated form on the same page is the winnable one.</t>
         </is>
@@ -9899,10 +10592,15 @@
       </c>
       <c r="N137" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O137" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O137" s="7" t="inlineStr"/>
+      <c r="P137" s="7" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
@@ -9960,10 +10658,15 @@
       </c>
       <c r="N138" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O138" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O138" s="7" t="inlineStr">
+      <c r="P138" s="7" t="inlineStr">
         <is>
           <t>Do NOT target on this page - retail SERP. The abbreviated form on the same page is the winnable one.</t>
         </is>
@@ -10025,10 +10728,15 @@
       </c>
       <c r="N139" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O139" s="6" t="inlineStr">
+        <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="O139" s="7" t="inlineStr">
+      <c r="P139" s="7" t="inlineStr">
         <is>
           <t>Same household cluster</t>
         </is>
@@ -10090,10 +10798,15 @@
       </c>
       <c r="N140" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O140" s="6" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="O140" s="7" t="inlineStr">
+      <c r="P140" s="7" t="inlineStr">
         <is>
           <t>Do NOT target on this page - retail SERP. The abbreviated form on the same page is the winnable one.</t>
         </is>
@@ -10155,10 +10868,15 @@
       </c>
       <c r="N141" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O141" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O141" s="7" t="inlineStr">
+      <c r="P141" s="7" t="inlineStr">
         <is>
           <t>Do NOT target on this page - retail SERP. The abbreviated form on the same page is the winnable one.</t>
         </is>
@@ -10220,10 +10938,15 @@
       </c>
       <c r="N142" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O142" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O142" s="7" t="inlineStr"/>
+      <c r="P142" s="7" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
@@ -10281,17 +11004,22 @@
       </c>
       <c r="N143" s="6" t="inlineStr">
         <is>
+          <t>Confirmed - Semrush keyword overview</t>
+        </is>
+      </c>
+      <c r="O143" s="6" t="inlineStr">
+        <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="O143" s="7" t="inlineStr">
+      <c r="P143" s="7" t="inlineStr">
         <is>
           <t>Do NOT target on this page - retail SERP. The abbreviated form on the same page is the winnable one.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O143"/>
+  <autoFilter ref="A1:P143"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/betterwaste-kw-audit/Better_Waste_Keyword_Plan.xlsx
+++ b/betterwaste-kw-audit/Better_Waste_Keyword_Plan.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Fixes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Keyword Plan'!$A$1:$H$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Keyword Plan'!$A$1:$I$178</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -122,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -139,6 +139,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -147,11 +150,14 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -521,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H178"/>
+  <dimension ref="A1:I178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -532,6 +538,7 @@
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="86" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -575,6 +582,11 @@
           <t>Current Position</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence (Authority Score)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -609,6 +621,11 @@
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>4 competitors rank at AS 25 or below: 11, 12, 12, 24. Confirm Better Waste offers skips</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr"/>
@@ -631,6 +648,11 @@
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "skip sizes uk". 4 competitors rank at AS 25 or below: 11, 12, 12, 24. Confirm Better Waste offers skips</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr"/>
@@ -653,6 +675,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "skip sizes uk". 4 competitors rank at AS 25 or below: 11, 12, 12, 24. Confirm Better Waste offers skips</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr"/>
@@ -675,6 +702,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "skip sizes uk". 4 competitors rank at AS 25 or below: 11, 12, 12, 24. Confirm Better Waste offers skips</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr"/>
@@ -697,16 +729,22 @@
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "skip sizes uk". 4 competitors rank at AS 25 or below: 11, 12, 12, 24. Confirm Better Waste offers skips</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -735,12 +773,17 @@
       <c r="F8" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial rubbish removal". 1 competitor ranks at AS 10. The only reachable term in the commercial head group</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr"/>
@@ -757,12 +800,17 @@
       <c r="F9" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial rubbish removal". 1 competitor ranks at AS 10. The only reachable term in the commercial head group</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr"/>
@@ -779,12 +827,17 @@
       <c r="F10" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>1 competitor ranks at AS 10. The only reachable term in the commercial head group</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr"/>
@@ -801,12 +854,17 @@
       <c r="F11" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>No competitor at AS 25 or below. Lowest is AS 31. 6 council results</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr"/>
@@ -823,12 +881,17 @@
       <c r="F12" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>No competitor at AS 25 or below. Lowest is AS 29. 5 council results</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr"/>
@@ -845,12 +908,17 @@
       <c r="F13" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>No competitor at AS 25 or below. Lowest is AS 41. 4 council results</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr"/>
@@ -867,12 +935,17 @@
       <c r="F14" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial waste collection". No competitor at AS 25 or below. Lowest is AS 31. 6 council results</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr"/>
@@ -889,12 +962,17 @@
       <c r="F15" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial waste disposal". No competitor at AS 25 or below. Lowest is AS 29. 5 council results</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr"/>
@@ -911,12 +989,17 @@
       <c r="F16" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "trade waste collection". No competitor at AS 25 or below. Lowest is AS 46. 6 council results</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr"/>
@@ -933,12 +1016,17 @@
       <c r="F17" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial waste management". No competitor at AS 25 or below. Lowest is AS 41. 4 council results</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr"/>
@@ -955,12 +1043,17 @@
       <c r="F18" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>No competitor at AS 25 or below. Lowest is AS 39. 4 council results</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr"/>
@@ -977,12 +1070,17 @@
       <c r="F19" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>No competitor at AS 25 or below. Lowest is AS 46. 6 council results</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr"/>
@@ -999,22 +1097,28 @@
       <c r="F20" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial waste management". No competitor at AS 25 or below. Lowest is AS 41. 4 council results</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1043,12 +1147,17 @@
       <c r="F22" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial bin sizes". 1 competitor ranks at AS 22. Two more sit just above at AS 26 and 29. 3 council results</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr"/>
@@ -1065,12 +1174,17 @@
       <c r="F23" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial waste collection". No competitor at AS 25 or below. Lowest is AS 31. 6 council results</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr"/>
@@ -1087,12 +1201,17 @@
       <c r="F24" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial waste collection". No competitor at AS 25 or below. Lowest is AS 31. 6 council results</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr"/>
@@ -1109,22 +1228,28 @@
       <c r="F25" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial waste collection". No competitor at AS 25 or below. Lowest is AS 31. 6 council results</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+      <c r="I26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1159,6 +1284,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Small shredding firms hold the results, including AS 16 and AS 10. No council results</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr"/>
@@ -1181,6 +1311,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>4 competitors rank at AS 25 or below: 6, 9, 10, 16. No council results</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr"/>
@@ -1203,6 +1338,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "confidential waste collection". 4 competitors rank at AS 25 or below: 6, 9, 10, 16. No council results</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr"/>
@@ -1225,6 +1365,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "document shredding". Small shredding firms hold the results, including AS 16 and AS 10. No council results</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr"/>
@@ -1247,6 +1392,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "document shredding". Small shredding firms hold the results, including AS 16 and AS 10. No council results</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr"/>
@@ -1269,6 +1419,11 @@
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "document shredding". Small shredding firms hold the results, including AS 16 and AS 10. No council results</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr"/>
@@ -1291,6 +1446,11 @@
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "document shredding". Small shredding firms hold the results, including AS 16 and AS 10. No council results</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr"/>
@@ -1307,22 +1467,28 @@
       <c r="F34" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>Mid size shredding firms hold the results. No council results</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="n"/>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
-      <c r="G35" s="6" t="n"/>
-      <c r="H35" s="6" t="n"/>
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1357,6 +1523,11 @@
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "business cardboard recycling". 3 competitors rank at AS 25 or below: 8, 9, 18</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr"/>
@@ -1379,6 +1550,11 @@
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "business cardboard recycling". 3 competitors rank at AS 25 or below: 8, 9, 18</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr"/>
@@ -1401,6 +1577,11 @@
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "business cardboard recycling". 3 competitors rank at AS 25 or below: 8, 9, 18</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr"/>
@@ -1423,6 +1604,11 @@
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>3 competitors rank at AS 25 or below: 8, 9, 18</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr"/>
@@ -1445,6 +1631,11 @@
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "business cardboard recycling". 3 competitors rank at AS 25 or below: 8, 9, 18</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr"/>
@@ -1467,6 +1658,11 @@
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "business cardboard recycling". 3 competitors rank at AS 25 or below: 8, 9, 18</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr"/>
@@ -1489,16 +1685,22 @@
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "business cardboard recycling". 3 competitors rank at AS 25 or below: 8, 9, 18</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="n"/>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="6" t="n"/>
-      <c r="G43" s="6" t="n"/>
-      <c r="H43" s="6" t="n"/>
+      <c r="A43" s="7" t="n"/>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="7" t="n"/>
+      <c r="G43" s="7" t="n"/>
+      <c r="H43" s="7" t="n"/>
+      <c r="I43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1533,6 +1735,11 @@
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "sanitary waste collection". 4 competitors rank at AS 25 or below: 9, 9, 13, 21. No council results</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr"/>
@@ -1555,16 +1762,22 @@
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>4 competitors rank at AS 25 or below: 9, 9, 13, 21. No council results</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="n"/>
-      <c r="B46" s="6" t="n"/>
-      <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="6" t="n"/>
-      <c r="G46" s="6" t="n"/>
-      <c r="H46" s="6" t="n"/>
+      <c r="A46" s="7" t="n"/>
+      <c r="B46" s="7" t="n"/>
+      <c r="C46" s="7" t="n"/>
+      <c r="D46" s="7" t="n"/>
+      <c r="E46" s="7" t="n"/>
+      <c r="F46" s="7" t="n"/>
+      <c r="G46" s="7" t="n"/>
+      <c r="H46" s="7" t="n"/>
+      <c r="I46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1599,6 +1812,11 @@
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "it equipment disposal". 6 competitors rank at AS 25 or below: 2, 8, 19, 19, 20, 20</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr"/>
@@ -1621,16 +1839,22 @@
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>6 competitors rank at AS 25 or below: 2, 8, 19, 19, 20, 20</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="n"/>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="6" t="n"/>
-      <c r="D49" s="6" t="n"/>
-      <c r="E49" s="6" t="n"/>
-      <c r="F49" s="6" t="n"/>
-      <c r="G49" s="6" t="n"/>
-      <c r="H49" s="6" t="n"/>
+      <c r="A49" s="7" t="n"/>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="7" t="n"/>
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="7" t="n"/>
+      <c r="G49" s="7" t="n"/>
+      <c r="H49" s="7" t="n"/>
+      <c r="I49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1665,6 +1889,11 @@
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "business cardboard recycling". 3 competitors rank at AS 25 or below: 8, 9, 18</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr"/>
@@ -1687,16 +1916,22 @@
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "business cardboard recycling". 3 competitors rank at AS 25 or below: 8, 9, 18</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="6" t="n"/>
-      <c r="B52" s="6" t="n"/>
-      <c r="C52" s="6" t="n"/>
-      <c r="D52" s="6" t="n"/>
-      <c r="E52" s="6" t="n"/>
-      <c r="F52" s="6" t="n"/>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="6" t="n"/>
+      <c r="A52" s="7" t="n"/>
+      <c r="B52" s="7" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="7" t="n"/>
+      <c r="E52" s="7" t="n"/>
+      <c r="F52" s="7" t="n"/>
+      <c r="G52" s="7" t="n"/>
+      <c r="H52" s="7" t="n"/>
+      <c r="I52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1731,16 +1966,22 @@
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>4 competitors rank at AS 25 or below: 9, 11, 18, 22</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="6" t="n"/>
-      <c r="B54" s="6" t="n"/>
-      <c r="C54" s="6" t="n"/>
-      <c r="D54" s="6" t="n"/>
-      <c r="E54" s="6" t="n"/>
-      <c r="F54" s="6" t="n"/>
-      <c r="G54" s="6" t="n"/>
-      <c r="H54" s="6" t="n"/>
+      <c r="A54" s="7" t="n"/>
+      <c r="B54" s="7" t="n"/>
+      <c r="C54" s="7" t="n"/>
+      <c r="D54" s="7" t="n"/>
+      <c r="E54" s="7" t="n"/>
+      <c r="F54" s="7" t="n"/>
+      <c r="G54" s="7" t="n"/>
+      <c r="H54" s="7" t="n"/>
+      <c r="I54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1775,16 +2016,22 @@
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>6 competitors rank at AS 25 or below: 2, 6, 7, 19, 19, 20</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="n"/>
-      <c r="B56" s="6" t="n"/>
-      <c r="C56" s="6" t="n"/>
-      <c r="D56" s="6" t="n"/>
-      <c r="E56" s="6" t="n"/>
-      <c r="F56" s="6" t="n"/>
-      <c r="G56" s="6" t="n"/>
-      <c r="H56" s="6" t="n"/>
+      <c r="A56" s="7" t="n"/>
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="7" t="n"/>
+      <c r="E56" s="7" t="n"/>
+      <c r="F56" s="7" t="n"/>
+      <c r="G56" s="7" t="n"/>
+      <c r="H56" s="7" t="n"/>
+      <c r="I56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1819,16 +2066,22 @@
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>5 competitors rank at AS 25 or below: 9, 11, 15, 17, 20. All are scrap merchants who buy scrap rather than sell collection</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="6" t="n"/>
-      <c r="B58" s="6" t="n"/>
-      <c r="C58" s="6" t="n"/>
-      <c r="D58" s="6" t="n"/>
-      <c r="E58" s="6" t="n"/>
-      <c r="F58" s="6" t="n"/>
-      <c r="G58" s="6" t="n"/>
-      <c r="H58" s="6" t="n"/>
+      <c r="A58" s="7" t="n"/>
+      <c r="B58" s="7" t="n"/>
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="7" t="n"/>
+      <c r="E58" s="7" t="n"/>
+      <c r="F58" s="7" t="n"/>
+      <c r="G58" s="7" t="n"/>
+      <c r="H58" s="7" t="n"/>
+      <c r="I58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1857,22 +2110,28 @@
       <c r="F59" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="G59" s="7" t="inlineStr">
+      <c r="G59" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "dental waste disposal". 1 competitor ranks at AS 10. The results are mostly guides and trade press</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="n"/>
-      <c r="B60" s="6" t="n"/>
-      <c r="C60" s="6" t="n"/>
-      <c r="D60" s="6" t="n"/>
-      <c r="E60" s="6" t="n"/>
-      <c r="F60" s="6" t="n"/>
-      <c r="G60" s="6" t="n"/>
-      <c r="H60" s="6" t="n"/>
+      <c r="A60" s="7" t="n"/>
+      <c r="B60" s="7" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
+      <c r="E60" s="7" t="n"/>
+      <c r="F60" s="7" t="n"/>
+      <c r="G60" s="7" t="n"/>
+      <c r="H60" s="7" t="n"/>
+      <c r="I60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -1901,12 +2160,17 @@
       <c r="F61" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="G61" s="7" t="inlineStr">
+      <c r="G61" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr"/>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>2 competitors rank at AS 25 or below: 14 and 18. 3 government results</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr"/>
@@ -1923,22 +2187,28 @@
       <c r="F62" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="G62" s="7" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "industrial waste disposal". 2 competitors rank at AS 25 or below: 14 and 18. 3 government results</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="n"/>
-      <c r="B63" s="6" t="n"/>
-      <c r="C63" s="6" t="n"/>
-      <c r="D63" s="6" t="n"/>
-      <c r="E63" s="6" t="n"/>
-      <c r="F63" s="6" t="n"/>
-      <c r="G63" s="6" t="n"/>
-      <c r="H63" s="6" t="n"/>
+      <c r="A63" s="7" t="n"/>
+      <c r="B63" s="7" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="7" t="n"/>
+      <c r="E63" s="7" t="n"/>
+      <c r="F63" s="7" t="n"/>
+      <c r="G63" s="7" t="n"/>
+      <c r="H63" s="7" t="n"/>
+      <c r="I63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1967,12 +2237,17 @@
       <c r="F64" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="G64" s="7" t="inlineStr">
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr"/>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>1 competitor ranks at AS 20. Powerday, Bywaters and Biffa hold the rest</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr"/>
@@ -1989,22 +2264,28 @@
       <c r="F65" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="G65" s="7" t="inlineStr">
+      <c r="G65" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr"/>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "construction waste disposal". 1 competitor ranks at AS 20. Powerday, Bywaters and Biffa hold the rest</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="6" t="n"/>
-      <c r="B66" s="6" t="n"/>
-      <c r="C66" s="6" t="n"/>
-      <c r="D66" s="6" t="n"/>
-      <c r="E66" s="6" t="n"/>
-      <c r="F66" s="6" t="n"/>
-      <c r="G66" s="6" t="n"/>
-      <c r="H66" s="6" t="n"/>
+      <c r="A66" s="7" t="n"/>
+      <c r="B66" s="7" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
+      <c r="E66" s="7" t="n"/>
+      <c r="F66" s="7" t="n"/>
+      <c r="G66" s="7" t="n"/>
+      <c r="H66" s="7" t="n"/>
+      <c r="I66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2033,22 +2314,28 @@
       <c r="F67" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G67" s="7" t="inlineStr">
+      <c r="G67" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr"/>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>1 competitor ranks at AS 24. 3 council results. The page already ranks p30</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="n"/>
-      <c r="B68" s="6" t="n"/>
-      <c r="C68" s="6" t="n"/>
-      <c r="D68" s="6" t="n"/>
-      <c r="E68" s="6" t="n"/>
-      <c r="F68" s="6" t="n"/>
-      <c r="G68" s="6" t="n"/>
-      <c r="H68" s="6" t="n"/>
+      <c r="A68" s="7" t="n"/>
+      <c r="B68" s="7" t="n"/>
+      <c r="C68" s="7" t="n"/>
+      <c r="D68" s="7" t="n"/>
+      <c r="E68" s="7" t="n"/>
+      <c r="F68" s="7" t="n"/>
+      <c r="G68" s="7" t="n"/>
+      <c r="H68" s="7" t="n"/>
+      <c r="I68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2077,12 +2364,17 @@
       <c r="F69" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="G69" s="7" t="inlineStr">
+      <c r="G69" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr"/>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial glass collection". 1 competitor ranks at AS 24. 3 council results. The page already ranks p30</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr"/>
@@ -2099,22 +2391,28 @@
       <c r="F70" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="G70" s="7" t="inlineStr">
+      <c r="G70" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr"/>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial glass collection". 1 competitor ranks at AS 24. 3 council results. The page already ranks p30</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="n"/>
-      <c r="B71" s="6" t="n"/>
-      <c r="C71" s="6" t="n"/>
-      <c r="D71" s="6" t="n"/>
-      <c r="E71" s="6" t="n"/>
-      <c r="F71" s="6" t="n"/>
-      <c r="G71" s="6" t="n"/>
-      <c r="H71" s="6" t="n"/>
+      <c r="A71" s="7" t="n"/>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="7" t="n"/>
+      <c r="E71" s="7" t="n"/>
+      <c r="F71" s="7" t="n"/>
+      <c r="G71" s="7" t="n"/>
+      <c r="H71" s="7" t="n"/>
+      <c r="I71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2143,12 +2441,17 @@
       <c r="F72" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="G72" s="8" t="inlineStr">
+      <c r="G72" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr"/>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>No competitor at AS 25 or below. Lowest is AS 34. Government and Wikipedia hold the results</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr"/>
@@ -2165,12 +2468,17 @@
       <c r="F73" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="G73" s="8" t="inlineStr">
+      <c r="G73" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr"/>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "waste transfer note". No competitor at AS 25 or below. Lowest is AS 45. 4 government results</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr"/>
@@ -2187,22 +2495,28 @@
       <c r="F74" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="G74" s="8" t="inlineStr">
+      <c r="G74" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr"/>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "weee waste". No competitor at AS 25 or below. Lowest is AS 34. Government and Wikipedia hold the results</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="n"/>
-      <c r="B75" s="6" t="n"/>
-      <c r="C75" s="6" t="n"/>
-      <c r="D75" s="6" t="n"/>
-      <c r="E75" s="6" t="n"/>
-      <c r="F75" s="6" t="n"/>
-      <c r="G75" s="6" t="n"/>
-      <c r="H75" s="6" t="n"/>
+      <c r="A75" s="7" t="n"/>
+      <c r="B75" s="7" t="n"/>
+      <c r="C75" s="7" t="n"/>
+      <c r="D75" s="7" t="n"/>
+      <c r="E75" s="7" t="n"/>
+      <c r="F75" s="7" t="n"/>
+      <c r="G75" s="7" t="n"/>
+      <c r="H75" s="7" t="n"/>
+      <c r="I75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2231,22 +2545,28 @@
       <c r="F76" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G76" s="8" t="inlineStr">
+      <c r="G76" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr"/>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>No competitor at AS 25 or below. Lowest is AS 45. All results are government or charity</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="n"/>
-      <c r="B77" s="6" t="n"/>
-      <c r="C77" s="6" t="n"/>
-      <c r="D77" s="6" t="n"/>
-      <c r="E77" s="6" t="n"/>
-      <c r="F77" s="6" t="n"/>
-      <c r="G77" s="6" t="n"/>
-      <c r="H77" s="6" t="n"/>
+      <c r="A77" s="7" t="n"/>
+      <c r="B77" s="7" t="n"/>
+      <c r="C77" s="7" t="n"/>
+      <c r="D77" s="7" t="n"/>
+      <c r="E77" s="7" t="n"/>
+      <c r="F77" s="7" t="n"/>
+      <c r="G77" s="7" t="n"/>
+      <c r="H77" s="7" t="n"/>
+      <c r="I77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2281,6 +2601,11 @@
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr"/>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "office waste management". 1 competitor ranks at AS 24. The page results are dated, half use http and one is a US agency</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr"/>
@@ -2303,6 +2628,11 @@
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr"/>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "office waste management". 1 competitor ranks at AS 24. The page results are dated, half use http and one is a US agency</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr"/>
@@ -2325,16 +2655,22 @@
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>1 competitor ranks at AS 24. The page results are dated, half use http and one is a US agency</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="n"/>
-      <c r="B81" s="6" t="n"/>
-      <c r="C81" s="6" t="n"/>
-      <c r="D81" s="6" t="n"/>
-      <c r="E81" s="6" t="n"/>
-      <c r="F81" s="6" t="n"/>
-      <c r="G81" s="6" t="n"/>
-      <c r="H81" s="6" t="n"/>
+      <c r="A81" s="7" t="n"/>
+      <c r="B81" s="7" t="n"/>
+      <c r="C81" s="7" t="n"/>
+      <c r="D81" s="7" t="n"/>
+      <c r="E81" s="7" t="n"/>
+      <c r="F81" s="7" t="n"/>
+      <c r="G81" s="7" t="n"/>
+      <c r="H81" s="7" t="n"/>
+      <c r="I81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2369,6 +2705,11 @@
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "butchers waste collection". 3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr"/>
@@ -2391,6 +2732,11 @@
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr"/>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "butchers waste collection". 3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr"/>
@@ -2413,16 +2759,22 @@
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "butchers waste collection". 3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="n"/>
-      <c r="B85" s="6" t="n"/>
-      <c r="C85" s="6" t="n"/>
-      <c r="D85" s="6" t="n"/>
-      <c r="E85" s="6" t="n"/>
-      <c r="F85" s="6" t="n"/>
-      <c r="G85" s="6" t="n"/>
-      <c r="H85" s="6" t="n"/>
+      <c r="A85" s="7" t="n"/>
+      <c r="B85" s="7" t="n"/>
+      <c r="C85" s="7" t="n"/>
+      <c r="D85" s="7" t="n"/>
+      <c r="E85" s="7" t="n"/>
+      <c r="F85" s="7" t="n"/>
+      <c r="G85" s="7" t="n"/>
+      <c r="H85" s="7" t="n"/>
+      <c r="I85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2457,16 +2809,22 @@
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "office waste management". 1 competitor ranks at AS 24. The page results are dated, half use http and one is a US agency</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="n"/>
-      <c r="B87" s="6" t="n"/>
-      <c r="C87" s="6" t="n"/>
-      <c r="D87" s="6" t="n"/>
-      <c r="E87" s="6" t="n"/>
-      <c r="F87" s="6" t="n"/>
-      <c r="G87" s="6" t="n"/>
-      <c r="H87" s="6" t="n"/>
+      <c r="A87" s="7" t="n"/>
+      <c r="B87" s="7" t="n"/>
+      <c r="C87" s="7" t="n"/>
+      <c r="D87" s="7" t="n"/>
+      <c r="E87" s="7" t="n"/>
+      <c r="F87" s="7" t="n"/>
+      <c r="G87" s="7" t="n"/>
+      <c r="H87" s="7" t="n"/>
+      <c r="I87" s="7" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2501,16 +2859,22 @@
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr"/>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="6" t="n"/>
-      <c r="B89" s="6" t="n"/>
-      <c r="C89" s="6" t="n"/>
-      <c r="D89" s="6" t="n"/>
-      <c r="E89" s="6" t="n"/>
-      <c r="F89" s="6" t="n"/>
-      <c r="G89" s="6" t="n"/>
-      <c r="H89" s="6" t="n"/>
+      <c r="A89" s="7" t="n"/>
+      <c r="B89" s="7" t="n"/>
+      <c r="C89" s="7" t="n"/>
+      <c r="D89" s="7" t="n"/>
+      <c r="E89" s="7" t="n"/>
+      <c r="F89" s="7" t="n"/>
+      <c r="G89" s="7" t="n"/>
+      <c r="H89" s="7" t="n"/>
+      <c r="I89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2545,6 +2909,11 @@
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "butchers waste collection". 3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr"/>
@@ -2567,16 +2936,22 @@
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr"/>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "butchers waste collection". 3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="n"/>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="6" t="n"/>
-      <c r="D92" s="6" t="n"/>
-      <c r="E92" s="6" t="n"/>
-      <c r="F92" s="6" t="n"/>
-      <c r="G92" s="6" t="n"/>
-      <c r="H92" s="6" t="n"/>
+      <c r="A92" s="7" t="n"/>
+      <c r="B92" s="7" t="n"/>
+      <c r="C92" s="7" t="n"/>
+      <c r="D92" s="7" t="n"/>
+      <c r="E92" s="7" t="n"/>
+      <c r="F92" s="7" t="n"/>
+      <c r="G92" s="7" t="n"/>
+      <c r="H92" s="7" t="n"/>
+      <c r="I92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2611,16 +2986,22 @@
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr"/>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "butchers waste collection". 3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="6" t="n"/>
-      <c r="B94" s="6" t="n"/>
-      <c r="C94" s="6" t="n"/>
-      <c r="D94" s="6" t="n"/>
-      <c r="E94" s="6" t="n"/>
-      <c r="F94" s="6" t="n"/>
-      <c r="G94" s="6" t="n"/>
-      <c r="H94" s="6" t="n"/>
+      <c r="A94" s="7" t="n"/>
+      <c r="B94" s="7" t="n"/>
+      <c r="C94" s="7" t="n"/>
+      <c r="D94" s="7" t="n"/>
+      <c r="E94" s="7" t="n"/>
+      <c r="F94" s="7" t="n"/>
+      <c r="G94" s="7" t="n"/>
+      <c r="H94" s="7" t="n"/>
+      <c r="I94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -2655,16 +3036,22 @@
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr"/>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "butchers waste collection". 3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="6" t="n"/>
-      <c r="B96" s="6" t="n"/>
-      <c r="C96" s="6" t="n"/>
-      <c r="D96" s="6" t="n"/>
-      <c r="E96" s="6" t="n"/>
-      <c r="F96" s="6" t="n"/>
-      <c r="G96" s="6" t="n"/>
-      <c r="H96" s="6" t="n"/>
+      <c r="A96" s="7" t="n"/>
+      <c r="B96" s="7" t="n"/>
+      <c r="C96" s="7" t="n"/>
+      <c r="D96" s="7" t="n"/>
+      <c r="E96" s="7" t="n"/>
+      <c r="F96" s="7" t="n"/>
+      <c r="G96" s="7" t="n"/>
+      <c r="H96" s="7" t="n"/>
+      <c r="I96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -2699,16 +3086,22 @@
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr"/>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "butchers waste collection". 3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="6" t="n"/>
-      <c r="B98" s="6" t="n"/>
-      <c r="C98" s="6" t="n"/>
-      <c r="D98" s="6" t="n"/>
-      <c r="E98" s="6" t="n"/>
-      <c r="F98" s="6" t="n"/>
-      <c r="G98" s="6" t="n"/>
-      <c r="H98" s="6" t="n"/>
+      <c r="A98" s="7" t="n"/>
+      <c r="B98" s="7" t="n"/>
+      <c r="C98" s="7" t="n"/>
+      <c r="D98" s="7" t="n"/>
+      <c r="E98" s="7" t="n"/>
+      <c r="F98" s="7" t="n"/>
+      <c r="G98" s="7" t="n"/>
+      <c r="H98" s="7" t="n"/>
+      <c r="I98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -2743,16 +3136,22 @@
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr"/>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "butchers waste collection". 3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="6" t="n"/>
-      <c r="B100" s="6" t="n"/>
-      <c r="C100" s="6" t="n"/>
-      <c r="D100" s="6" t="n"/>
-      <c r="E100" s="6" t="n"/>
-      <c r="F100" s="6" t="n"/>
-      <c r="G100" s="6" t="n"/>
-      <c r="H100" s="6" t="n"/>
+      <c r="A100" s="7" t="n"/>
+      <c r="B100" s="7" t="n"/>
+      <c r="C100" s="7" t="n"/>
+      <c r="D100" s="7" t="n"/>
+      <c r="E100" s="7" t="n"/>
+      <c r="F100" s="7" t="n"/>
+      <c r="G100" s="7" t="n"/>
+      <c r="H100" s="7" t="n"/>
+      <c r="I100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -2781,22 +3180,28 @@
       <c r="F101" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G101" s="7" t="inlineStr">
+      <c r="G101" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr"/>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>2 competitors rank at AS 25 or below: 10 and 22. Stericycle and PHS hold two places</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="6" t="n"/>
-      <c r="B102" s="6" t="n"/>
-      <c r="C102" s="6" t="n"/>
-      <c r="D102" s="6" t="n"/>
-      <c r="E102" s="6" t="n"/>
-      <c r="F102" s="6" t="n"/>
-      <c r="G102" s="6" t="n"/>
-      <c r="H102" s="6" t="n"/>
+      <c r="A102" s="7" t="n"/>
+      <c r="B102" s="7" t="n"/>
+      <c r="C102" s="7" t="n"/>
+      <c r="D102" s="7" t="n"/>
+      <c r="E102" s="7" t="n"/>
+      <c r="F102" s="7" t="n"/>
+      <c r="G102" s="7" t="n"/>
+      <c r="H102" s="7" t="n"/>
+      <c r="I102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -2825,22 +3230,28 @@
       <c r="F103" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G103" s="7" t="inlineStr">
+      <c r="G103" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr"/>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>1 competitor ranks at AS 10. The results are mostly guides and trade press</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="6" t="n"/>
-      <c r="B104" s="6" t="n"/>
-      <c r="C104" s="6" t="n"/>
-      <c r="D104" s="6" t="n"/>
-      <c r="E104" s="6" t="n"/>
-      <c r="F104" s="6" t="n"/>
-      <c r="G104" s="6" t="n"/>
-      <c r="H104" s="6" t="n"/>
+      <c r="A104" s="7" t="n"/>
+      <c r="B104" s="7" t="n"/>
+      <c r="C104" s="7" t="n"/>
+      <c r="D104" s="7" t="n"/>
+      <c r="E104" s="7" t="n"/>
+      <c r="F104" s="7" t="n"/>
+      <c r="G104" s="7" t="n"/>
+      <c r="H104" s="7" t="n"/>
+      <c r="I104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -2869,22 +3280,28 @@
       <c r="F105" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G105" s="7" t="inlineStr">
+      <c r="G105" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr"/>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "care home waste management". 2 competitors rank at AS 25 or below: 10 and 22. Stericycle and PHS hold two places</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="6" t="n"/>
-      <c r="B106" s="6" t="n"/>
-      <c r="C106" s="6" t="n"/>
-      <c r="D106" s="6" t="n"/>
-      <c r="E106" s="6" t="n"/>
-      <c r="F106" s="6" t="n"/>
-      <c r="G106" s="6" t="n"/>
-      <c r="H106" s="6" t="n"/>
+      <c r="A106" s="7" t="n"/>
+      <c r="B106" s="7" t="n"/>
+      <c r="C106" s="7" t="n"/>
+      <c r="D106" s="7" t="n"/>
+      <c r="E106" s="7" t="n"/>
+      <c r="F106" s="7" t="n"/>
+      <c r="G106" s="7" t="n"/>
+      <c r="H106" s="7" t="n"/>
+      <c r="I106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -2913,22 +3330,28 @@
       <c r="F107" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G107" s="7" t="inlineStr">
+      <c r="G107" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr"/>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>2 competitors rank at AS 25 or below: 19 and 20. The results are mostly guides, not services</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="6" t="n"/>
-      <c r="B108" s="6" t="n"/>
-      <c r="C108" s="6" t="n"/>
-      <c r="D108" s="6" t="n"/>
-      <c r="E108" s="6" t="n"/>
-      <c r="F108" s="6" t="n"/>
-      <c r="G108" s="6" t="n"/>
-      <c r="H108" s="6" t="n"/>
+      <c r="A108" s="7" t="n"/>
+      <c r="B108" s="7" t="n"/>
+      <c r="C108" s="7" t="n"/>
+      <c r="D108" s="7" t="n"/>
+      <c r="E108" s="7" t="n"/>
+      <c r="F108" s="7" t="n"/>
+      <c r="G108" s="7" t="n"/>
+      <c r="H108" s="7" t="n"/>
+      <c r="I108" s="7" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -2963,16 +3386,22 @@
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr"/>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>5 competitors rank at AS 25 or below: 13, 21, 21, 24, 25. 2 council results</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="6" t="n"/>
-      <c r="B110" s="6" t="n"/>
-      <c r="C110" s="6" t="n"/>
-      <c r="D110" s="6" t="n"/>
-      <c r="E110" s="6" t="n"/>
-      <c r="F110" s="6" t="n"/>
-      <c r="G110" s="6" t="n"/>
-      <c r="H110" s="6" t="n"/>
+      <c r="A110" s="7" t="n"/>
+      <c r="B110" s="7" t="n"/>
+      <c r="C110" s="7" t="n"/>
+      <c r="D110" s="7" t="n"/>
+      <c r="E110" s="7" t="n"/>
+      <c r="F110" s="7" t="n"/>
+      <c r="G110" s="7" t="n"/>
+      <c r="H110" s="7" t="n"/>
+      <c r="I110" s="7" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -3007,16 +3436,22 @@
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr"/>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial waste collection leeds". 5 competitors rank at AS 25 or below: 13, 21, 21, 24, 25. 2 council results</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="6" t="n"/>
-      <c r="B112" s="6" t="n"/>
-      <c r="C112" s="6" t="n"/>
-      <c r="D112" s="6" t="n"/>
-      <c r="E112" s="6" t="n"/>
-      <c r="F112" s="6" t="n"/>
-      <c r="G112" s="6" t="n"/>
-      <c r="H112" s="6" t="n"/>
+      <c r="A112" s="7" t="n"/>
+      <c r="B112" s="7" t="n"/>
+      <c r="C112" s="7" t="n"/>
+      <c r="D112" s="7" t="n"/>
+      <c r="E112" s="7" t="n"/>
+      <c r="F112" s="7" t="n"/>
+      <c r="G112" s="7" t="n"/>
+      <c r="H112" s="7" t="n"/>
+      <c r="I112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -3051,16 +3486,22 @@
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr"/>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial waste collection leeds". 5 competitors rank at AS 25 or below: 13, 21, 21, 24, 25. 2 council results</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="6" t="n"/>
-      <c r="B114" s="6" t="n"/>
-      <c r="C114" s="6" t="n"/>
-      <c r="D114" s="6" t="n"/>
-      <c r="E114" s="6" t="n"/>
-      <c r="F114" s="6" t="n"/>
-      <c r="G114" s="6" t="n"/>
-      <c r="H114" s="6" t="n"/>
+      <c r="A114" s="7" t="n"/>
+      <c r="B114" s="7" t="n"/>
+      <c r="C114" s="7" t="n"/>
+      <c r="D114" s="7" t="n"/>
+      <c r="E114" s="7" t="n"/>
+      <c r="F114" s="7" t="n"/>
+      <c r="G114" s="7" t="n"/>
+      <c r="H114" s="7" t="n"/>
+      <c r="I114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -3095,16 +3536,22 @@
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr"/>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial waste collection leeds". 5 competitors rank at AS 25 or below: 13, 21, 21, 24, 25. 2 council results</t>
+        </is>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" s="6" t="n"/>
-      <c r="B116" s="6" t="n"/>
-      <c r="C116" s="6" t="n"/>
-      <c r="D116" s="6" t="n"/>
-      <c r="E116" s="6" t="n"/>
-      <c r="F116" s="6" t="n"/>
-      <c r="G116" s="6" t="n"/>
-      <c r="H116" s="6" t="n"/>
+      <c r="A116" s="7" t="n"/>
+      <c r="B116" s="7" t="n"/>
+      <c r="C116" s="7" t="n"/>
+      <c r="D116" s="7" t="n"/>
+      <c r="E116" s="7" t="n"/>
+      <c r="F116" s="7" t="n"/>
+      <c r="G116" s="7" t="n"/>
+      <c r="H116" s="7" t="n"/>
+      <c r="I116" s="7" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -3139,16 +3586,22 @@
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial waste collection leeds". 5 competitors rank at AS 25 or below: 13, 21, 21, 24, 25. 2 council results</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="6" t="n"/>
-      <c r="B118" s="6" t="n"/>
-      <c r="C118" s="6" t="n"/>
-      <c r="D118" s="6" t="n"/>
-      <c r="E118" s="6" t="n"/>
-      <c r="F118" s="6" t="n"/>
-      <c r="G118" s="6" t="n"/>
-      <c r="H118" s="6" t="n"/>
+      <c r="A118" s="7" t="n"/>
+      <c r="B118" s="7" t="n"/>
+      <c r="C118" s="7" t="n"/>
+      <c r="D118" s="7" t="n"/>
+      <c r="E118" s="7" t="n"/>
+      <c r="F118" s="7" t="n"/>
+      <c r="G118" s="7" t="n"/>
+      <c r="H118" s="7" t="n"/>
+      <c r="I118" s="7" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -3183,16 +3636,22 @@
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr"/>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial waste collection leeds". 5 competitors rank at AS 25 or below: 13, 21, 21, 24, 25. 2 council results</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="6" t="n"/>
-      <c r="B120" s="6" t="n"/>
-      <c r="C120" s="6" t="n"/>
-      <c r="D120" s="6" t="n"/>
-      <c r="E120" s="6" t="n"/>
-      <c r="F120" s="6" t="n"/>
-      <c r="G120" s="6" t="n"/>
-      <c r="H120" s="6" t="n"/>
+      <c r="A120" s="7" t="n"/>
+      <c r="B120" s="7" t="n"/>
+      <c r="C120" s="7" t="n"/>
+      <c r="D120" s="7" t="n"/>
+      <c r="E120" s="7" t="n"/>
+      <c r="F120" s="7" t="n"/>
+      <c r="G120" s="7" t="n"/>
+      <c r="H120" s="7" t="n"/>
+      <c r="I120" s="7" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -3221,12 +3680,17 @@
       <c r="F121" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="G121" s="7" t="inlineStr">
+      <c r="G121" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr"/>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>Shares the city page results. Semrush holds no keyword data for this term, so treat the volume as indicative only</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr"/>
@@ -3243,12 +3707,17 @@
       <c r="F122" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="G122" s="7" t="inlineStr">
+      <c r="G122" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>Shares the city page results. Semrush holds no keyword data for this term, so treat the volume as indicative only</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr"/>
@@ -3265,12 +3734,17 @@
       <c r="F123" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G123" s="7" t="inlineStr">
+      <c r="G123" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr"/>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>Shares the city page results. Semrush holds no keyword data for this term, so treat the volume as indicative only</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr"/>
@@ -3287,22 +3761,28 @@
       <c r="F124" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G124" s="7" t="inlineStr">
+      <c r="G124" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr"/>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>Shares the city page results. Semrush holds no keyword data for this term, so treat the volume as indicative only</t>
+        </is>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="6" t="n"/>
-      <c r="B125" s="6" t="n"/>
-      <c r="C125" s="6" t="n"/>
-      <c r="D125" s="6" t="n"/>
-      <c r="E125" s="6" t="n"/>
-      <c r="F125" s="6" t="n"/>
-      <c r="G125" s="6" t="n"/>
-      <c r="H125" s="6" t="n"/>
+      <c r="A125" s="7" t="n"/>
+      <c r="B125" s="7" t="n"/>
+      <c r="C125" s="7" t="n"/>
+      <c r="D125" s="7" t="n"/>
+      <c r="E125" s="7" t="n"/>
+      <c r="F125" s="7" t="n"/>
+      <c r="G125" s="7" t="n"/>
+      <c r="H125" s="7" t="n"/>
+      <c r="I125" s="7" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -3331,12 +3811,17 @@
       <c r="F126" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="G126" s="7" t="inlineStr">
+      <c r="G126" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>Shares the city page results. Semrush holds no keyword data for this term, so treat the volume as indicative only</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr"/>
@@ -3353,22 +3838,28 @@
       <c r="F127" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="G127" s="7" t="inlineStr">
+      <c r="G127" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr"/>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>Shares the city page results. Semrush holds no keyword data for this term, so treat the volume as indicative only</t>
+        </is>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" s="6" t="n"/>
-      <c r="B128" s="6" t="n"/>
-      <c r="C128" s="6" t="n"/>
-      <c r="D128" s="6" t="n"/>
-      <c r="E128" s="6" t="n"/>
-      <c r="F128" s="6" t="n"/>
-      <c r="G128" s="6" t="n"/>
-      <c r="H128" s="6" t="n"/>
+      <c r="A128" s="7" t="n"/>
+      <c r="B128" s="7" t="n"/>
+      <c r="C128" s="7" t="n"/>
+      <c r="D128" s="7" t="n"/>
+      <c r="E128" s="7" t="n"/>
+      <c r="F128" s="7" t="n"/>
+      <c r="G128" s="7" t="n"/>
+      <c r="H128" s="7" t="n"/>
+      <c r="I128" s="7" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -3397,12 +3888,17 @@
       <c r="F129" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="G129" s="7" t="inlineStr">
+      <c r="G129" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr"/>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>Shares the city page results. Semrush holds no keyword data for this term, so treat the volume as indicative only</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr"/>
@@ -3419,22 +3915,28 @@
       <c r="F130" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="G130" s="7" t="inlineStr">
+      <c r="G130" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>Same results as the London commercial waste page. 2 competitors rank at AS 25 or below: 18 and 25</t>
+        </is>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="6" t="n"/>
-      <c r="B131" s="6" t="n"/>
-      <c r="C131" s="6" t="n"/>
-      <c r="D131" s="6" t="n"/>
-      <c r="E131" s="6" t="n"/>
-      <c r="F131" s="6" t="n"/>
-      <c r="G131" s="6" t="n"/>
-      <c r="H131" s="6" t="n"/>
+      <c r="A131" s="7" t="n"/>
+      <c r="B131" s="7" t="n"/>
+      <c r="C131" s="7" t="n"/>
+      <c r="D131" s="7" t="n"/>
+      <c r="E131" s="7" t="n"/>
+      <c r="F131" s="7" t="n"/>
+      <c r="G131" s="7" t="n"/>
+      <c r="H131" s="7" t="n"/>
+      <c r="I131" s="7" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -3463,12 +3965,17 @@
       <c r="F132" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G132" s="7" t="inlineStr">
+      <c r="G132" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr"/>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>Same results as the Manchester city page. Lowest competitor is AS 27. 2 council results</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr"/>
@@ -3485,22 +3992,28 @@
       <c r="F133" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="G133" s="7" t="inlineStr">
+      <c r="G133" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr"/>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>Same results as the Manchester city page. Lowest competitor is AS 27. 2 council results</t>
+        </is>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" s="6" t="n"/>
-      <c r="B134" s="6" t="n"/>
-      <c r="C134" s="6" t="n"/>
-      <c r="D134" s="6" t="n"/>
-      <c r="E134" s="6" t="n"/>
-      <c r="F134" s="6" t="n"/>
-      <c r="G134" s="6" t="n"/>
-      <c r="H134" s="6" t="n"/>
+      <c r="A134" s="7" t="n"/>
+      <c r="B134" s="7" t="n"/>
+      <c r="C134" s="7" t="n"/>
+      <c r="D134" s="7" t="n"/>
+      <c r="E134" s="7" t="n"/>
+      <c r="F134" s="7" t="n"/>
+      <c r="G134" s="7" t="n"/>
+      <c r="H134" s="7" t="n"/>
+      <c r="I134" s="7" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -3529,22 +4042,28 @@
       <c r="F135" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="G135" s="7" t="inlineStr">
+      <c r="G135" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>1 competitor ranks at AS 24. Biffa at AS 46 holds third. 2 council results</t>
+        </is>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" s="6" t="n"/>
-      <c r="B136" s="6" t="n"/>
-      <c r="C136" s="6" t="n"/>
-      <c r="D136" s="6" t="n"/>
-      <c r="E136" s="6" t="n"/>
-      <c r="F136" s="6" t="n"/>
-      <c r="G136" s="6" t="n"/>
-      <c r="H136" s="6" t="n"/>
+      <c r="A136" s="7" t="n"/>
+      <c r="B136" s="7" t="n"/>
+      <c r="C136" s="7" t="n"/>
+      <c r="D136" s="7" t="n"/>
+      <c r="E136" s="7" t="n"/>
+      <c r="F136" s="7" t="n"/>
+      <c r="G136" s="7" t="n"/>
+      <c r="H136" s="7" t="n"/>
+      <c r="I136" s="7" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -3579,6 +4098,11 @@
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr"/>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "1100l bin". 3 competitors rank at AS 25 or below: 12, 13, 22. The matching page already exists</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr"/>
@@ -3601,16 +4125,22 @@
         </is>
       </c>
       <c r="H138" s="4" t="inlineStr"/>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>3 competitors rank at AS 25 or below: 12, 13, 22. The matching page already exists</t>
+        </is>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="6" t="n"/>
-      <c r="B139" s="6" t="n"/>
-      <c r="C139" s="6" t="n"/>
-      <c r="D139" s="6" t="n"/>
-      <c r="E139" s="6" t="n"/>
-      <c r="F139" s="6" t="n"/>
-      <c r="G139" s="6" t="n"/>
-      <c r="H139" s="6" t="n"/>
+      <c r="A139" s="7" t="n"/>
+      <c r="B139" s="7" t="n"/>
+      <c r="C139" s="7" t="n"/>
+      <c r="D139" s="7" t="n"/>
+      <c r="E139" s="7" t="n"/>
+      <c r="F139" s="7" t="n"/>
+      <c r="G139" s="7" t="n"/>
+      <c r="H139" s="7" t="n"/>
+      <c r="I139" s="7" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -3645,6 +4175,11 @@
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "1100l bin". 3 competitors rank at AS 25 or below: 12, 13, 22. The matching page already exists</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr"/>
@@ -3667,16 +4202,22 @@
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr"/>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "1100l bin". 3 competitors rank at AS 25 or below: 12, 13, 22. The matching page already exists</t>
+        </is>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" s="6" t="n"/>
-      <c r="B142" s="6" t="n"/>
-      <c r="C142" s="6" t="n"/>
-      <c r="D142" s="6" t="n"/>
-      <c r="E142" s="6" t="n"/>
-      <c r="F142" s="6" t="n"/>
-      <c r="G142" s="6" t="n"/>
-      <c r="H142" s="6" t="n"/>
+      <c r="A142" s="7" t="n"/>
+      <c r="B142" s="7" t="n"/>
+      <c r="C142" s="7" t="n"/>
+      <c r="D142" s="7" t="n"/>
+      <c r="E142" s="7" t="n"/>
+      <c r="F142" s="7" t="n"/>
+      <c r="G142" s="7" t="n"/>
+      <c r="H142" s="7" t="n"/>
+      <c r="I142" s="7" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -3711,6 +4252,11 @@
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr"/>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "1100l bin". 3 competitors rank at AS 25 or below: 12, 13, 22. The matching page already exists</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr"/>
@@ -3727,12 +4273,17 @@
       <c r="F144" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G144" s="7" t="inlineStr">
+      <c r="G144" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr"/>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial bin sizes". 1 competitor ranks at AS 22. Two more sit just above at AS 26 and 29. 3 council results</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr"/>
@@ -3749,22 +4300,28 @@
       <c r="F145" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G145" s="7" t="inlineStr">
+      <c r="G145" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "commercial bin sizes". 1 competitor ranks at AS 22. Two more sit just above at AS 26 and 29. 3 council results</t>
+        </is>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" s="6" t="n"/>
-      <c r="B146" s="6" t="n"/>
-      <c r="C146" s="6" t="n"/>
-      <c r="D146" s="6" t="n"/>
-      <c r="E146" s="6" t="n"/>
-      <c r="F146" s="6" t="n"/>
-      <c r="G146" s="6" t="n"/>
-      <c r="H146" s="6" t="n"/>
+      <c r="A146" s="7" t="n"/>
+      <c r="B146" s="7" t="n"/>
+      <c r="C146" s="7" t="n"/>
+      <c r="D146" s="7" t="n"/>
+      <c r="E146" s="7" t="n"/>
+      <c r="F146" s="7" t="n"/>
+      <c r="G146" s="7" t="n"/>
+      <c r="H146" s="7" t="n"/>
+      <c r="I146" s="7" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -3799,16 +4356,22 @@
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr"/>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "1100l bin". 3 competitors rank at AS 25 or below: 12, 13, 22. The matching page already exists</t>
+        </is>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="6" t="n"/>
-      <c r="B148" s="6" t="n"/>
-      <c r="C148" s="6" t="n"/>
-      <c r="D148" s="6" t="n"/>
-      <c r="E148" s="6" t="n"/>
-      <c r="F148" s="6" t="n"/>
-      <c r="G148" s="6" t="n"/>
-      <c r="H148" s="6" t="n"/>
+      <c r="A148" s="7" t="n"/>
+      <c r="B148" s="7" t="n"/>
+      <c r="C148" s="7" t="n"/>
+      <c r="D148" s="7" t="n"/>
+      <c r="E148" s="7" t="n"/>
+      <c r="F148" s="7" t="n"/>
+      <c r="G148" s="7" t="n"/>
+      <c r="H148" s="7" t="n"/>
+      <c r="I148" s="7" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -3843,16 +4406,22 @@
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr"/>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "1100l bin". 3 competitors rank at AS 25 or below: 12, 13, 22. The matching page already exists</t>
+        </is>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" s="6" t="n"/>
-      <c r="B150" s="6" t="n"/>
-      <c r="C150" s="6" t="n"/>
-      <c r="D150" s="6" t="n"/>
-      <c r="E150" s="6" t="n"/>
-      <c r="F150" s="6" t="n"/>
-      <c r="G150" s="6" t="n"/>
-      <c r="H150" s="6" t="n"/>
+      <c r="A150" s="7" t="n"/>
+      <c r="B150" s="7" t="n"/>
+      <c r="C150" s="7" t="n"/>
+      <c r="D150" s="7" t="n"/>
+      <c r="E150" s="7" t="n"/>
+      <c r="F150" s="7" t="n"/>
+      <c r="G150" s="7" t="n"/>
+      <c r="H150" s="7" t="n"/>
+      <c r="I150" s="7" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -3881,12 +4450,17 @@
       <c r="F151" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G151" s="7" t="inlineStr">
+      <c r="G151" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H151" s="4" t="inlineStr"/>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>1 competitor ranks at AS 15. 2 council results and three places held by Reddit, Facebook and YouTube</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr"/>
@@ -3903,12 +4477,17 @@
       <c r="F152" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="G152" s="7" t="inlineStr">
+      <c r="G152" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "maggots wheelie bins hot weather". 1 competitor ranks at AS 15. 2 council results and three places held by Reddit, Facebook and YouTube</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr"/>
@@ -3925,12 +4504,17 @@
       <c r="F153" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="G153" s="7" t="inlineStr">
+      <c r="G153" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr"/>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "maggots wheelie bins hot weather". 1 competitor ranks at AS 15. 2 council results and three places held by Reddit, Facebook and YouTube</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr"/>
@@ -3947,12 +4531,17 @@
       <c r="F154" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G154" s="7" t="inlineStr">
+      <c r="G154" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr"/>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "maggots wheelie bins hot weather". 1 competitor ranks at AS 15. 2 council results and three places held by Reddit, Facebook and YouTube</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr"/>
@@ -3969,22 +4558,28 @@
       <c r="F155" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G155" s="7" t="inlineStr">
+      <c r="G155" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr"/>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "maggots wheelie bins hot weather". 1 competitor ranks at AS 15. 2 council results and three places held by Reddit, Facebook and YouTube</t>
+        </is>
+      </c>
     </row>
     <row r="156">
-      <c r="A156" s="6" t="n"/>
-      <c r="B156" s="6" t="n"/>
-      <c r="C156" s="6" t="n"/>
-      <c r="D156" s="6" t="n"/>
-      <c r="E156" s="6" t="n"/>
-      <c r="F156" s="6" t="n"/>
-      <c r="G156" s="6" t="n"/>
-      <c r="H156" s="6" t="n"/>
+      <c r="A156" s="7" t="n"/>
+      <c r="B156" s="7" t="n"/>
+      <c r="C156" s="7" t="n"/>
+      <c r="D156" s="7" t="n"/>
+      <c r="E156" s="7" t="n"/>
+      <c r="F156" s="7" t="n"/>
+      <c r="G156" s="7" t="n"/>
+      <c r="H156" s="7" t="n"/>
+      <c r="I156" s="7" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -4013,22 +4608,28 @@
       <c r="F157" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G157" s="7" t="inlineStr">
+      <c r="G157" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="H157" s="4" t="inlineStr"/>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>1 competitor ranks at AS 22. Two more sit just above at AS 26 and 29. 3 council results</t>
+        </is>
+      </c>
     </row>
     <row r="158">
-      <c r="A158" s="6" t="n"/>
-      <c r="B158" s="6" t="n"/>
-      <c r="C158" s="6" t="n"/>
-      <c r="D158" s="6" t="n"/>
-      <c r="E158" s="6" t="n"/>
-      <c r="F158" s="6" t="n"/>
-      <c r="G158" s="6" t="n"/>
-      <c r="H158" s="6" t="n"/>
+      <c r="A158" s="7" t="n"/>
+      <c r="B158" s="7" t="n"/>
+      <c r="C158" s="7" t="n"/>
+      <c r="D158" s="7" t="n"/>
+      <c r="E158" s="7" t="n"/>
+      <c r="F158" s="7" t="n"/>
+      <c r="G158" s="7" t="n"/>
+      <c r="H158" s="7" t="n"/>
+      <c r="I158" s="7" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -4057,12 +4658,17 @@
       <c r="F159" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="G159" s="8" t="inlineStr">
+      <c r="G159" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H159" s="4" t="inlineStr"/>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>No competitor at AS 25 or below. 4 government results plus BBC and Guardian</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr"/>
@@ -4079,12 +4685,17 @@
       <c r="F160" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="G160" s="8" t="inlineStr">
+      <c r="G160" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H160" s="4" t="inlineStr"/>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "england bin collection rules 2026". No competitor at AS 25 or below. 4 government results plus BBC and Guardian</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr"/>
@@ -4101,12 +4712,17 @@
       <c r="F161" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="G161" s="8" t="inlineStr">
+      <c r="G161" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr"/>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "england bin collection rules 2026". No competitor at AS 25 or below. 4 government results plus BBC and Guardian</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr"/>
@@ -4123,12 +4739,17 @@
       <c r="F162" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="G162" s="8" t="inlineStr">
+      <c r="G162" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr"/>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "england bin collection rules 2026". No competitor at AS 25 or below. 4 government results plus BBC and Guardian</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr"/>
@@ -4145,12 +4766,17 @@
       <c r="F163" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="G163" s="8" t="inlineStr">
+      <c r="G163" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr"/>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>No competitor at AS 25 or below. Lowest is AS 41. 4 government results. Top 3 is out of reach but p8 to p10 is realistic</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr"/>
@@ -4167,12 +4793,17 @@
       <c r="F164" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="G164" s="8" t="inlineStr">
+      <c r="G164" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr"/>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "england bin collection rules 2026". No competitor at AS 25 or below. 4 government results plus BBC and Guardian</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr"/>
@@ -4189,22 +4820,28 @@
       <c r="F165" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="G165" s="8" t="inlineStr">
+      <c r="G165" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H165" s="4" t="inlineStr"/>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "simpler recycling". No competitor at AS 25 or below. Lowest is AS 41. 4 government results. Top 3 is out of reach but p8 to p10 is realistic</t>
+        </is>
+      </c>
     </row>
     <row r="166">
-      <c r="A166" s="6" t="n"/>
-      <c r="B166" s="6" t="n"/>
-      <c r="C166" s="6" t="n"/>
-      <c r="D166" s="6" t="n"/>
-      <c r="E166" s="6" t="n"/>
-      <c r="F166" s="6" t="n"/>
-      <c r="G166" s="6" t="n"/>
-      <c r="H166" s="6" t="n"/>
+      <c r="A166" s="7" t="n"/>
+      <c r="B166" s="7" t="n"/>
+      <c r="C166" s="7" t="n"/>
+      <c r="D166" s="7" t="n"/>
+      <c r="E166" s="7" t="n"/>
+      <c r="F166" s="7" t="n"/>
+      <c r="G166" s="7" t="n"/>
+      <c r="H166" s="7" t="n"/>
+      <c r="I166" s="7" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -4233,12 +4870,17 @@
       <c r="F167" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G167" s="8" t="inlineStr">
+      <c r="G167" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H167" s="4" t="inlineStr"/>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "waste transfer note". No competitor at AS 25 or below. Lowest is AS 45. 4 government results</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr"/>
@@ -4255,22 +4897,28 @@
       <c r="F168" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="G168" s="8" t="inlineStr">
+      <c r="G168" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr"/>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "waste transfer note". No competitor at AS 25 or below. Lowest is AS 45. 4 government results</t>
+        </is>
+      </c>
     </row>
     <row r="169">
-      <c r="A169" s="6" t="n"/>
-      <c r="B169" s="6" t="n"/>
-      <c r="C169" s="6" t="n"/>
-      <c r="D169" s="6" t="n"/>
-      <c r="E169" s="6" t="n"/>
-      <c r="F169" s="6" t="n"/>
-      <c r="G169" s="6" t="n"/>
-      <c r="H169" s="6" t="n"/>
+      <c r="A169" s="7" t="n"/>
+      <c r="B169" s="7" t="n"/>
+      <c r="C169" s="7" t="n"/>
+      <c r="D169" s="7" t="n"/>
+      <c r="E169" s="7" t="n"/>
+      <c r="F169" s="7" t="n"/>
+      <c r="G169" s="7" t="n"/>
+      <c r="H169" s="7" t="n"/>
+      <c r="I169" s="7" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -4299,22 +4947,28 @@
       <c r="F170" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="G170" s="8" t="inlineStr">
+      <c r="G170" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr"/>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>No competitor at AS 25 or below. 6 results are government registers</t>
+        </is>
+      </c>
     </row>
     <row r="171">
-      <c r="A171" s="6" t="n"/>
-      <c r="B171" s="6" t="n"/>
-      <c r="C171" s="6" t="n"/>
-      <c r="D171" s="6" t="n"/>
-      <c r="E171" s="6" t="n"/>
-      <c r="F171" s="6" t="n"/>
-      <c r="G171" s="6" t="n"/>
-      <c r="H171" s="6" t="n"/>
+      <c r="A171" s="7" t="n"/>
+      <c r="B171" s="7" t="n"/>
+      <c r="C171" s="7" t="n"/>
+      <c r="D171" s="7" t="n"/>
+      <c r="E171" s="7" t="n"/>
+      <c r="F171" s="7" t="n"/>
+      <c r="G171" s="7" t="n"/>
+      <c r="H171" s="7" t="n"/>
+      <c r="I171" s="7" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -4343,12 +4997,17 @@
       <c r="F172" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="G172" s="8" t="inlineStr">
+      <c r="G172" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H172" s="4" t="inlineStr"/>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "waste carriers licence". No competitor at AS 25 or below. 6 results are government registers</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr"/>
@@ -4365,22 +5024,28 @@
       <c r="F173" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="G173" s="8" t="inlineStr">
+      <c r="G173" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H173" s="4" t="inlineStr"/>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "waste carriers licence". No competitor at AS 25 or below. 6 results are government registers</t>
+        </is>
+      </c>
     </row>
     <row r="174">
-      <c r="A174" s="6" t="n"/>
-      <c r="B174" s="6" t="n"/>
-      <c r="C174" s="6" t="n"/>
-      <c r="D174" s="6" t="n"/>
-      <c r="E174" s="6" t="n"/>
-      <c r="F174" s="6" t="n"/>
-      <c r="G174" s="6" t="n"/>
-      <c r="H174" s="6" t="n"/>
+      <c r="A174" s="7" t="n"/>
+      <c r="B174" s="7" t="n"/>
+      <c r="C174" s="7" t="n"/>
+      <c r="D174" s="7" t="n"/>
+      <c r="E174" s="7" t="n"/>
+      <c r="F174" s="7" t="n"/>
+      <c r="G174" s="7" t="n"/>
+      <c r="H174" s="7" t="n"/>
+      <c r="I174" s="7" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -4409,12 +5074,17 @@
       <c r="F175" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="G175" s="8" t="inlineStr">
+      <c r="G175" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H175" s="4" t="inlineStr"/>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>No competitor at AS 25 or below. Lowest is AS 45. 4 government results</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr"/>
@@ -4431,12 +5101,17 @@
       <c r="F176" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="G176" s="8" t="inlineStr">
+      <c r="G176" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H176" s="4" t="inlineStr"/>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "waste transfer note". No competitor at AS 25 or below. Lowest is AS 45. 4 government results</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr"/>
@@ -4453,25 +5128,31 @@
       <c r="F177" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="G177" s="8" t="inlineStr">
+      <c r="G177" s="9" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
       <c r="H177" s="4" t="inlineStr"/>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>Same results as "waste transfer note". No competitor at AS 25 or below. Lowest is AS 45. 4 government results</t>
+        </is>
+      </c>
     </row>
     <row r="178">
-      <c r="A178" s="6" t="n"/>
-      <c r="B178" s="6" t="n"/>
-      <c r="C178" s="6" t="n"/>
-      <c r="D178" s="6" t="n"/>
-      <c r="E178" s="6" t="n"/>
-      <c r="F178" s="6" t="n"/>
-      <c r="G178" s="6" t="n"/>
-      <c r="H178" s="6" t="n"/>
+      <c r="A178" s="7" t="n"/>
+      <c r="B178" s="7" t="n"/>
+      <c r="C178" s="7" t="n"/>
+      <c r="D178" s="7" t="n"/>
+      <c r="E178" s="7" t="n"/>
+      <c r="F178" s="7" t="n"/>
+      <c r="G178" s="7" t="n"/>
+      <c r="H178" s="7" t="n"/>
+      <c r="I178" s="7" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H178"/>
+  <autoFilter ref="A1:I178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4491,302 +5172,302 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Keyword</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>SV</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Why not</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>bulky waste collection</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="12" t="n">
         <v>9900</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>Council collection intent</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>clinical waste disposal</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="12" t="n">
         <v>2900</v>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="11" t="inlineStr">
         <is>
           <t>Household intent - 6 council results</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>weee recycling</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="12" t="n">
         <v>2400</v>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>Consumer scheme at #1, Amazon at #6</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>clinical waste collection</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="12" t="n">
         <v>1900</v>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>Household intent - 6 council results</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>hazardous waste disposal</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="12" t="n">
         <v>1900</v>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Household hazardous waste</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>clinical waste</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="12" t="n">
         <v>1600</v>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Household intent</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>waste container</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="12" t="n">
         <v>1600</v>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>Retail intent - bin shops</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>hazardous waste collection</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="12" t="n">
         <v>1300</v>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Household hazardous waste</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>green waste collection</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="12" t="n">
         <v>1300</v>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Residential garden waste</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>medical waste collection</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="12" t="n">
         <v>880</v>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>Household sharps - 7 council results</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>1100 litre bin</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="12" t="n">
         <v>720</v>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Retail intent - bin shops</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>660 litre bin</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="12" t="n">
         <v>720</v>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Retail intent - bin shops</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>electrical waste disposal</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="12" t="n">
         <v>590</v>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>6 council and national-scheme results</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>240 litre bin</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="12" t="n">
         <v>590</v>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Retail intent - bin shops</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>clinical waste removal</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="12" t="n">
         <v>590</v>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Household intent</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>commercial wheelie bin</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="12" t="n">
         <v>320</v>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Retail intent - bin shops</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>wheelie bin hire</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="12" t="n">
         <v>320</v>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Retail intent - bin shops</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>eurobin</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="12" t="n">
         <v>260</v>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Retail intent - bin shops</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>1100 litre bin dimensions</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Retail intent - bin shops</t>
         </is>
@@ -4803,283 +5484,418 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="72" customWidth="1" min="2" max="2"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>Issue</t>
-        </is>
-      </c>
-      <c r="C1" s="9" t="inlineStr">
-        <is>
-          <t>Action</t>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>What is wrong</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>What to do</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>Manchester/London/Birmingham city pages: the "new" URLs 301 while the "-old" URLs serve 200</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>VERIFY FIRST where the three 301s point, then either rename the -old URLs as canonical or fix the redirect. Do NOT blindly 301 old-&gt;new: that risks a loop</t>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Redirects</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>The Manchester, London and Birmingham city URLs redirect while their older equivalents are the live pages</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>/areas-we-cover-old/manchester/, /london/ and /birmingham/ all return 200. /areas-we-cover/manchester/, /london/ and /birmingham/ all return 301. Google ranks the older URLs because they are the only ones resolving</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Check where the three redirects point before changing anything. If they point at the older URLs, rename those as canonical. If they point elsewhere, the redirect is the bug. Do not redirect old to new without checking, it may create a loop</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>www and non-www both indexed</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Enforce one hostname via 301 + canonical + GSC property</t>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Duplicate pages</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Four live pages target the same commercial head terms</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>/commercial-waste-collection/, /commercial-waste-management/, /business-waste-collections/ and /trade-waste-collections/ all return 200 and all target commercial waste terms. business waste collection at 2,400 SV ranks twice, p26 and p34, and neither reaches the top 20</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Choose /commercial-waste-collection/ as the single money page. Redirect or de optimise the other three</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Two pages competing for the core money term</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Consolidate into one canonical money page; 301 the other</t>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Canonical</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>The site resolves on both www and non www</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Both betterwaste.co.uk/polystyrene-and-recycling/ and www.betterwaste.co.uk/polystyrene-and-recycling rank as separate URLs. Same for /business-waste-collections</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Pick one hostname. Add a site wide 301, set the canonical tag, and set the preferred property in Search Console</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Simpler Recycling page stuck just outside top 10</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Refresh content + internal links; target top 10</t>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Quick win</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>The Simpler Recycling page sits just outside the top 10</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>simpler recycling at 1,000 SV and KD 22 ranks p14 on /simpler-recycling-legislation-for-businesses-in-england-what-you-need-to-know/</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Refresh the content and add internal links. This is the cheapest ranking gain available on the site</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Glass keywords mapped to the wrong page block</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Re-map all glass terms to /glass-waste/</t>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Keyword mapping</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Glass keywords are mapped to the food waste page</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>In the current tracker the glass terms sit inside the /food-waste/ block. A live /glass-waste/ page already ranks p30 to p38 for them</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Move all glass terms onto /glass-waste/</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Location hub ranking for national service terms</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Build the national /commercial-waste-collection/ page and de-optimise the hub</t>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Wrong page ranking</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>The areas hub ranks for national service terms it should not own</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>/areas-we-cover/ ranks for business refuse collection p5 at 590 SV, waste collection for business p59, commercial waste services p54, industrial waste collection p83 and waste disposal companies p63</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Optimise the existing /commercial-waste-collection/ page for these terms and remove them from the areas hub</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Blog post and service page competing</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Differentiate intent; internal-link blog to the service page</t>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Internal linking</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>The strongest page on the site passes no value to the commercial pages</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>/top-10-commercial-waste-management-companies-in-the-uk/ ranks p4 to p8 for around 20 head terms. It is a listicle naming competitors and links nowhere useful</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Add prominent internal links from it to /commercial-waste-collection/</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Strongest page not passing equity to money pages</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Add prominent internal links to the new commercial waste page</t>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Duplicate pages</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>A blog post outranks the service page for a commercial term</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>commercial waste management companies ranks p7 with the blog listicle and p90 with /business-waste-collections/</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Separate the two by intent and link the blog to the service page</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Several keywords returning two URLs from the same site</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Audit for duplicate/paginated variants and consolidate</t>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Duplicate pages</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Two live pages cover clinical and healthcare waste</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>/clinical-waste-disposal-clinical-waste-collection-companies/ and /healthcare-waste/ both return 200</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Merge into one page. Target commercial terms such as dental waste disposal and sharps bin collection rather than the household head terms</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Duplicate URLs</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Six keywords return two of your own URLs in the same results</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>business waste birmingham p19 and p26, commercial waste clearance birmingham p40 and p41, waste management companies london p29 and p32, zero waste to landfill p54 and p60, aluminium recycling p18 and p24, expanded polystyrene recycling p65 and p66</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Find the duplicate or paginated variants behind each and consolidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Duplicate URLs</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Pages load on both the slash and non slash URL</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>/about and /about/, /binpedia and /binpedia/, /contact-us and /contact-us/, /blog and /blog/, /faqs and /faqs/, /how-to-be-green and /how-to-be-green/</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Pick one convention and redirect the other site wide</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Index bloat</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Test and duplicate pages are indexable</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>/222-2/, /test-2/, /home/, /thank-you/, /thank-you-2/, /trial-form/, /quote2-old/, /quote-commercial-waste-old/ and /quote-waste-services-old/ all return 200. /quote2/ also has six indexable parameter variants</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Noindex or remove them and add parameter handling for the quote form</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Sheet volumes materially out of date vs Semrush</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Refresh all SV in the mapping sheet from Semrush UK</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Four live pages target overlapping commercial head terms</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Pick one canonical money page, 301 or de-optimise the other three</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>Two live clinical/healthcare waste pages</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Consolidate into one, re-point at commercial entry terms not the household head terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Test, duplicate and thank-you pages indexable</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>noindex or remove; add parameter handling for ?slink=</t>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Lost pages</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Four former pages now return 404 and may still hold links</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>/better-waste-solutions-birmingham/, /better-waste-solutions-london/, /better-waste-solutions-manchester/ and /business-waste-management-yorkshire/</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Check referring domains for each. Redirect any that hold links to the matching city or service page</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Trailing-slash and non-slash both serve 200</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Enforce one trailing-slash convention site-wide</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Four former pages now 404 and may hold links</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Check referring domains for each; 301 the ones with links to the relevant city or service page</t>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Data hygiene</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Volumes in the current tracker are out of date</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>dry mixed recycling bins is listed at 320, Semrush shows 720. commercial cardboard waste is listed at 110, Semrush shows 320. commercial food waste disposal is listed at 210, Semrush shows 480</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Refresh every volume in the tracker from Semrush UK</t>
         </is>
       </c>
     </row>

--- a/betterwaste-kw-audit/Better_Waste_Keyword_Plan.xlsx
+++ b/betterwaste-kw-audit/Better_Waste_Keyword_Plan.xlsx
@@ -8,11 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Keyword Plan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Do Not Target" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Fixes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Fixes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Keyword Plan'!$A$1:$I$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Keyword Plan'!$A$1:$J$178</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -122,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,12 +149,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -527,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I178"/>
+  <dimension ref="A1:J178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -538,7 +531,8 @@
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="86" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="86" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -587,6 +581,11 @@
           <t>Evidence (Authority Score)</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Who ranks now (Authority Score)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -624,6 +623,11 @@
       <c r="I2" s="6" t="inlineStr">
         <is>
           <t>4 competitors rank at AS 25 or below: 11, 12, 12, 24. Confirm Better Waste offers skips</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>tj-waste.co.uk (31), wsrecycling.co.uk (29), tomwhitewaste.co.uk (24), budgetskipsdirect.co.uk (12), thewastemonkeys.co.uk (11)</t>
         </is>
       </c>
     </row>
@@ -653,6 +657,11 @@
           <t>Same results as "skip sizes uk". 4 competitors rank at AS 25 or below: 11, 12, 12, 24. Confirm Better Waste offers skips</t>
         </is>
       </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>tj-waste.co.uk (31), wsrecycling.co.uk (29), tomwhitewaste.co.uk (24), budgetskipsdirect.co.uk (12), thewastemonkeys.co.uk (11)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr"/>
@@ -680,6 +689,11 @@
           <t>Same results as "skip sizes uk". 4 competitors rank at AS 25 or below: 11, 12, 12, 24. Confirm Better Waste offers skips</t>
         </is>
       </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>tj-waste.co.uk (31), wsrecycling.co.uk (29), tomwhitewaste.co.uk (24), budgetskipsdirect.co.uk (12), thewastemonkeys.co.uk (11)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr"/>
@@ -707,6 +721,11 @@
           <t>Same results as "skip sizes uk". 4 competitors rank at AS 25 or below: 11, 12, 12, 24. Confirm Better Waste offers skips</t>
         </is>
       </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>tj-waste.co.uk (31), wsrecycling.co.uk (29), tomwhitewaste.co.uk (24), budgetskipsdirect.co.uk (12), thewastemonkeys.co.uk (11)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr"/>
@@ -732,6 +751,11 @@
       <c r="I6" s="6" t="inlineStr">
         <is>
           <t>Same results as "skip sizes uk". 4 competitors rank at AS 25 or below: 11, 12, 12, 24. Confirm Better Waste offers skips</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>tj-waste.co.uk (31), wsrecycling.co.uk (29), tomwhitewaste.co.uk (24), budgetskipsdirect.co.uk (12), thewastemonkeys.co.uk (11)</t>
         </is>
       </c>
     </row>
@@ -745,6 +769,7 @@
       <c r="G7" s="7" t="n"/>
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -782,6 +807,11 @@
       <c r="I8" s="6" t="inlineStr">
         <is>
           <t>Same results as "commercial rubbish removal". 1 competitor ranks at AS 10. The only reachable term in the commercial head group</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>veolia.co.uk (48), gov.uk, junkwize.com (30), thefirstmile.co.uk (39), chuckit.co.uk (10)</t>
         </is>
       </c>
     </row>
@@ -811,6 +841,11 @@
           <t>Same results as "commercial rubbish removal". 1 competitor ranks at AS 10. The only reachable term in the commercial head group</t>
         </is>
       </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>veolia.co.uk (48), gov.uk, junkwize.com (30), thefirstmile.co.uk (39), chuckit.co.uk (10)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr"/>
@@ -838,6 +873,11 @@
           <t>1 competitor ranks at AS 10. The only reachable term in the commercial head group</t>
         </is>
       </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>veolia.co.uk (48), gov.uk, junkwize.com (30), thefirstmile.co.uk (39), chuckit.co.uk (10)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr"/>
@@ -865,6 +905,11 @@
           <t>No competitor at AS 25 or below. Lowest is AS 31. 6 council results</t>
         </is>
       </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>biffa.co.uk (46), veolia.co.uk (48), gov.uk, ipswich.gov.uk, hillingdon.gov.uk</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr"/>
@@ -892,6 +937,11 @@
           <t>No competitor at AS 25 or below. Lowest is AS 29. 5 council results</t>
         </is>
       </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>gov.uk, dudley.gov.uk, recycleforgreatermanchester.com, hertfordshire.gov.uk, ward.com</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr"/>
@@ -919,6 +969,11 @@
           <t>No competitor at AS 25 or below. Lowest is AS 41. 4 council results</t>
         </is>
       </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>veolia.co.uk (48), biffa.co.uk (46), gov.uk, businesswaste.co.uk (41), dudley.gov.uk</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr"/>
@@ -946,6 +1001,11 @@
           <t>Same results as "commercial waste collection". No competitor at AS 25 or below. Lowest is AS 31. 6 council results</t>
         </is>
       </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>biffa.co.uk (46), veolia.co.uk (48), gov.uk, ipswich.gov.uk, hillingdon.gov.uk</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr"/>
@@ -973,6 +1033,11 @@
           <t>Same results as "commercial waste disposal". No competitor at AS 25 or below. Lowest is AS 29. 5 council results</t>
         </is>
       </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>gov.uk, dudley.gov.uk, recycleforgreatermanchester.com, hertfordshire.gov.uk, ward.com</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr"/>
@@ -1000,6 +1065,11 @@
           <t>Same results as "trade waste collection". No competitor at AS 25 or below. Lowest is AS 46. 6 council results</t>
         </is>
       </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>veolia.co.uk (48), biffa.co.uk (46), newport.gov.uk, cardifftradewaste.co.uk, harrow.gov.uk</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr"/>
@@ -1027,6 +1097,11 @@
           <t>Same results as "commercial waste management". No competitor at AS 25 or below. Lowest is AS 41. 4 council results</t>
         </is>
       </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>veolia.co.uk (48), biffa.co.uk (46), gov.uk, businesswaste.co.uk (41), dudley.gov.uk</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr"/>
@@ -1054,6 +1129,11 @@
           <t>No competitor at AS 25 or below. Lowest is AS 39. 4 council results</t>
         </is>
       </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>biffa.co.uk (46), veolia.co.uk (48), gov.uk, businesswaste.co.uk (41), hertfordshire.gov.uk</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr"/>
@@ -1081,6 +1161,11 @@
           <t>No competitor at AS 25 or below. Lowest is AS 46. 6 council results</t>
         </is>
       </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>veolia.co.uk (48), biffa.co.uk (46), newport.gov.uk, cardifftradewaste.co.uk, harrow.gov.uk</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr"/>
@@ -1106,6 +1191,11 @@
       <c r="I20" s="6" t="inlineStr">
         <is>
           <t>Same results as "commercial waste management". No competitor at AS 25 or below. Lowest is AS 41. 4 council results</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>veolia.co.uk (48), biffa.co.uk (46), gov.uk, businesswaste.co.uk (41), dudley.gov.uk</t>
         </is>
       </c>
     </row>
@@ -1119,6 +1209,7 @@
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="7" t="n"/>
       <c r="I21" s="7" t="n"/>
+      <c r="J21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1156,6 +1247,11 @@
       <c r="I22" s="6" t="inlineStr">
         <is>
           <t>Same results as "commercial bin sizes". 1 competitor ranks at AS 22. Two more sit just above at AS 26 and 29. 3 council results</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>businesswaste.co.uk (41), braintree.gov.uk, gwrwastemanagement.co.uk (22), wheeliebinsolutions.co.uk (33), ashwasteservices.co.uk (26)</t>
         </is>
       </c>
     </row>
@@ -1185,6 +1281,11 @@
           <t>Same results as "commercial waste collection". No competitor at AS 25 or below. Lowest is AS 31. 6 council results</t>
         </is>
       </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>biffa.co.uk (46), veolia.co.uk (48), gov.uk, ipswich.gov.uk, hillingdon.gov.uk</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr"/>
@@ -1212,6 +1313,11 @@
           <t>Same results as "commercial waste collection". No competitor at AS 25 or below. Lowest is AS 31. 6 council results</t>
         </is>
       </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>biffa.co.uk (46), veolia.co.uk (48), gov.uk, ipswich.gov.uk, hillingdon.gov.uk</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr"/>
@@ -1237,6 +1343,11 @@
       <c r="I25" s="6" t="inlineStr">
         <is>
           <t>Same results as "commercial waste collection". No competitor at AS 25 or below. Lowest is AS 31. 6 council results</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>biffa.co.uk (46), veolia.co.uk (48), gov.uk, ipswich.gov.uk, hillingdon.gov.uk</t>
         </is>
       </c>
     </row>
@@ -1250,6 +1361,7 @@
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
       <c r="I26" s="7" t="n"/>
+      <c r="J26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1287,6 +1399,11 @@
       <c r="I27" s="6" t="inlineStr">
         <is>
           <t>Small shredding firms hold the results, including AS 16 and AS 10. No council results</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>homeshreduk.co.uk, restore.co.uk (37), shredstation.co.uk, simply-shredding.co.uk (16), doxbond.co.uk (10)</t>
         </is>
       </c>
     </row>
@@ -1316,6 +1433,11 @@
           <t>4 competitors rank at AS 25 or below: 6, 9, 10, 16. No council results</t>
         </is>
       </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>simply-shredding.co.uk (16), recorra.co.uk (30), prioritywaste.co.uk (9), shredalert.co.uk (6), doxbond.co.uk (10)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr"/>
@@ -1343,6 +1465,11 @@
           <t>Same results as "confidential waste collection". 4 competitors rank at AS 25 or below: 6, 9, 10, 16. No council results</t>
         </is>
       </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>simply-shredding.co.uk (16), recorra.co.uk (30), prioritywaste.co.uk (9), shredalert.co.uk (6), doxbond.co.uk (10)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr"/>
@@ -1370,6 +1497,11 @@
           <t>Same results as "document shredding". Small shredding firms hold the results, including AS 16 and AS 10. No council results</t>
         </is>
       </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>homeshreduk.co.uk, restore.co.uk (37), shredstation.co.uk, simply-shredding.co.uk (16), doxbond.co.uk (10)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr"/>
@@ -1397,6 +1529,11 @@
           <t>Same results as "document shredding". Small shredding firms hold the results, including AS 16 and AS 10. No council results</t>
         </is>
       </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>homeshreduk.co.uk, restore.co.uk (37), shredstation.co.uk, simply-shredding.co.uk (16), doxbond.co.uk (10)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr"/>
@@ -1424,6 +1561,11 @@
           <t>Same results as "document shredding". Small shredding firms hold the results, including AS 16 and AS 10. No council results</t>
         </is>
       </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>homeshreduk.co.uk, restore.co.uk (37), shredstation.co.uk, simply-shredding.co.uk (16), doxbond.co.uk (10)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr"/>
@@ -1451,6 +1593,11 @@
           <t>Same results as "document shredding". Small shredding firms hold the results, including AS 16 and AS 10. No council results</t>
         </is>
       </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>homeshreduk.co.uk, restore.co.uk (37), shredstation.co.uk, simply-shredding.co.uk (16), doxbond.co.uk (10)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr"/>
@@ -1476,6 +1623,11 @@
       <c r="I34" s="6" t="inlineStr">
         <is>
           <t>Mid size shredding firms hold the results. No council results</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>homeshreduk.co.uk, thefirstmile.co.uk (39), suez.co.uk (40), restore.co.uk (37), printwaste.co.uk (24)</t>
         </is>
       </c>
     </row>
@@ -1489,6 +1641,7 @@
       <c r="G35" s="7" t="n"/>
       <c r="H35" s="7" t="n"/>
       <c r="I35" s="7" t="n"/>
+      <c r="J35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1526,6 +1679,11 @@
       <c r="I36" s="6" t="inlineStr">
         <is>
           <t>Same results as "business cardboard recycling". 3 competitors rank at AS 25 or below: 8, 9, 18</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>businesswaste.co.uk (41), ecogenrecycling.co.uk (18), thefirstmile.co.uk (39), yorwaste.co.uk (29), inspirewaste.co.uk (20)</t>
         </is>
       </c>
     </row>
@@ -1555,6 +1713,11 @@
           <t>Same results as "business cardboard recycling". 3 competitors rank at AS 25 or below: 8, 9, 18</t>
         </is>
       </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>businesswaste.co.uk (41), ecogenrecycling.co.uk (18), thefirstmile.co.uk (39), yorwaste.co.uk (29), inspirewaste.co.uk (20)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr"/>
@@ -1582,6 +1745,11 @@
           <t>Same results as "business cardboard recycling". 3 competitors rank at AS 25 or below: 8, 9, 18</t>
         </is>
       </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>businesswaste.co.uk (41), ecogenrecycling.co.uk (18), thefirstmile.co.uk (39), yorwaste.co.uk (29), inspirewaste.co.uk (20)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr"/>
@@ -1609,6 +1777,11 @@
           <t>3 competitors rank at AS 25 or below: 8, 9, 18</t>
         </is>
       </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>businesswaste.co.uk (41), ecogenrecycling.co.uk (18), thefirstmile.co.uk (39), yorwaste.co.uk (29), inspirewaste.co.uk (20)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr"/>
@@ -1636,6 +1809,11 @@
           <t>Same results as "business cardboard recycling". 3 competitors rank at AS 25 or below: 8, 9, 18</t>
         </is>
       </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>businesswaste.co.uk (41), ecogenrecycling.co.uk (18), thefirstmile.co.uk (39), yorwaste.co.uk (29), inspirewaste.co.uk (20)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr"/>
@@ -1663,6 +1841,11 @@
           <t>Same results as "business cardboard recycling". 3 competitors rank at AS 25 or below: 8, 9, 18</t>
         </is>
       </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>businesswaste.co.uk (41), ecogenrecycling.co.uk (18), thefirstmile.co.uk (39), yorwaste.co.uk (29), inspirewaste.co.uk (20)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr"/>
@@ -1688,6 +1871,11 @@
       <c r="I42" s="6" t="inlineStr">
         <is>
           <t>Same results as "business cardboard recycling". 3 competitors rank at AS 25 or below: 8, 9, 18</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>businesswaste.co.uk (41), ecogenrecycling.co.uk (18), thefirstmile.co.uk (39), yorwaste.co.uk (29), inspirewaste.co.uk (20)</t>
         </is>
       </c>
     </row>
@@ -1701,6 +1889,7 @@
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="7" t="n"/>
       <c r="I43" s="7" t="n"/>
+      <c r="J43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1738,6 +1927,11 @@
       <c r="I44" s="6" t="inlineStr">
         <is>
           <t>Same results as "sanitary waste collection". 4 competitors rank at AS 25 or below: 9, 9, 13, 21. No council results</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>phs.co.uk (40), initial.co.uk (35), trusthygiene.co.uk (21), anwaywashrooms.co.uk (9), cleaningservicesbirmingham.org (9)</t>
         </is>
       </c>
     </row>
@@ -1765,6 +1959,11 @@
       <c r="I45" s="6" t="inlineStr">
         <is>
           <t>4 competitors rank at AS 25 or below: 9, 9, 13, 21. No council results</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>phs.co.uk (40), initial.co.uk (35), trusthygiene.co.uk (21), anwaywashrooms.co.uk (9), cleaningservicesbirmingham.org (9)</t>
         </is>
       </c>
     </row>
@@ -1778,6 +1977,7 @@
       <c r="G46" s="7" t="n"/>
       <c r="H46" s="7" t="n"/>
       <c r="I46" s="7" t="n"/>
+      <c r="J46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1815,6 +2015,11 @@
       <c r="I47" s="6" t="inlineStr">
         <is>
           <t>Same results as "it equipment disposal". 6 competitors rank at AS 25 or below: 2, 8, 19, 19, 20, 20</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>greenitdisposal.co.uk (16), computeritdisposals.co.uk (25), nationalitdisposal.co.uk (19), conceptmanagement.co.uk (19), mghscotland.co.uk (2)</t>
         </is>
       </c>
     </row>
@@ -1842,6 +2047,11 @@
       <c r="I48" s="6" t="inlineStr">
         <is>
           <t>6 competitors rank at AS 25 or below: 2, 8, 19, 19, 20, 20</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>greenitdisposal.co.uk (16), computeritdisposals.co.uk (25), nationalitdisposal.co.uk (19), conceptmanagement.co.uk (19), mghscotland.co.uk (2)</t>
         </is>
       </c>
     </row>
@@ -1855,6 +2065,7 @@
       <c r="G49" s="7" t="n"/>
       <c r="H49" s="7" t="n"/>
       <c r="I49" s="7" t="n"/>
+      <c r="J49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1892,6 +2103,11 @@
       <c r="I50" s="6" t="inlineStr">
         <is>
           <t>Same results as "business cardboard recycling". 3 competitors rank at AS 25 or below: 8, 9, 18</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>businesswaste.co.uk (41), ecogenrecycling.co.uk (18), thefirstmile.co.uk (39), yorwaste.co.uk (29), inspirewaste.co.uk (20)</t>
         </is>
       </c>
     </row>
@@ -1919,6 +2135,11 @@
       <c r="I51" s="6" t="inlineStr">
         <is>
           <t>Same results as "business cardboard recycling". 3 competitors rank at AS 25 or below: 8, 9, 18</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>businesswaste.co.uk (41), ecogenrecycling.co.uk (18), thefirstmile.co.uk (39), yorwaste.co.uk (29), inspirewaste.co.uk (20)</t>
         </is>
       </c>
     </row>
@@ -1932,6 +2153,7 @@
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="7" t="n"/>
       <c r="I52" s="7" t="n"/>
+      <c r="J52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1969,6 +2191,11 @@
       <c r="I53" s="6" t="inlineStr">
         <is>
           <t>4 competitors rank at AS 25 or below: 9, 11, 18, 22</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>londonrubbishcollection.uk (9), communitywoodrecycling.org.uk (29), bodensgroup.com (18), jerichowoodshack.uk (22), cshenvironmental.co.uk (11)</t>
         </is>
       </c>
     </row>
@@ -1982,6 +2209,7 @@
       <c r="G54" s="7" t="n"/>
       <c r="H54" s="7" t="n"/>
       <c r="I54" s="7" t="n"/>
+      <c r="J54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2019,6 +2247,11 @@
       <c r="I55" s="6" t="inlineStr">
         <is>
           <t>6 competitors rank at AS 25 or below: 2, 6, 7, 19, 19, 20</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>watersidefoods.co.uk (20), oil-solutions.co.uk (7), cawleys.co.uk (26), oilcollector.co.uk (6), ulevo.co.uk (2)</t>
         </is>
       </c>
     </row>
@@ -2032,6 +2265,7 @@
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
       <c r="I56" s="7" t="n"/>
+      <c r="J56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2069,6 +2303,11 @@
       <c r="I57" s="6" t="inlineStr">
         <is>
           <t>5 competitors rank at AS 25 or below: 9, 11, 15, 17, 20. All are scrap merchants who buy scrap rather than sell collection</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>mattmetal.co.uk (9), scrapmetalcollection.net (20), recyclemetals.org (36), scrap4free.co.uk (11), ukmetals.co.uk (15)</t>
         </is>
       </c>
     </row>
@@ -2082,6 +2321,7 @@
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
       <c r="I58" s="7" t="n"/>
+      <c r="J58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2119,6 +2359,11 @@
       <c r="I59" s="6" t="inlineStr">
         <is>
           <t>Same results as "dental waste disposal". 1 competitor ranks at AS 10. The results are mostly guides and trade press</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>bda.org, phs.co.uk (40), stericycle.co.uk (32), reconomy.com (34), wgswaste.co.uk (10)</t>
         </is>
       </c>
     </row>
@@ -2132,6 +2377,7 @@
       <c r="G60" s="7" t="n"/>
       <c r="H60" s="7" t="n"/>
       <c r="I60" s="7" t="n"/>
+      <c r="J60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2169,6 +2415,11 @@
       <c r="I61" s="6" t="inlineStr">
         <is>
           <t>2 competitors rank at AS 25 or below: 14 and 18. 3 government results</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>veolia.co.uk (48), envirocraft.co.uk (14), gov.uk, businesswaste.co.uk (41), oatesenvironmental.co.uk (18)</t>
         </is>
       </c>
     </row>
@@ -2196,6 +2447,11 @@
       <c r="I62" s="6" t="inlineStr">
         <is>
           <t>Same results as "industrial waste disposal". 2 competitors rank at AS 25 or below: 14 and 18. 3 government results</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>veolia.co.uk (48), envirocraft.co.uk (14), gov.uk, businesswaste.co.uk (41), oatesenvironmental.co.uk (18)</t>
         </is>
       </c>
     </row>
@@ -2209,6 +2465,7 @@
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="7" t="n"/>
       <c r="I63" s="7" t="n"/>
+      <c r="J63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2246,6 +2503,11 @@
       <c r="I64" s="6" t="inlineStr">
         <is>
           <t>1 competitor ranks at AS 20. Powerday, Bywaters and Biffa hold the rest</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>powerday.co.uk (29), bywaters.co.uk (32), westminster.gov.uk, biffa.co.uk (46), cirecoscotland.co.uk (20)</t>
         </is>
       </c>
     </row>
@@ -2273,6 +2535,11 @@
       <c r="I65" s="6" t="inlineStr">
         <is>
           <t>Same results as "construction waste disposal". 1 competitor ranks at AS 20. Powerday, Bywaters and Biffa hold the rest</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>powerday.co.uk (29), bywaters.co.uk (32), westminster.gov.uk, biffa.co.uk (46), cirecoscotland.co.uk (20)</t>
         </is>
       </c>
     </row>
@@ -2286,6 +2553,7 @@
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="7" t="n"/>
       <c r="I66" s="7" t="n"/>
+      <c r="J66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2323,6 +2591,11 @@
       <c r="I67" s="6" t="inlineStr">
         <is>
           <t>1 competitor ranks at AS 24. 3 council results. The page already ranks p30</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>grundon.com (34), gaskellswaste.co.uk (28), veolia.co.uk (48), westminster.gov.uk, daygroup.co.uk (24)</t>
         </is>
       </c>
     </row>
@@ -2336,6 +2609,7 @@
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="7" t="n"/>
       <c r="I68" s="7" t="n"/>
+      <c r="J68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2373,6 +2647,11 @@
       <c r="I69" s="6" t="inlineStr">
         <is>
           <t>Same results as "commercial glass collection". 1 competitor ranks at AS 24. 3 council results. The page already ranks p30</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>grundon.com (34), gaskellswaste.co.uk (28), veolia.co.uk (48), westminster.gov.uk, daygroup.co.uk (24)</t>
         </is>
       </c>
     </row>
@@ -2400,6 +2679,11 @@
       <c r="I70" s="6" t="inlineStr">
         <is>
           <t>Same results as "commercial glass collection". 1 competitor ranks at AS 24. 3 council results. The page already ranks p30</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>grundon.com (34), gaskellswaste.co.uk (28), veolia.co.uk (48), westminster.gov.uk, daygroup.co.uk (24)</t>
         </is>
       </c>
     </row>
@@ -2413,6 +2697,7 @@
       <c r="G71" s="7" t="n"/>
       <c r="H71" s="7" t="n"/>
       <c r="I71" s="7" t="n"/>
+      <c r="J71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2450,6 +2735,11 @@
       <c r="I72" s="6" t="inlineStr">
         <is>
           <t>No competitor at AS 25 or below. Lowest is AS 34. Government and Wikipedia hold the results</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>gov.uk, reconomy.com (34), europa.eu, veolia.co.uk (48), businesswaste.co.uk (41)</t>
         </is>
       </c>
     </row>
@@ -2479,6 +2769,11 @@
           <t>Same results as "waste transfer note". No competitor at AS 25 or below. Lowest is AS 45. 4 government results</t>
         </is>
       </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>gov.uk, netregs.org.uk (38), mandata.co.uk (27), biffa.co.uk (46), thefirstmile.co.uk (39)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr"/>
@@ -2504,6 +2799,11 @@
       <c r="I74" s="6" t="inlineStr">
         <is>
           <t>Same results as "weee waste". No competitor at AS 25 or below. Lowest is AS 34. Government and Wikipedia hold the results</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>gov.uk, reconomy.com (34), europa.eu, veolia.co.uk (48), businesswaste.co.uk (41)</t>
         </is>
       </c>
     </row>
@@ -2517,6 +2817,7 @@
       <c r="G75" s="7" t="n"/>
       <c r="H75" s="7" t="n"/>
       <c r="I75" s="7" t="n"/>
+      <c r="J75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2554,6 +2855,11 @@
       <c r="I76" s="6" t="inlineStr">
         <is>
           <t>No competitor at AS 25 or below. Lowest is AS 45. All results are government or charity</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>cuprecyclingscheme.co.uk (26), recyclenow.com (54), veolia.co.uk (48), keepscotlandbeautiful.org, walesrecycles.org.uk</t>
         </is>
       </c>
     </row>
@@ -2567,6 +2873,7 @@
       <c r="G77" s="7" t="n"/>
       <c r="H77" s="7" t="n"/>
       <c r="I77" s="7" t="n"/>
+      <c r="J77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2604,6 +2911,11 @@
       <c r="I78" s="6" t="inlineStr">
         <is>
           <t>Same results as "office waste management". 1 competitor ranks at AS 24. The page results are dated, half use http and one is a US agency</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>recycle-more.co.uk, wastecare.co.uk, wrap.org.uk, printwaste.co.uk (24), biffa.co.uk (46)</t>
         </is>
       </c>
     </row>
@@ -2633,6 +2945,11 @@
           <t>Same results as "office waste management". 1 competitor ranks at AS 24. The page results are dated, half use http and one is a US agency</t>
         </is>
       </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>recycle-more.co.uk, wastecare.co.uk, wrap.org.uk, printwaste.co.uk (24), biffa.co.uk (46)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr"/>
@@ -2658,6 +2975,11 @@
       <c r="I80" s="6" t="inlineStr">
         <is>
           <t>1 competitor ranks at AS 24. The page results are dated, half use http and one is a US agency</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>recycle-more.co.uk, wastecare.co.uk, wrap.org.uk, printwaste.co.uk (24), biffa.co.uk (46)</t>
         </is>
       </c>
     </row>
@@ -2671,6 +2993,7 @@
       <c r="G81" s="7" t="n"/>
       <c r="H81" s="7" t="n"/>
       <c r="I81" s="7" t="n"/>
+      <c r="J81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2708,6 +3031,11 @@
       <c r="I82" s="6" t="inlineStr">
         <is>
           <t>Same results as "butchers waste collection". 3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>jgpears.com (26), affordablewastemanagement.co.uk (28), wastemanaged.co.uk (37), wheeldonbrothers.co.uk (24), martlands.co.uk (10)</t>
         </is>
       </c>
     </row>
@@ -2737,6 +3065,11 @@
           <t>Same results as "butchers waste collection". 3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
         </is>
       </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>jgpears.com (26), affordablewastemanagement.co.uk (28), wastemanaged.co.uk (37), wheeldonbrothers.co.uk (24), martlands.co.uk (10)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr"/>
@@ -2762,6 +3095,11 @@
       <c r="I84" s="6" t="inlineStr">
         <is>
           <t>Same results as "butchers waste collection". 3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>jgpears.com (26), affordablewastemanagement.co.uk (28), wastemanaged.co.uk (37), wheeldonbrothers.co.uk (24), martlands.co.uk (10)</t>
         </is>
       </c>
     </row>
@@ -2775,6 +3113,7 @@
       <c r="G85" s="7" t="n"/>
       <c r="H85" s="7" t="n"/>
       <c r="I85" s="7" t="n"/>
+      <c r="J85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2812,6 +3151,11 @@
       <c r="I86" s="6" t="inlineStr">
         <is>
           <t>Same results as "office waste management". 1 competitor ranks at AS 24. The page results are dated, half use http and one is a US agency</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>recycle-more.co.uk, wastecare.co.uk, wrap.org.uk, printwaste.co.uk (24), biffa.co.uk (46)</t>
         </is>
       </c>
     </row>
@@ -2825,6 +3169,7 @@
       <c r="G87" s="7" t="n"/>
       <c r="H87" s="7" t="n"/>
       <c r="I87" s="7" t="n"/>
+      <c r="J87" s="7" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2862,6 +3207,11 @@
       <c r="I88" s="6" t="inlineStr">
         <is>
           <t>3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>jgpears.com (26), affordablewastemanagement.co.uk (28), wastemanaged.co.uk (37), wheeldonbrothers.co.uk (24), martlands.co.uk (10)</t>
         </is>
       </c>
     </row>
@@ -2875,6 +3225,7 @@
       <c r="G89" s="7" t="n"/>
       <c r="H89" s="7" t="n"/>
       <c r="I89" s="7" t="n"/>
+      <c r="J89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2912,6 +3263,11 @@
       <c r="I90" s="6" t="inlineStr">
         <is>
           <t>Same results as "butchers waste collection". 3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>jgpears.com (26), affordablewastemanagement.co.uk (28), wastemanaged.co.uk (37), wheeldonbrothers.co.uk (24), martlands.co.uk (10)</t>
         </is>
       </c>
     </row>
@@ -2939,6 +3295,11 @@
       <c r="I91" s="6" t="inlineStr">
         <is>
           <t>Same results as "butchers waste collection". 3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>jgpears.com (26), affordablewastemanagement.co.uk (28), wastemanaged.co.uk (37), wheeldonbrothers.co.uk (24), martlands.co.uk (10)</t>
         </is>
       </c>
     </row>
@@ -2952,6 +3313,7 @@
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="7" t="n"/>
       <c r="I92" s="7" t="n"/>
+      <c r="J92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2989,6 +3351,11 @@
       <c r="I93" s="6" t="inlineStr">
         <is>
           <t>Same results as "butchers waste collection". 3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>jgpears.com (26), affordablewastemanagement.co.uk (28), wastemanaged.co.uk (37), wheeldonbrothers.co.uk (24), martlands.co.uk (10)</t>
         </is>
       </c>
     </row>
@@ -3002,6 +3369,7 @@
       <c r="G94" s="7" t="n"/>
       <c r="H94" s="7" t="n"/>
       <c r="I94" s="7" t="n"/>
+      <c r="J94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -3039,6 +3407,11 @@
       <c r="I95" s="6" t="inlineStr">
         <is>
           <t>Same results as "butchers waste collection". 3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>jgpears.com (26), affordablewastemanagement.co.uk (28), wastemanaged.co.uk (37), wheeldonbrothers.co.uk (24), martlands.co.uk (10)</t>
         </is>
       </c>
     </row>
@@ -3052,6 +3425,7 @@
       <c r="G96" s="7" t="n"/>
       <c r="H96" s="7" t="n"/>
       <c r="I96" s="7" t="n"/>
+      <c r="J96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -3089,6 +3463,11 @@
       <c r="I97" s="6" t="inlineStr">
         <is>
           <t>Same results as "butchers waste collection". 3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>jgpears.com (26), affordablewastemanagement.co.uk (28), wastemanaged.co.uk (37), wheeldonbrothers.co.uk (24), martlands.co.uk (10)</t>
         </is>
       </c>
     </row>
@@ -3102,6 +3481,7 @@
       <c r="G98" s="7" t="n"/>
       <c r="H98" s="7" t="n"/>
       <c r="I98" s="7" t="n"/>
+      <c r="J98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -3139,6 +3519,11 @@
       <c r="I99" s="6" t="inlineStr">
         <is>
           <t>Same results as "butchers waste collection". 3 competitors rank at AS 25 or below: 10, 10, 24. 1 council result</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>jgpears.com (26), affordablewastemanagement.co.uk (28), wastemanaged.co.uk (37), wheeldonbrothers.co.uk (24), martlands.co.uk (10)</t>
         </is>
       </c>
     </row>
@@ -3152,6 +3537,7 @@
       <c r="G100" s="7" t="n"/>
       <c r="H100" s="7" t="n"/>
       <c r="I100" s="7" t="n"/>
+      <c r="J100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -3189,6 +3575,11 @@
       <c r="I101" s="6" t="inlineStr">
         <is>
           <t>2 competitors rank at AS 25 or below: 10 and 22. Stericycle and PHS hold two places</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>infectionpreventioncontrol.co.uk, stericycle.co.uk (32), wastemanaged.co.uk (37), busybins.co.uk (22), bwsl.co.uk (10)</t>
         </is>
       </c>
     </row>
@@ -3202,6 +3593,7 @@
       <c r="G102" s="7" t="n"/>
       <c r="H102" s="7" t="n"/>
       <c r="I102" s="7" t="n"/>
+      <c r="J102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -3239,6 +3631,11 @@
       <c r="I103" s="6" t="inlineStr">
         <is>
           <t>1 competitor ranks at AS 10. The results are mostly guides and trade press</t>
+        </is>
+      </c>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>bda.org, phs.co.uk (40), stericycle.co.uk (32), reconomy.com (34), wgswaste.co.uk (10)</t>
         </is>
       </c>
     </row>
@@ -3252,6 +3649,7 @@
       <c r="G104" s="7" t="n"/>
       <c r="H104" s="7" t="n"/>
       <c r="I104" s="7" t="n"/>
+      <c r="J104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -3289,6 +3687,11 @@
       <c r="I105" s="6" t="inlineStr">
         <is>
           <t>Same results as "care home waste management". 2 competitors rank at AS 25 or below: 10 and 22. Stericycle and PHS hold two places</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>infectionpreventioncontrol.co.uk, stericycle.co.uk (32), wastemanaged.co.uk (37), busybins.co.uk (22), bwsl.co.uk (10)</t>
         </is>
       </c>
     </row>
@@ -3302,6 +3705,7 @@
       <c r="G106" s="7" t="n"/>
       <c r="H106" s="7" t="n"/>
       <c r="I106" s="7" t="n"/>
+      <c r="J106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -3339,6 +3743,11 @@
       <c r="I107" s="6" t="inlineStr">
         <is>
           <t>2 competitors rank at AS 25 or below: 19 and 20. The results are mostly guides, not services</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>solgrid.org.uk, buyingforschools.blog.gov.uk, hills-waste.co.uk (26), aegissupportservices.com (20), unyfi.co.uk (19)</t>
         </is>
       </c>
     </row>
@@ -3352,6 +3761,7 @@
       <c r="G108" s="7" t="n"/>
       <c r="H108" s="7" t="n"/>
       <c r="I108" s="7" t="n"/>
+      <c r="J108" s="7" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -3389,6 +3799,11 @@
       <c r="I109" s="6" t="inlineStr">
         <is>
           <t>5 competitors rank at AS 25 or below: 13, 21, 21, 24, 25. 2 council results</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="inlineStr">
+        <is>
+          <t>leeds.gov.uk (59), sensawaste.com (24), businesswaste.co.uk (41), liliwaste.co.uk (21), lsswaste.co.uk (13)</t>
         </is>
       </c>
     </row>
@@ -3402,6 +3817,7 @@
       <c r="G110" s="7" t="n"/>
       <c r="H110" s="7" t="n"/>
       <c r="I110" s="7" t="n"/>
+      <c r="J110" s="7" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -3439,6 +3855,11 @@
       <c r="I111" s="6" t="inlineStr">
         <is>
           <t>Same results as "commercial waste collection leeds". 5 competitors rank at AS 25 or below: 13, 21, 21, 24, 25. 2 council results</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="inlineStr">
+        <is>
+          <t>leeds.gov.uk (59), sensawaste.com (24), businesswaste.co.uk (41), liliwaste.co.uk (21), lsswaste.co.uk (13)</t>
         </is>
       </c>
     </row>
@@ -3452,6 +3873,7 @@
       <c r="G112" s="7" t="n"/>
       <c r="H112" s="7" t="n"/>
       <c r="I112" s="7" t="n"/>
+      <c r="J112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -3489,6 +3911,11 @@
       <c r="I113" s="6" t="inlineStr">
         <is>
           <t>Same results as "commercial waste collection leeds". 5 competitors rank at AS 25 or below: 13, 21, 21, 24, 25. 2 council results</t>
+        </is>
+      </c>
+      <c r="J113" s="6" t="inlineStr">
+        <is>
+          <t>leeds.gov.uk (59), sensawaste.com (24), businesswaste.co.uk (41), liliwaste.co.uk (21), lsswaste.co.uk (13)</t>
         </is>
       </c>
     </row>
@@ -3502,6 +3929,7 @@
       <c r="G114" s="7" t="n"/>
       <c r="H114" s="7" t="n"/>
       <c r="I114" s="7" t="n"/>
+      <c r="J114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -3539,6 +3967,11 @@
       <c r="I115" s="6" t="inlineStr">
         <is>
           <t>Same results as "commercial waste collection leeds". 5 competitors rank at AS 25 or below: 13, 21, 21, 24, 25. 2 council results</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>leeds.gov.uk (59), sensawaste.com (24), businesswaste.co.uk (41), liliwaste.co.uk (21), lsswaste.co.uk (13)</t>
         </is>
       </c>
     </row>
@@ -3552,6 +3985,7 @@
       <c r="G116" s="7" t="n"/>
       <c r="H116" s="7" t="n"/>
       <c r="I116" s="7" t="n"/>
+      <c r="J116" s="7" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -3589,6 +4023,11 @@
       <c r="I117" s="6" t="inlineStr">
         <is>
           <t>Same results as "commercial waste collection leeds". 5 competitors rank at AS 25 or below: 13, 21, 21, 24, 25. 2 council results</t>
+        </is>
+      </c>
+      <c r="J117" s="6" t="inlineStr">
+        <is>
+          <t>leeds.gov.uk (59), sensawaste.com (24), businesswaste.co.uk (41), liliwaste.co.uk (21), lsswaste.co.uk (13)</t>
         </is>
       </c>
     </row>
@@ -3602,6 +4041,7 @@
       <c r="G118" s="7" t="n"/>
       <c r="H118" s="7" t="n"/>
       <c r="I118" s="7" t="n"/>
+      <c r="J118" s="7" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -3639,6 +4079,11 @@
       <c r="I119" s="6" t="inlineStr">
         <is>
           <t>Same results as "commercial waste collection leeds". 5 competitors rank at AS 25 or below: 13, 21, 21, 24, 25. 2 council results</t>
+        </is>
+      </c>
+      <c r="J119" s="6" t="inlineStr">
+        <is>
+          <t>leeds.gov.uk (59), sensawaste.com (24), businesswaste.co.uk (41), liliwaste.co.uk (21), lsswaste.co.uk (13)</t>
         </is>
       </c>
     </row>
@@ -3652,6 +4097,7 @@
       <c r="G120" s="7" t="n"/>
       <c r="H120" s="7" t="n"/>
       <c r="I120" s="7" t="n"/>
+      <c r="J120" s="7" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -3689,6 +4135,11 @@
       <c r="I121" s="6" t="inlineStr">
         <is>
           <t>Shares the city page results. Semrush holds no keyword data for this term, so treat the volume as indicative only</t>
+        </is>
+      </c>
+      <c r="J121" s="6" t="inlineStr">
+        <is>
+          <t>recycleforgreatermanchester.com (49), manchester.gov.uk, kennywastemanagement.co.uk (27), bandmwaste.com (29), fswaste.co.uk (30)</t>
         </is>
       </c>
     </row>
@@ -3718,6 +4169,11 @@
           <t>Shares the city page results. Semrush holds no keyword data for this term, so treat the volume as indicative only</t>
         </is>
       </c>
+      <c r="J122" s="6" t="inlineStr">
+        <is>
+          <t>recycleforgreatermanchester.com (49), manchester.gov.uk, kennywastemanagement.co.uk (27), bandmwaste.com (29), fswaste.co.uk (30)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr"/>
@@ -3745,6 +4201,11 @@
           <t>Shares the city page results. Semrush holds no keyword data for this term, so treat the volume as indicative only</t>
         </is>
       </c>
+      <c r="J123" s="6" t="inlineStr">
+        <is>
+          <t>recycleforgreatermanchester.com (49), manchester.gov.uk, kennywastemanagement.co.uk (27), bandmwaste.com (29), fswaste.co.uk (30)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr"/>
@@ -3770,6 +4231,11 @@
       <c r="I124" s="6" t="inlineStr">
         <is>
           <t>Shares the city page results. Semrush holds no keyword data for this term, so treat the volume as indicative only</t>
+        </is>
+      </c>
+      <c r="J124" s="6" t="inlineStr">
+        <is>
+          <t>recycleforgreatermanchester.com (49), manchester.gov.uk, kennywastemanagement.co.uk (27), bandmwaste.com (29), fswaste.co.uk (30)</t>
         </is>
       </c>
     </row>
@@ -3783,6 +4249,7 @@
       <c r="G125" s="7" t="n"/>
       <c r="H125" s="7" t="n"/>
       <c r="I125" s="7" t="n"/>
+      <c r="J125" s="7" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -3820,6 +4287,11 @@
       <c r="I126" s="6" t="inlineStr">
         <is>
           <t>Shares the city page results. Semrush holds no keyword data for this term, so treat the volume as indicative only</t>
+        </is>
+      </c>
+      <c r="J126" s="6" t="inlineStr">
+        <is>
+          <t>recycleforgreatermanchester.com (49), manchester.gov.uk, kennywastemanagement.co.uk (27), bandmwaste.com (29), fswaste.co.uk (30)</t>
         </is>
       </c>
     </row>
@@ -3847,6 +4319,11 @@
       <c r="I127" s="6" t="inlineStr">
         <is>
           <t>Shares the city page results. Semrush holds no keyword data for this term, so treat the volume as indicative only</t>
+        </is>
+      </c>
+      <c r="J127" s="6" t="inlineStr">
+        <is>
+          <t>recycleforgreatermanchester.com (49), manchester.gov.uk, kennywastemanagement.co.uk (27), bandmwaste.com (29), fswaste.co.uk (30)</t>
         </is>
       </c>
     </row>
@@ -3860,6 +4337,7 @@
       <c r="G128" s="7" t="n"/>
       <c r="H128" s="7" t="n"/>
       <c r="I128" s="7" t="n"/>
+      <c r="J128" s="7" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -3897,6 +4375,11 @@
       <c r="I129" s="6" t="inlineStr">
         <is>
           <t>Shares the city page results. Semrush holds no keyword data for this term, so treat the volume as indicative only</t>
+        </is>
+      </c>
+      <c r="J129" s="6" t="inlineStr">
+        <is>
+          <t>biffa.co.uk (46), lbhf.gov.uk, businesswaste.co.uk (41), greenlineenvironmental.co.uk (18), envirowastemanagement.com (25)</t>
         </is>
       </c>
     </row>
@@ -3924,6 +4407,11 @@
       <c r="I130" s="6" t="inlineStr">
         <is>
           <t>Same results as the London commercial waste page. 2 competitors rank at AS 25 or below: 18 and 25</t>
+        </is>
+      </c>
+      <c r="J130" s="6" t="inlineStr">
+        <is>
+          <t>biffa.co.uk (46), lbhf.gov.uk, businesswaste.co.uk (41), greenlineenvironmental.co.uk (18), envirowastemanagement.com (25)</t>
         </is>
       </c>
     </row>
@@ -3937,6 +4425,7 @@
       <c r="G131" s="7" t="n"/>
       <c r="H131" s="7" t="n"/>
       <c r="I131" s="7" t="n"/>
+      <c r="J131" s="7" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -3974,6 +4463,11 @@
       <c r="I132" s="6" t="inlineStr">
         <is>
           <t>Same results as the Manchester city page. Lowest competitor is AS 27. 2 council results</t>
+        </is>
+      </c>
+      <c r="J132" s="6" t="inlineStr">
+        <is>
+          <t>recycleforgreatermanchester.com (49), manchester.gov.uk, kennywastemanagement.co.uk (27), bandmwaste.com (29), fswaste.co.uk (30)</t>
         </is>
       </c>
     </row>
@@ -4001,6 +4495,11 @@
       <c r="I133" s="6" t="inlineStr">
         <is>
           <t>Same results as the Manchester city page. Lowest competitor is AS 27. 2 council results</t>
+        </is>
+      </c>
+      <c r="J133" s="6" t="inlineStr">
+        <is>
+          <t>recycleforgreatermanchester.com (49), manchester.gov.uk, kennywastemanagement.co.uk (27), bandmwaste.com (29), fswaste.co.uk (30)</t>
         </is>
       </c>
     </row>
@@ -4014,6 +4513,7 @@
       <c r="G134" s="7" t="n"/>
       <c r="H134" s="7" t="n"/>
       <c r="I134" s="7" t="n"/>
+      <c r="J134" s="7" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -4051,6 +4551,11 @@
       <c r="I135" s="6" t="inlineStr">
         <is>
           <t>1 competitor ranks at AS 24. Biffa at AS 46 holds third. 2 council results</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="inlineStr">
+        <is>
+          <t>sheffield.gov.uk, sensawaste.com (24), biffa.co.uk (46), sommerswastesolutions.com (11), direct365.co.uk (32)</t>
         </is>
       </c>
     </row>
@@ -4064,6 +4569,7 @@
       <c r="G136" s="7" t="n"/>
       <c r="H136" s="7" t="n"/>
       <c r="I136" s="7" t="n"/>
+      <c r="J136" s="7" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -4101,6 +4607,11 @@
       <c r="I137" s="6" t="inlineStr">
         <is>
           <t>Same results as "1100l bin". 3 competitors rank at AS 25 or below: 12, 13, 22. The matching page already exists</t>
+        </is>
+      </c>
+      <c r="J137" s="6" t="inlineStr">
+        <is>
+          <t>wheeliebinwarehouse.com (13), wheeliebinsolutions.co.uk (33), businesswaste.co.uk (41), sgmwastemanagement.co.uk (12), bins.co.uk (22)</t>
         </is>
       </c>
     </row>
@@ -4128,6 +4639,11 @@
       <c r="I138" s="6" t="inlineStr">
         <is>
           <t>3 competitors rank at AS 25 or below: 12, 13, 22. The matching page already exists</t>
+        </is>
+      </c>
+      <c r="J138" s="6" t="inlineStr">
+        <is>
+          <t>wheeliebinwarehouse.com (13), wheeliebinsolutions.co.uk (33), businesswaste.co.uk (41), sgmwastemanagement.co.uk (12), bins.co.uk (22)</t>
         </is>
       </c>
     </row>
@@ -4141,6 +4657,7 @@
       <c r="G139" s="7" t="n"/>
       <c r="H139" s="7" t="n"/>
       <c r="I139" s="7" t="n"/>
+      <c r="J139" s="7" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -4178,6 +4695,11 @@
       <c r="I140" s="6" t="inlineStr">
         <is>
           <t>Same results as "1100l bin". 3 competitors rank at AS 25 or below: 12, 13, 22. The matching page already exists</t>
+        </is>
+      </c>
+      <c r="J140" s="6" t="inlineStr">
+        <is>
+          <t>wheeliebinwarehouse.com (13), wheeliebinsolutions.co.uk (33), businesswaste.co.uk (41), sgmwastemanagement.co.uk (12), bins.co.uk (22)</t>
         </is>
       </c>
     </row>
@@ -4205,6 +4727,11 @@
       <c r="I141" s="6" t="inlineStr">
         <is>
           <t>Same results as "1100l bin". 3 competitors rank at AS 25 or below: 12, 13, 22. The matching page already exists</t>
+        </is>
+      </c>
+      <c r="J141" s="6" t="inlineStr">
+        <is>
+          <t>wheeliebinwarehouse.com (13), wheeliebinsolutions.co.uk (33), businesswaste.co.uk (41), sgmwastemanagement.co.uk (12), bins.co.uk (22)</t>
         </is>
       </c>
     </row>
@@ -4218,6 +4745,7 @@
       <c r="G142" s="7" t="n"/>
       <c r="H142" s="7" t="n"/>
       <c r="I142" s="7" t="n"/>
+      <c r="J142" s="7" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -4255,6 +4783,11 @@
       <c r="I143" s="6" t="inlineStr">
         <is>
           <t>Same results as "1100l bin". 3 competitors rank at AS 25 or below: 12, 13, 22. The matching page already exists</t>
+        </is>
+      </c>
+      <c r="J143" s="6" t="inlineStr">
+        <is>
+          <t>wheeliebinwarehouse.com (13), wheeliebinsolutions.co.uk (33), businesswaste.co.uk (41), sgmwastemanagement.co.uk (12), bins.co.uk (22)</t>
         </is>
       </c>
     </row>
@@ -4284,6 +4817,11 @@
           <t>Same results as "commercial bin sizes". 1 competitor ranks at AS 22. Two more sit just above at AS 26 and 29. 3 council results</t>
         </is>
       </c>
+      <c r="J144" s="6" t="inlineStr">
+        <is>
+          <t>businesswaste.co.uk (41), braintree.gov.uk, gwrwastemanagement.co.uk (22), wheeliebinsolutions.co.uk (33), ashwasteservices.co.uk (26)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr"/>
@@ -4309,6 +4847,11 @@
       <c r="I145" s="6" t="inlineStr">
         <is>
           <t>Same results as "commercial bin sizes". 1 competitor ranks at AS 22. Two more sit just above at AS 26 and 29. 3 council results</t>
+        </is>
+      </c>
+      <c r="J145" s="6" t="inlineStr">
+        <is>
+          <t>businesswaste.co.uk (41), braintree.gov.uk, gwrwastemanagement.co.uk (22), wheeliebinsolutions.co.uk (33), ashwasteservices.co.uk (26)</t>
         </is>
       </c>
     </row>
@@ -4322,6 +4865,7 @@
       <c r="G146" s="7" t="n"/>
       <c r="H146" s="7" t="n"/>
       <c r="I146" s="7" t="n"/>
+      <c r="J146" s="7" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -4359,6 +4903,11 @@
       <c r="I147" s="6" t="inlineStr">
         <is>
           <t>Same results as "1100l bin". 3 competitors rank at AS 25 or below: 12, 13, 22. The matching page already exists</t>
+        </is>
+      </c>
+      <c r="J147" s="6" t="inlineStr">
+        <is>
+          <t>wheeliebinwarehouse.com (13), wheeliebinsolutions.co.uk (33), businesswaste.co.uk (41), sgmwastemanagement.co.uk (12), bins.co.uk (22)</t>
         </is>
       </c>
     </row>
@@ -4372,6 +4921,7 @@
       <c r="G148" s="7" t="n"/>
       <c r="H148" s="7" t="n"/>
       <c r="I148" s="7" t="n"/>
+      <c r="J148" s="7" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -4409,6 +4959,11 @@
       <c r="I149" s="6" t="inlineStr">
         <is>
           <t>Same results as "1100l bin". 3 competitors rank at AS 25 or below: 12, 13, 22. The matching page already exists</t>
+        </is>
+      </c>
+      <c r="J149" s="6" t="inlineStr">
+        <is>
+          <t>wheeliebinwarehouse.com (13), wheeliebinsolutions.co.uk (33), businesswaste.co.uk (41), sgmwastemanagement.co.uk (12), bins.co.uk (22)</t>
         </is>
       </c>
     </row>
@@ -4422,6 +4977,7 @@
       <c r="G150" s="7" t="n"/>
       <c r="H150" s="7" t="n"/>
       <c r="I150" s="7" t="n"/>
+      <c r="J150" s="7" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -4459,6 +5015,11 @@
       <c r="I151" s="6" t="inlineStr">
         <is>
           <t>1 competitor ranks at AS 15. 2 council results and three places held by Reddit, Facebook and YouTube</t>
+        </is>
+      </c>
+      <c r="J151" s="6" t="inlineStr">
+        <is>
+          <t>mhs.org.uk (31), express.co.uk, westsuffolk.gov.uk, lbcclean.co.uk (15), businesswaste.co.uk (41)</t>
         </is>
       </c>
     </row>
@@ -4488,6 +5049,11 @@
           <t>Same results as "maggots wheelie bins hot weather". 1 competitor ranks at AS 15. 2 council results and three places held by Reddit, Facebook and YouTube</t>
         </is>
       </c>
+      <c r="J152" s="6" t="inlineStr">
+        <is>
+          <t>mhs.org.uk (31), express.co.uk, westsuffolk.gov.uk, lbcclean.co.uk (15), businesswaste.co.uk (41)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr"/>
@@ -4515,6 +5081,11 @@
           <t>Same results as "maggots wheelie bins hot weather". 1 competitor ranks at AS 15. 2 council results and three places held by Reddit, Facebook and YouTube</t>
         </is>
       </c>
+      <c r="J153" s="6" t="inlineStr">
+        <is>
+          <t>mhs.org.uk (31), express.co.uk, westsuffolk.gov.uk, lbcclean.co.uk (15), businesswaste.co.uk (41)</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr"/>
@@ -4542,6 +5113,11 @@
           <t>Same results as "maggots wheelie bins hot weather". 1 competitor ranks at AS 15. 2 council results and three places held by Reddit, Facebook and YouTube</t>
         </is>
       </c>
+      <c r="J154" s="6" t="inlineStr">
+        <is>
+          <t>mhs.org.uk (31), express.co.uk, westsuffolk.gov.uk, lbcclean.co.uk (15), businesswaste.co.uk (41)</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr"/>
@@ -4567,6 +5143,11 @@
       <c r="I155" s="6" t="inlineStr">
         <is>
           <t>Same results as "maggots wheelie bins hot weather". 1 competitor ranks at AS 15. 2 council results and three places held by Reddit, Facebook and YouTube</t>
+        </is>
+      </c>
+      <c r="J155" s="6" t="inlineStr">
+        <is>
+          <t>mhs.org.uk (31), express.co.uk, westsuffolk.gov.uk, lbcclean.co.uk (15), businesswaste.co.uk (41)</t>
         </is>
       </c>
     </row>
@@ -4580,6 +5161,7 @@
       <c r="G156" s="7" t="n"/>
       <c r="H156" s="7" t="n"/>
       <c r="I156" s="7" t="n"/>
+      <c r="J156" s="7" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -4617,6 +5199,11 @@
       <c r="I157" s="6" t="inlineStr">
         <is>
           <t>1 competitor ranks at AS 22. Two more sit just above at AS 26 and 29. 3 council results</t>
+        </is>
+      </c>
+      <c r="J157" s="6" t="inlineStr">
+        <is>
+          <t>businesswaste.co.uk (41), braintree.gov.uk, gwrwastemanagement.co.uk (22), wheeliebinsolutions.co.uk (33), ashwasteservices.co.uk (26)</t>
         </is>
       </c>
     </row>
@@ -4630,6 +5217,7 @@
       <c r="G158" s="7" t="n"/>
       <c r="H158" s="7" t="n"/>
       <c r="I158" s="7" t="n"/>
+      <c r="J158" s="7" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -4667,6 +5255,11 @@
       <c r="I159" s="6" t="inlineStr">
         <is>
           <t>No competitor at AS 25 or below. 4 government results plus BBC and Guardian</t>
+        </is>
+      </c>
+      <c r="J159" s="6" t="inlineStr">
+        <is>
+          <t>gov.uk, arun.gov.uk, wheeliebinsolutions.co.uk (33), bbc.co.uk, durham.gov.uk</t>
         </is>
       </c>
     </row>
@@ -4696,6 +5289,11 @@
           <t>Same results as "england bin collection rules 2026". No competitor at AS 25 or below. 4 government results plus BBC and Guardian</t>
         </is>
       </c>
+      <c r="J160" s="6" t="inlineStr">
+        <is>
+          <t>gov.uk, arun.gov.uk, wheeliebinsolutions.co.uk (33), bbc.co.uk, durham.gov.uk</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr"/>
@@ -4723,6 +5321,11 @@
           <t>Same results as "england bin collection rules 2026". No competitor at AS 25 or below. 4 government results plus BBC and Guardian</t>
         </is>
       </c>
+      <c r="J161" s="6" t="inlineStr">
+        <is>
+          <t>gov.uk, arun.gov.uk, wheeliebinsolutions.co.uk (33), bbc.co.uk, durham.gov.uk</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr"/>
@@ -4750,6 +5353,11 @@
           <t>Same results as "england bin collection rules 2026". No competitor at AS 25 or below. 4 government results plus BBC and Guardian</t>
         </is>
       </c>
+      <c r="J162" s="6" t="inlineStr">
+        <is>
+          <t>gov.uk, arun.gov.uk, wheeliebinsolutions.co.uk (33), bbc.co.uk, durham.gov.uk</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr"/>
@@ -4777,6 +5385,11 @@
           <t>No competitor at AS 25 or below. Lowest is AS 41. 4 government results. Top 3 is out of reach but p8 to p10 is realistic</t>
         </is>
       </c>
+      <c r="J163" s="6" t="inlineStr">
+        <is>
+          <t>gov.uk, veolia.co.uk (48), biffa.co.uk (46), recyclenow.com (54), businesswaste.co.uk (41)</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr"/>
@@ -4804,6 +5417,11 @@
           <t>Same results as "england bin collection rules 2026". No competitor at AS 25 or below. 4 government results plus BBC and Guardian</t>
         </is>
       </c>
+      <c r="J164" s="6" t="inlineStr">
+        <is>
+          <t>gov.uk, arun.gov.uk, wheeliebinsolutions.co.uk (33), bbc.co.uk, durham.gov.uk</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr"/>
@@ -4829,6 +5447,11 @@
       <c r="I165" s="6" t="inlineStr">
         <is>
           <t>Same results as "simpler recycling". No competitor at AS 25 or below. Lowest is AS 41. 4 government results. Top 3 is out of reach but p8 to p10 is realistic</t>
+        </is>
+      </c>
+      <c r="J165" s="6" t="inlineStr">
+        <is>
+          <t>gov.uk, veolia.co.uk (48), biffa.co.uk (46), recyclenow.com (54), businesswaste.co.uk (41)</t>
         </is>
       </c>
     </row>
@@ -4842,6 +5465,7 @@
       <c r="G166" s="7" t="n"/>
       <c r="H166" s="7" t="n"/>
       <c r="I166" s="7" t="n"/>
+      <c r="J166" s="7" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -4879,6 +5503,11 @@
       <c r="I167" s="6" t="inlineStr">
         <is>
           <t>Same results as "waste transfer note". No competitor at AS 25 or below. Lowest is AS 45. 4 government results</t>
+        </is>
+      </c>
+      <c r="J167" s="6" t="inlineStr">
+        <is>
+          <t>gov.uk, netregs.org.uk (38), mandata.co.uk (27), biffa.co.uk (46), thefirstmile.co.uk (39)</t>
         </is>
       </c>
     </row>
@@ -4906,6 +5535,11 @@
       <c r="I168" s="6" t="inlineStr">
         <is>
           <t>Same results as "waste transfer note". No competitor at AS 25 or below. Lowest is AS 45. 4 government results</t>
+        </is>
+      </c>
+      <c r="J168" s="6" t="inlineStr">
+        <is>
+          <t>gov.uk, netregs.org.uk (38), mandata.co.uk (27), biffa.co.uk (46), thefirstmile.co.uk (39)</t>
         </is>
       </c>
     </row>
@@ -4919,6 +5553,7 @@
       <c r="G169" s="7" t="n"/>
       <c r="H169" s="7" t="n"/>
       <c r="I169" s="7" t="n"/>
+      <c r="J169" s="7" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -4956,6 +5591,11 @@
       <c r="I170" s="6" t="inlineStr">
         <is>
           <t>No competitor at AS 25 or below. 6 results are government registers</t>
+        </is>
+      </c>
+      <c r="J170" s="6" t="inlineStr">
+        <is>
+          <t>environment.data.gov.uk, gov.uk, naturalresources.wales, sepa.org.uk, businesswaste.co.uk (41)</t>
         </is>
       </c>
     </row>
@@ -4969,6 +5609,7 @@
       <c r="G171" s="7" t="n"/>
       <c r="H171" s="7" t="n"/>
       <c r="I171" s="7" t="n"/>
+      <c r="J171" s="7" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -5006,6 +5647,11 @@
       <c r="I172" s="6" t="inlineStr">
         <is>
           <t>Same results as "waste carriers licence". No competitor at AS 25 or below. 6 results are government registers</t>
+        </is>
+      </c>
+      <c r="J172" s="6" t="inlineStr">
+        <is>
+          <t>environment.data.gov.uk, gov.uk, naturalresources.wales, sepa.org.uk, businesswaste.co.uk (41)</t>
         </is>
       </c>
     </row>
@@ -5033,6 +5679,11 @@
       <c r="I173" s="6" t="inlineStr">
         <is>
           <t>Same results as "waste carriers licence". No competitor at AS 25 or below. 6 results are government registers</t>
+        </is>
+      </c>
+      <c r="J173" s="6" t="inlineStr">
+        <is>
+          <t>environment.data.gov.uk, gov.uk, naturalresources.wales, sepa.org.uk, businesswaste.co.uk (41)</t>
         </is>
       </c>
     </row>
@@ -5046,6 +5697,7 @@
       <c r="G174" s="7" t="n"/>
       <c r="H174" s="7" t="n"/>
       <c r="I174" s="7" t="n"/>
+      <c r="J174" s="7" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -5083,6 +5735,11 @@
       <c r="I175" s="6" t="inlineStr">
         <is>
           <t>No competitor at AS 25 or below. Lowest is AS 45. 4 government results</t>
+        </is>
+      </c>
+      <c r="J175" s="6" t="inlineStr">
+        <is>
+          <t>gov.uk, netregs.org.uk (38), mandata.co.uk (27), biffa.co.uk (46), thefirstmile.co.uk (39)</t>
         </is>
       </c>
     </row>
@@ -5112,6 +5769,11 @@
           <t>Same results as "waste transfer note". No competitor at AS 25 or below. Lowest is AS 45. 4 government results</t>
         </is>
       </c>
+      <c r="J176" s="6" t="inlineStr">
+        <is>
+          <t>gov.uk, netregs.org.uk (38), mandata.co.uk (27), biffa.co.uk (46), thefirstmile.co.uk (39)</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr"/>
@@ -5137,6 +5799,11 @@
       <c r="I177" s="6" t="inlineStr">
         <is>
           <t>Same results as "waste transfer note". No competitor at AS 25 or below. Lowest is AS 45. 4 government results</t>
+        </is>
+      </c>
+      <c r="J177" s="6" t="inlineStr">
+        <is>
+          <t>gov.uk, netregs.org.uk (38), mandata.co.uk (27), biffa.co.uk (46), thefirstmile.co.uk (39)</t>
         </is>
       </c>
     </row>
@@ -5150,9 +5817,10 @@
       <c r="G178" s="7" t="n"/>
       <c r="H178" s="7" t="n"/>
       <c r="I178" s="7" t="n"/>
+      <c r="J178" s="7" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I178"/>
+  <autoFilter ref="A1:J178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5163,739 +5831,232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="86" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>Issue</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>Why not</t>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>What to do</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>bulky waste collection</t>
-        </is>
-      </c>
-      <c r="B2" s="12" t="n">
-        <v>9900</v>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>Council collection intent</t>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Your Manchester, London and Birmingham rankings sit on URLs that look retired. /areas-we-cover-old/manchester/ returns 200 and ranks p11 to p22 for the whole Manchester cluster. /areas-we-cover/manchester/ returns a redirect and ranks for nothing. Same for London and Birmingham.</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Around 3,000 SV of city traffic is attached to URLs nobody is maintaining or linking to. Any work on the intended pages will not connect to it.</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Check where the three redirects point. If they point at the older URLs, rename those as canonical and keep the rankings. If they point anywhere else, fix the redirect. Do not simply redirect old to new, it may create a loop.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>clinical waste disposal</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="n">
-        <v>2900</v>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Household intent - 6 council results</t>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>The Simpler Recycling page ranks p14 for simpler recycling at 1,000 SV and KD 22.</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>It is one position band away from page one on an existing page. Nothing else on the site is this close for this little work.</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Refresh the content and add internal links from related pages. Target p8 to p10.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>weee recycling</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="n">
-        <v>2400</v>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Consumer scheme at #1, Amazon at #6</t>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>The site answers on both www and non www. betterwaste.co.uk/polystyrene-and-recycling/ and www.betterwaste.co.uk/polystyrene-and-recycling both rank as separate pages.</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Every page is competing with a copy of itself. Links and ranking signals are split in half across two versions of the site.</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Pick one hostname. Add a site wide redirect, set the canonical tag and set the preferred property in Search Console.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>clinical waste collection</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="n">
-        <v>1900</v>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Household intent - 6 council results</t>
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Four live pages chase the same commercial terms: /commercial-waste-collection/, /commercial-waste-management/, /business-waste-collections/ and /trade-waste-collections/. On top of that the /areas-we-cover/ hub ranks for national terms like business refuse collection at p5.</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>business waste collection at 2,400 SV ranks twice, p26 and p34, and neither gets near the top 20. Five pages are sharing the authority that one page needs.</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Make /commercial-waste-collection/ the single commercial page. Redirect or de optimise the other three and remove the national terms from the areas hub.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>hazardous waste disposal</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="n">
-        <v>1900</v>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>Household hazardous waste</t>
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Your strongest page is a blog post listing competitors. /top-10-commercial-waste-management-companies-in-the-uk/ ranks p4 to p8 for around 20 head terms and links nowhere useful. It also outranks your own service page for commercial waste management companies, p7 against p90.</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>It is the best ranking asset on the site, it sends in market visitors to read about competitors, and it passes none of its authority to a page that converts.</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Add prominent internal links from it to /commercial-waste-collection/ and reframe it so the service page wins the commercial terms.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>clinical waste</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="n">
-        <v>1600</v>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Household intent</t>
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Pages load on both the slash and non slash URL, and six keywords return two of your own URLs at once. Examples: /about and /about/, business waste birmingham at p19 and p26, waste management companies london at p29 and p32.</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Same problem as the www issue but smaller. It dilutes signals on individual pages rather than the whole site.</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Pick one trailing slash convention and redirect the other. Find the duplicate page behind each doubled keyword and consolidate.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>waste container</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="n">
-        <v>1600</v>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>Retail intent - bin shops</t>
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Test and leftover pages are indexable: /222-2/, /test-2/, /home/, /thank-you/, /trial-form/, /quote2-old/ and two other old quote forms. /quote2/ also has six indexable parameter versions.</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Low impact on its own, but it is wasted crawl budget and these pages say nothing good about site quality.</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Noindex or delete them and add parameter handling for the quote form.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>hazardous waste collection</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Household hazardous waste</t>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Two live pages cover the same service: /clinical-waste-disposal-clinical-waste-collection-companies/ and /healthcare-waste/.</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Low priority because the clinical head terms are council dominated and not winnable anyway. Worth tidying when you next touch that area.</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Merge into one page and point it at commercial terms such as dental waste disposal and sharps bin collection.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>green waste collection</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="n">
-        <v>1300</v>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>Residential garden waste</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>medical waste collection</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n">
-        <v>880</v>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Household sharps - 7 council results</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>1100 litre bin</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n">
-        <v>720</v>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Retail intent - bin shops</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>660 litre bin</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n">
-        <v>720</v>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>Retail intent - bin shops</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>electrical waste disposal</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n">
-        <v>590</v>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>6 council and national-scheme results</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>240 litre bin</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n">
-        <v>590</v>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Retail intent - bin shops</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>clinical waste removal</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>590</v>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Household intent</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>commercial wheelie bin</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n">
-        <v>320</v>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Retail intent - bin shops</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>wheelie bin hire</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="n">
-        <v>320</v>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Retail intent - bin shops</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>eurobin</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="n">
-        <v>260</v>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Retail intent - bin shops</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>1100 litre bin dimensions</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Retail intent - bin shops</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>What is wrong</t>
-        </is>
-      </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>What to do</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Redirects</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>The Manchester, London and Birmingham city URLs redirect while their older equivalents are the live pages</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>/areas-we-cover-old/manchester/, /london/ and /birmingham/ all return 200. /areas-we-cover/manchester/, /london/ and /birmingham/ all return 301. Google ranks the older URLs because they are the only ones resolving</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>Check where the three redirects point before changing anything. If they point at the older URLs, rename those as canonical. If they point elsewhere, the redirect is the bug. Do not redirect old to new without checking, it may create a loop</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Duplicate pages</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>Four live pages target the same commercial head terms</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>/commercial-waste-collection/, /commercial-waste-management/, /business-waste-collections/ and /trade-waste-collections/ all return 200 and all target commercial waste terms. business waste collection at 2,400 SV ranks twice, p26 and p34, and neither reaches the top 20</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>Choose /commercial-waste-collection/ as the single money page. Redirect or de optimise the other three</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Canonical</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>The site resolves on both www and non www</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Both betterwaste.co.uk/polystyrene-and-recycling/ and www.betterwaste.co.uk/polystyrene-and-recycling rank as separate URLs. Same for /business-waste-collections</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Pick one hostname. Add a site wide 301, set the canonical tag, and set the preferred property in Search Console</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Quick win</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>The Simpler Recycling page sits just outside the top 10</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>simpler recycling at 1,000 SV and KD 22 ranks p14 on /simpler-recycling-legislation-for-businesses-in-england-what-you-need-to-know/</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Refresh the content and add internal links. This is the cheapest ranking gain available on the site</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Keyword mapping</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Glass keywords are mapped to the food waste page</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>In the current tracker the glass terms sit inside the /food-waste/ block. A live /glass-waste/ page already ranks p30 to p38 for them</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Move all glass terms onto /glass-waste/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Wrong page ranking</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>The areas hub ranks for national service terms it should not own</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>/areas-we-cover/ ranks for business refuse collection p5 at 590 SV, waste collection for business p59, commercial waste services p54, industrial waste collection p83 and waste disposal companies p63</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Optimise the existing /commercial-waste-collection/ page for these terms and remove them from the areas hub</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Internal linking</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>The strongest page on the site passes no value to the commercial pages</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>/top-10-commercial-waste-management-companies-in-the-uk/ ranks p4 to p8 for around 20 head terms. It is a listicle naming competitors and links nowhere useful</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Add prominent internal links from it to /commercial-waste-collection/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Duplicate pages</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>A blog post outranks the service page for a commercial term</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>commercial waste management companies ranks p7 with the blog listicle and p90 with /business-waste-collections/</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Separate the two by intent and link the blog to the service page</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Duplicate pages</t>
+          <t>Four former pages now return 404: /better-waste-solutions-birmingham/, /better-waste-solutions-london/, /better-waste-solutions-manchester/ and /business-waste-management-yorkshire/.</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Two live pages cover clinical and healthcare waste</t>
+          <t>If anyone links to these the value is being thrown away. If nobody does, there is nothing to fix.</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>/clinical-waste-disposal-clinical-waste-collection-companies/ and /healthcare-waste/ both return 200</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Merge into one page. Target commercial terms such as dental waste disposal and sharps bin collection rather than the household head terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Duplicate URLs</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Six keywords return two of your own URLs in the same results</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>business waste birmingham p19 and p26, commercial waste clearance birmingham p40 and p41, waste management companies london p29 and p32, zero waste to landfill p54 and p60, aluminium recycling p18 and p24, expanded polystyrene recycling p65 and p66</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Find the duplicate or paginated variants behind each and consolidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Duplicate URLs</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Pages load on both the slash and non slash URL</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>/about and /about/, /binpedia and /binpedia/, /contact-us and /contact-us/, /blog and /blog/, /faqs and /faqs/, /how-to-be-green and /how-to-be-green/</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Pick one convention and redirect the other site wide</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Index bloat</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Test and duplicate pages are indexable</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>/222-2/, /test-2/, /home/, /thank-you/, /thank-you-2/, /trial-form/, /quote2-old/, /quote-commercial-waste-old/ and /quote-waste-services-old/ all return 200. /quote2/ also has six indexable parameter variants</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Noindex or remove them and add parameter handling for the quote form</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Lost pages</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Four former pages now return 404 and may still hold links</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>/better-waste-solutions-birmingham/, /better-waste-solutions-london/, /better-waste-solutions-manchester/ and /business-waste-management-yorkshire/</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Check referring domains for each. Redirect any that hold links to the matching city or service page</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Data hygiene</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Volumes in the current tracker are out of date</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>dry mixed recycling bins is listed at 320, Semrush shows 720. commercial cardboard waste is listed at 110, Semrush shows 320. commercial food waste disposal is listed at 210, Semrush shows 480</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Refresh every volume in the tracker from Semrush UK</t>
+          <t>Check referring domains for each. Redirect only the ones that actually hold links.</t>
         </is>
       </c>
     </row>

--- a/betterwaste-kw-audit/Better_Waste_Keyword_Plan.xlsx
+++ b/betterwaste-kw-audit/Better_Waste_Keyword_Plan.xlsx
@@ -5831,7 +5831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5870,17 +5870,17 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Your Manchester, London and Birmingham rankings sit on URLs that look retired. /areas-we-cover-old/manchester/ returns 200 and ranks p11 to p22 for the whole Manchester cluster. /areas-we-cover/manchester/ returns a redirect and ranks for nothing. Same for London and Birmingham.</t>
+          <t>Manchester rankings sit entirely on a URL that looks retired. Semrush shows 16 keywords worth 5,080 SV on /areas-we-cover-old/manchester/, 9 of them in the top 20 and the best at p11. The intended page /areas-we-cover/manchester/ has zero keywords in Semrush. London and Birmingham are not affected, their current URLs rank normally.</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Around 3,000 SV of city traffic is attached to URLs nobody is maintaining or linking to. Any work on the intended pages will not connect to it.</t>
+          <t>All of your Manchester visibility, including commercial waste collection manchester at p20, is attached to a URL nobody is maintaining or linking to. Any work on the intended page will not connect to it.</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Check where the three redirects point. If they point at the older URLs, rename those as canonical and keep the rankings. If they point anywhere else, fix the redirect. Do not simply redirect old to new, it may create a loop.</t>
+          <t>Check where /areas-we-cover/manchester/ redirects to. If it points at the older URL, rename that one as canonical and keep the rankings. If it points elsewhere, the redirect is the bug. Do not redirect old to new without checking, it may create a loop.</t>
         </is>
       </c>
     </row>
@@ -5936,17 +5936,17 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Four live pages chase the same commercial terms: /commercial-waste-collection/, /commercial-waste-management/, /business-waste-collections/ and /trade-waste-collections/. On top of that the /areas-we-cover/ hub ranks for national terms like business refuse collection at p5.</t>
+          <t>The London and Birmingham city URLs were recorded as redirecting when Ahrefs last crawled the site on 28 and 29 July 2026, yet both rank normally in Semrush today. /areas-we-cover-old/london/ and /areas-we-cover-old/birmingham/ still return 200 with live page titles.</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>business waste collection at 2,400 SV ranks twice, p26 and p34, and neither gets near the top 20. Five pages are sharing the authority that one page needs.</t>
+          <t>Nothing is broken in the rankings, so this is not urgent. But two live copies of each city page is the same duplication problem as the www issue, and the crawl data is two months old so the current state is unconfirmed.</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Make /commercial-waste-collection/ the single commercial page. Redirect or de optimise the other three and remove the national terms from the areas hub.</t>
+          <t>Open both current city URLs and both older ones in a browser. If the older pages still load, redirect them to the current ones.</t>
         </is>
       </c>
     </row>
@@ -5958,39 +5958,39 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Your strongest page is a blog post listing competitors. /top-10-commercial-waste-management-companies-in-the-uk/ ranks p4 to p8 for around 20 head terms and links nowhere useful. It also outranks your own service page for commercial waste management companies, p7 against p90.</t>
+          <t>Four live pages chase the same commercial terms: /commercial-waste-collection/, /commercial-waste-management/, /business-waste-collections/ and /trade-waste-collections/. On top of that the /areas-we-cover/ hub ranks for national terms like business refuse collection at p5.</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>It is the best ranking asset on the site, it sends in market visitors to read about competitors, and it passes none of its authority to a page that converts.</t>
+          <t>business waste collection at 2,400 SV ranks twice, p26 and p34, and neither gets near the top 20. Five pages are sharing the authority that one page needs.</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Add prominent internal links from it to /commercial-waste-collection/ and reframe it so the service page wins the commercial terms.</t>
+          <t>Make /commercial-waste-collection/ the single commercial page. Redirect or de optimise the other three and remove the national terms from the areas hub.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Pages load on both the slash and non slash URL, and six keywords return two of your own URLs at once. Examples: /about and /about/, business waste birmingham at p19 and p26, waste management companies london at p29 and p32.</t>
+          <t>Your strongest page is a blog post listing competitors. /top-10-commercial-waste-management-companies-in-the-uk/ ranks p4 to p8 for around 20 head terms and links nowhere useful. It also outranks your own service page for commercial waste management companies, p7 against p90.</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Same problem as the www issue but smaller. It dilutes signals on individual pages rather than the whole site.</t>
+          <t>It is the best ranking asset on the site, it sends in market visitors to read about competitors, and it passes none of its authority to a page that converts.</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Pick one trailing slash convention and redirect the other. Find the duplicate page behind each doubled keyword and consolidate.</t>
+          <t>Add prominent internal links from it to /commercial-waste-collection/ and reframe it so the service page wins the commercial terms.</t>
         </is>
       </c>
     </row>
@@ -6002,17 +6002,17 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Test and leftover pages are indexable: /222-2/, /test-2/, /home/, /thank-you/, /trial-form/, /quote2-old/ and two other old quote forms. /quote2/ also has six indexable parameter versions.</t>
+          <t>Pages load on both the slash and non slash URL, and six keywords return two of your own URLs at once. Examples: /about and /about/, business waste birmingham at p19 and p26, waste management companies london at p29 and p32.</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Low impact on its own, but it is wasted crawl budget and these pages say nothing good about site quality.</t>
+          <t>Same problem as the www issue but smaller. It dilutes signals on individual pages rather than the whole site.</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Noindex or delete them and add parameter handling for the quote form.</t>
+          <t>Pick one trailing slash convention and redirect the other. Find the duplicate page behind each doubled keyword and consolidate.</t>
         </is>
       </c>
     </row>
@@ -6024,17 +6024,17 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Two live pages cover the same service: /clinical-waste-disposal-clinical-waste-collection-companies/ and /healthcare-waste/.</t>
+          <t>Test and leftover pages are indexable: /222-2/, /test-2/, /home/, /thank-you/, /trial-form/, /quote2-old/ and two other old quote forms. /quote2/ also has six indexable parameter versions.</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Low priority because the clinical head terms are council dominated and not winnable anyway. Worth tidying when you next touch that area.</t>
+          <t>Low impact on its own, but it is wasted crawl budget and these pages say nothing good about site quality.</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Merge into one page and point it at commercial terms such as dental waste disposal and sharps bin collection.</t>
+          <t>Noindex or delete them and add parameter handling for the quote form.</t>
         </is>
       </c>
     </row>
@@ -6046,15 +6046,37 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
+          <t>Two live pages cover the same service: /clinical-waste-disposal-clinical-waste-collection-companies/ and /healthcare-waste/.</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Low priority because the clinical head terms are council dominated and not winnable anyway. Worth tidying when you next touch that area.</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Merge into one page and point it at commercial terms such as dental waste disposal and sharps bin collection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
           <t>Four former pages now return 404: /better-waste-solutions-birmingham/, /better-waste-solutions-london/, /better-waste-solutions-manchester/ and /business-waste-management-yorkshire/.</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>If anyone links to these the value is being thrown away. If nobody does, there is nothing to fix.</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Check referring domains for each. Redirect only the ones that actually hold links.</t>
         </is>

--- a/betterwaste-kw-audit/Better_Waste_Keyword_Plan.xlsx
+++ b/betterwaste-kw-audit/Better_Waste_Keyword_Plan.xlsx
@@ -5831,7 +5831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5870,17 +5870,17 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Manchester rankings sit entirely on a URL that looks retired. Semrush shows 16 keywords worth 5,080 SV on /areas-we-cover-old/manchester/, 9 of them in the top 20 and the best at p11. The intended page /areas-we-cover/manchester/ has zero keywords in Semrush. London and Birmingham are not affected, their current URLs rank normally.</t>
+          <t>The /areas-we-cover/ hub holds 90 ranking keywords, more than any page on the site except the homepage. Among them are national service terms it should not own: business refuse collection at p5 and 590 SV, waste collection for business at p59, commercial waste services at p54, industrial waste collection at p83 and waste disposal companies at p63.</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>All of your Manchester visibility, including commercial waste collection manchester at p20, is attached to a URL nobody is maintaining or linking to. Any work on the intended page will not connect to it.</t>
+          <t>A location hub is the wrong page for national commercial terms. Someone searching business refuse collection lands on a list of areas instead of a service page, and the terms cannot be properly optimised while they sit there.</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Check where /areas-we-cover/manchester/ redirects to. If it points at the older URL, rename that one as canonical and keep the rankings. If it points elsewhere, the redirect is the bug. Do not redirect old to new without checking, it may create a loop.</t>
+          <t>Move the national service terms onto /commercial-waste-collection/ and let the hub cover locations only.</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>It is one position band away from page one on an existing page. Nothing else on the site is this close for this little work.</t>
+          <t>It is one position band off page one, on a page that already exists and already ranks.</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -5907,24 +5907,24 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>The site answers on both www and non www. betterwaste.co.uk/polystyrene-and-recycling/ and www.betterwaste.co.uk/polystyrene-and-recycling both rank as separate pages.</t>
+          <t>Four pages target the same commercial terms but only two rank at all. /business-waste-collections/ has 4 keywords and /commercial-waste-management/ has 1. /commercial-waste-collection/ and /trade-waste-collections/ rank for nothing. business waste collection at 2,400 SV ranks twice, p26 with one page and p34 with the other.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Every page is competing with a copy of itself. Links and ranking signals are split in half across two versions of the site.</t>
+          <t>The commercial terms are spread across four pages and none of them is winning. Two of the four are invisible in search despite being live.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Pick one hostname. Add a site wide redirect, set the canonical tag and set the preferred property in Search Console.</t>
+          <t>Pick /commercial-waste-collection/ as the single commercial page, since the plan targets it. Redirect or de optimise the other three.</t>
         </is>
       </c>
     </row>
@@ -5936,149 +5936,61 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>The London and Birmingham city URLs were recorded as redirecting when Ahrefs last crawled the site on 28 and 29 July 2026, yet both rank normally in Semrush today. /areas-we-cover-old/london/ and /areas-we-cover-old/birmingham/ still return 200 with live page titles.</t>
+          <t>Your best ranking page is a blog post listing competitors. /top-10-commercial-waste-management-companies-in-the-uk/ holds 19 keywords and 77 of the site's estimated monthly visits, second only to the homepage. It also outranks your own service page for commercial waste management companies, p7 against p90.</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Nothing is broken in the rankings, so this is not urgent. But two live copies of each city page is the same duplication problem as the www issue, and the crawl data is two months old so the current state is unconfirmed.</t>
+          <t>It is the strongest asset on the site, it sends in market visitors to read about competitors, and it passes none of that authority to a page that converts.</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Open both current city URLs and both older ones in a browser. If the older pages still load, redirect them to the current ones.</t>
+          <t>Add prominent internal links from it to /commercial-waste-collection/.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Four live pages chase the same commercial terms: /commercial-waste-collection/, /commercial-waste-management/, /business-waste-collections/ and /trade-waste-collections/. On top of that the /areas-we-cover/ hub ranks for national terms like business refuse collection at p5.</t>
+          <t>Six keywords return two of your own URLs at the same time. Examples: business waste birmingham at p19 and p26, waste management companies london at p29 and p32, aluminium recycling at p18 and p24, zero waste to landfill at p54 and p60.</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>business waste collection at 2,400 SV ranks twice, p26 and p34, and neither gets near the top 20. Five pages are sharing the authority that one page needs.</t>
+          <t>Two of your pages are competing for the same search instead of one ranking well.</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Make /commercial-waste-collection/ the single commercial page. Redirect or de optimise the other three and remove the national terms from the areas hub.</t>
+          <t>Find the duplicate or near duplicate page behind each and consolidate.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Your strongest page is a blog post listing competitors. /top-10-commercial-waste-management-companies-in-the-uk/ ranks p4 to p8 for around 20 head terms and links nowhere useful. It also outranks your own service page for commercial waste management companies, p7 against p90.</t>
+          <t>Semrush still shows 16 keywords worth 5,080 SV on /areas-we-cover-old/manchester/, including commercial waste collection manchester at p20. You have confirmed the old URL now redirects to the current one.</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>It is the best ranking asset on the site, it sends in market visitors to read about competitors, and it passes none of its authority to a page that converts.</t>
+          <t>No action needed. Semrush is lagging behind the redirect. Worth watching rather than fixing.</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Add prominent internal links from it to /commercial-waste-collection/ and reframe it so the service page wins the commercial terms.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Pages load on both the slash and non slash URL, and six keywords return two of your own URLs at once. Examples: /about and /about/, business waste birmingham at p19 and p26, waste management companies london at p29 and p32.</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Same problem as the www issue but smaller. It dilutes signals on individual pages rather than the whole site.</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Pick one trailing slash convention and redirect the other. Find the duplicate page behind each doubled keyword and consolidate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Test and leftover pages are indexable: /222-2/, /test-2/, /home/, /thank-you/, /trial-form/, /quote2-old/ and two other old quote forms. /quote2/ also has six indexable parameter versions.</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Low impact on its own, but it is wasted crawl budget and these pages say nothing good about site quality.</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Noindex or delete them and add parameter handling for the quote form.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Two live pages cover the same service: /clinical-waste-disposal-clinical-waste-collection-companies/ and /healthcare-waste/.</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Low priority because the clinical head terms are council dominated and not winnable anyway. Worth tidying when you next touch that area.</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Merge into one page and point it at commercial terms such as dental waste disposal and sharps bin collection.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Four former pages now return 404: /better-waste-solutions-birmingham/, /better-waste-solutions-london/, /better-waste-solutions-manchester/ and /business-waste-management-yorkshire/.</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>If anyone links to these the value is being thrown away. If nobody does, there is nothing to fix.</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Check referring domains for each. Redirect only the ones that actually hold links.</t>
+          <t>Check in four to eight weeks that the 16 keywords have moved onto /areas-we-cover/manchester/. If they have not, the redirect needs looking at.</t>
         </is>
       </c>
     </row>
